--- a/www/flightdata/xlsx/eoss-358.xlsx
+++ b/www/flightdata/xlsx/eoss-358.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="991" uniqueCount="368">
   <si>
     <t>flight</t>
   </si>
@@ -36,6 +36,18 @@
     <t>h2fill</t>
   </si>
   <si>
+    <t>maxaltitude</t>
+  </si>
+  <si>
+    <t>numpoints</t>
+  </si>
+  <si>
+    <t>flighttime</t>
+  </si>
+  <si>
+    <t>flighttime_secs</t>
+  </si>
+  <si>
     <t>weights.client</t>
   </si>
   <si>
@@ -73,6 +85,9 @@
   </si>
   <si>
     <t>267</t>
+  </si>
+  <si>
+    <t>1hrs 27mins 49secs</t>
   </si>
   <si>
     <t>6.64</t>
@@ -1466,10 +1481,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1509,46 +1524,70 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="G2">
+        <v>89485</v>
+      </c>
+      <c r="H2">
+        <v>150</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
-      </c>
-      <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="J2">
+        <v>5269</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -1563,102 +1602,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2">
         <v>45416.28501981482</v>
@@ -1676,13 +1715,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="J2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K2">
         <v>20</v>
@@ -1718,7 +1757,7 @@
         <v>5.13333333</v>
       </c>
       <c r="V2" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="X2">
         <v>5.133333</v>
@@ -1729,10 +1768,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
         <v>45416.28524439815</v>
@@ -1750,13 +1789,13 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I3" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K3">
         <v>59</v>
@@ -1792,7 +1831,7 @@
         <v>18.13333333</v>
       </c>
       <c r="V3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W3">
         <v>0.433333</v>
@@ -1815,10 +1854,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2">
         <v>45416.28533979167</v>
@@ -1836,13 +1875,13 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I4" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="J4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="K4">
         <v>116</v>
@@ -1878,7 +1917,7 @@
         <v>19.6</v>
       </c>
       <c r="V4" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W4">
         <v>0.048889</v>
@@ -1907,10 +1946,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C5" s="2">
         <v>45416.28556251158</v>
@@ -1928,13 +1967,13 @@
         <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I5" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="J5" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K5">
         <v>298</v>
@@ -1970,7 +2009,7 @@
         <v>21.63333333</v>
       </c>
       <c r="V5" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W5">
         <v>0.067778</v>
@@ -1999,10 +2038,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2">
         <v>45416.28571474537</v>
@@ -2020,13 +2059,13 @@
         <v>60</v>
       </c>
       <c r="H6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="J6" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="K6">
         <v>314</v>
@@ -2062,7 +2101,7 @@
         <v>21</v>
       </c>
       <c r="V6" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W6">
         <v>-0.021111</v>
@@ -2091,10 +2130,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C7" s="2">
         <v>45416.28593912037</v>
@@ -2112,13 +2151,13 @@
         <v>79</v>
       </c>
       <c r="H7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J7" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="K7">
         <v>275</v>
@@ -2154,7 +2193,7 @@
         <v>18.63333333</v>
       </c>
       <c r="V7" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W7">
         <v>-0.078889</v>
@@ -2183,10 +2222,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2">
         <v>45416.28603229167</v>
@@ -2204,13 +2243,13 @@
         <v>90</v>
       </c>
       <c r="H8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I8" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J8" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="K8">
         <v>271</v>
@@ -2246,7 +2285,7 @@
         <v>19.16666667</v>
       </c>
       <c r="V8" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W8">
         <v>0.017778</v>
@@ -2275,10 +2314,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C9" s="2">
         <v>45416.28625826389</v>
@@ -2296,13 +2335,13 @@
         <v>109</v>
       </c>
       <c r="H9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="J9" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="K9">
         <v>271</v>
@@ -2338,7 +2377,7 @@
         <v>19.56666667</v>
       </c>
       <c r="V9" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W9">
         <v>0.013333</v>
@@ -2367,10 +2406,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C10" s="2">
         <v>45416.28640918982</v>
@@ -2388,13 +2427,13 @@
         <v>120</v>
       </c>
       <c r="H10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J10" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K10">
         <v>244</v>
@@ -2430,7 +2469,7 @@
         <v>19.86666667</v>
       </c>
       <c r="V10" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W10">
         <v>0.01</v>
@@ -2459,10 +2498,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C11" s="2">
         <v>45416.28663488426</v>
@@ -2480,13 +2519,13 @@
         <v>139</v>
       </c>
       <c r="H11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I11" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J11" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="K11">
         <v>246</v>
@@ -2522,7 +2561,7 @@
         <v>21</v>
       </c>
       <c r="V11" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W11">
         <v>0.037778</v>
@@ -2551,10 +2590,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C12" s="2">
         <v>45416.28672798611</v>
@@ -2572,13 +2611,13 @@
         <v>150</v>
       </c>
       <c r="H12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I12" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J12" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="K12">
         <v>210</v>
@@ -2614,7 +2653,7 @@
         <v>21.4</v>
       </c>
       <c r="V12" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W12">
         <v>0.013333</v>
@@ -2643,10 +2682,10 @@
     </row>
     <row r="13" spans="1:30">
       <c r="A13" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C13" s="2">
         <v>45416.28695288194</v>
@@ -2664,13 +2703,13 @@
         <v>169</v>
       </c>
       <c r="H13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I13" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J13" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="K13">
         <v>183</v>
@@ -2706,7 +2745,7 @@
         <v>21.43333333</v>
       </c>
       <c r="V13" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W13">
         <v>0.001111</v>
@@ -2735,10 +2774,10 @@
     </row>
     <row r="14" spans="1:30">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2">
         <v>45416.28710354167</v>
@@ -2756,13 +2795,13 @@
         <v>180</v>
       </c>
       <c r="H14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I14" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J14" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="K14">
         <v>234</v>
@@ -2798,7 +2837,7 @@
         <v>20.1</v>
       </c>
       <c r="V14" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W14">
         <v>-0.044444</v>
@@ -2827,10 +2866,10 @@
     </row>
     <row r="15" spans="1:30">
       <c r="A15" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C15" s="2">
         <v>45416.2874396412</v>
@@ -2848,13 +2887,13 @@
         <v>210</v>
       </c>
       <c r="H15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I15" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="K15">
         <v>149</v>
@@ -2890,7 +2929,7 @@
         <v>21.03333333</v>
       </c>
       <c r="V15" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W15">
         <v>0.031111</v>
@@ -2919,10 +2958,10 @@
     </row>
     <row r="16" spans="1:30">
       <c r="A16" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C16" s="2">
         <v>45416.28764791667</v>
@@ -2940,13 +2979,13 @@
         <v>229</v>
       </c>
       <c r="H16" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I16" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="J16" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K16">
         <v>66</v>
@@ -2982,7 +3021,7 @@
         <v>20.88333333</v>
       </c>
       <c r="V16" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W16">
         <v>-0.0025</v>
@@ -3011,10 +3050,10 @@
     </row>
     <row r="17" spans="1:30">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C17" s="2">
         <v>45416.28779834491</v>
@@ -3032,13 +3071,13 @@
         <v>240</v>
       </c>
       <c r="H17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I17" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="J17" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K17">
         <v>109</v>
@@ -3074,7 +3113,7 @@
         <v>20.5</v>
       </c>
       <c r="V17" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W17">
         <v>-0.012778</v>
@@ -3103,10 +3142,10 @@
     </row>
     <row r="18" spans="1:30">
       <c r="A18" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C18" s="2">
         <v>45416.28811732639</v>
@@ -3124,13 +3163,13 @@
         <v>270</v>
       </c>
       <c r="H18" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I18" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J18" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K18">
         <v>34</v>
@@ -3166,7 +3205,7 @@
         <v>21.5</v>
       </c>
       <c r="V18" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W18">
         <v>0.033333</v>
@@ -3195,10 +3234,10 @@
     </row>
     <row r="19" spans="1:30">
       <c r="A19" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C19" s="2">
         <v>45416.28834163195</v>
@@ -3216,13 +3255,13 @@
         <v>289</v>
       </c>
       <c r="H19" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I19" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J19" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K19">
         <v>42</v>
@@ -3258,7 +3297,7 @@
         <v>20.15</v>
       </c>
       <c r="V19" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W19">
         <v>-0.0225</v>
@@ -3287,10 +3326,10 @@
     </row>
     <row r="20" spans="1:30">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B20" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2">
         <v>45416.28849383102</v>
@@ -3308,13 +3347,13 @@
         <v>300</v>
       </c>
       <c r="H20" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I20" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="J20" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="K20">
         <v>65</v>
@@ -3350,7 +3389,7 @@
         <v>20.63333333</v>
       </c>
       <c r="V20" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W20">
         <v>0.016111</v>
@@ -3379,10 +3418,10 @@
     </row>
     <row r="21" spans="1:30">
       <c r="A21" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C21" s="2">
         <v>45416.28881193287</v>
@@ -3400,13 +3439,13 @@
         <v>330</v>
       </c>
       <c r="H21" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I21" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="K21">
         <v>56</v>
@@ -3442,7 +3481,7 @@
         <v>17.86666667</v>
       </c>
       <c r="V21" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W21">
         <v>-0.092222</v>
@@ -3471,10 +3510,10 @@
     </row>
     <row r="22" spans="1:30">
       <c r="A22" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C22" s="2">
         <v>45416.28903572917</v>
@@ -3492,13 +3531,13 @@
         <v>349</v>
       </c>
       <c r="H22" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I22" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="K22">
         <v>72</v>
@@ -3534,7 +3573,7 @@
         <v>19.18333333</v>
       </c>
       <c r="V22" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W22">
         <v>0.021944</v>
@@ -3563,10 +3602,10 @@
     </row>
     <row r="23" spans="1:30">
       <c r="A23" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2">
         <v>45416.28918784722</v>
@@ -3584,13 +3623,13 @@
         <v>360</v>
       </c>
       <c r="H23" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I23" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="K23">
         <v>95</v>
@@ -3626,7 +3665,7 @@
         <v>19.03333333</v>
       </c>
       <c r="V23" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W23">
         <v>-0.005</v>
@@ -3655,10 +3694,10 @@
     </row>
     <row r="24" spans="1:30">
       <c r="A24" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2">
         <v>45416.28950773148</v>
@@ -3676,13 +3715,13 @@
         <v>390</v>
       </c>
       <c r="H24" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I24" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J24" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="K24">
         <v>80</v>
@@ -3718,7 +3757,7 @@
         <v>18.83333333</v>
       </c>
       <c r="V24" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W24">
         <v>-0.006667</v>
@@ -3747,10 +3786,10 @@
     </row>
     <row r="25" spans="1:30">
       <c r="A25" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2">
         <v>45416.28972934028</v>
@@ -3768,13 +3807,13 @@
         <v>409</v>
       </c>
       <c r="H25" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I25" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="J25" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="K25">
         <v>89</v>
@@ -3810,7 +3849,7 @@
         <v>18.76666667</v>
       </c>
       <c r="V25" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W25">
         <v>-0.001111</v>
@@ -3839,10 +3878,10 @@
     </row>
     <row r="26" spans="1:30">
       <c r="A26" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C26" s="2">
         <v>45416.28988243055</v>
@@ -3860,13 +3899,13 @@
         <v>420</v>
       </c>
       <c r="H26" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I26" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J26" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="K26">
         <v>81</v>
@@ -3902,7 +3941,7 @@
         <v>19.5</v>
       </c>
       <c r="V26" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W26">
         <v>0.024444</v>
@@ -3931,10 +3970,10 @@
     </row>
     <row r="27" spans="1:30">
       <c r="A27" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C27" s="2">
         <v>45416.2902003125</v>
@@ -3952,13 +3991,13 @@
         <v>450</v>
       </c>
       <c r="H27" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I27" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="J27" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="K27">
         <v>84</v>
@@ -3994,7 +4033,7 @@
         <v>19.66666667</v>
       </c>
       <c r="V27" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W27">
         <v>0.005556</v>
@@ -4023,10 +4062,10 @@
     </row>
     <row r="28" spans="1:30">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C28" s="2">
         <v>45416.29042340278</v>
@@ -4044,13 +4083,13 @@
         <v>469</v>
       </c>
       <c r="H28" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I28" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="J28" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="K28">
         <v>82</v>
@@ -4086,7 +4125,7 @@
         <v>19.38333333</v>
       </c>
       <c r="V28" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W28">
         <v>-0.004722</v>
@@ -4115,10 +4154,10 @@
     </row>
     <row r="29" spans="1:30">
       <c r="A29" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B29" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C29" s="2">
         <v>45416.29057700231</v>
@@ -4136,13 +4175,13 @@
         <v>480</v>
       </c>
       <c r="H29" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I29" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="J29" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="K29">
         <v>99</v>
@@ -4178,7 +4217,7 @@
         <v>18.13333333</v>
       </c>
       <c r="V29" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W29">
         <v>-0.041667</v>
@@ -4207,10 +4246,10 @@
     </row>
     <row r="30" spans="1:30">
       <c r="A30" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2">
         <v>45416.29089520833</v>
@@ -4228,13 +4267,13 @@
         <v>510</v>
       </c>
       <c r="H30" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I30" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="J30" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="K30">
         <v>96</v>
@@ -4270,7 +4309,7 @@
         <v>18.4</v>
       </c>
       <c r="V30" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W30">
         <v>0.008888999999999999</v>
@@ -4299,10 +4338,10 @@
     </row>
     <row r="31" spans="1:30">
       <c r="A31" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2">
         <v>45416.29111777778</v>
@@ -4320,13 +4359,13 @@
         <v>529</v>
       </c>
       <c r="H31" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I31" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J31" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="K31">
         <v>106</v>
@@ -4362,7 +4401,7 @@
         <v>18.25</v>
       </c>
       <c r="V31" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W31">
         <v>-0.0025</v>
@@ -4391,10 +4430,10 @@
     </row>
     <row r="32" spans="1:30">
       <c r="A32" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2">
         <v>45416.29127113426</v>
@@ -4412,13 +4451,13 @@
         <v>540</v>
       </c>
       <c r="H32" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I32" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J32" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="K32">
         <v>97</v>
@@ -4454,7 +4493,7 @@
         <v>17.23333333</v>
       </c>
       <c r="V32" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W32">
         <v>-0.033889</v>
@@ -4483,10 +4522,10 @@
     </row>
     <row r="33" spans="1:30">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B33" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C33" s="2">
         <v>45416.29158898148</v>
@@ -4504,13 +4543,13 @@
         <v>570</v>
       </c>
       <c r="H33" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I33" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J33" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="K33">
         <v>95</v>
@@ -4546,7 +4585,7 @@
         <v>21.13333333</v>
       </c>
       <c r="V33" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W33">
         <v>0.13</v>
@@ -4575,10 +4614,10 @@
     </row>
     <row r="34" spans="1:30">
       <c r="A34" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C34" s="2">
         <v>45416.29181238426</v>
@@ -4596,13 +4635,13 @@
         <v>589</v>
       </c>
       <c r="H34" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I34" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="J34" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="K34">
         <v>88</v>
@@ -4638,7 +4677,7 @@
         <v>19.26666667</v>
       </c>
       <c r="V34" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W34">
         <v>-0.031111</v>
@@ -4667,10 +4706,10 @@
     </row>
     <row r="35" spans="1:30">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C35" s="2">
         <v>45416.29196631945</v>
@@ -4688,13 +4727,13 @@
         <v>600</v>
       </c>
       <c r="H35" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I35" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="J35" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="K35">
         <v>105</v>
@@ -4730,7 +4769,7 @@
         <v>17.83333333</v>
       </c>
       <c r="V35" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W35">
         <v>-0.047778</v>
@@ -4759,10 +4798,10 @@
     </row>
     <row r="36" spans="1:30">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C36" s="2">
         <v>45416.2922846875</v>
@@ -4780,13 +4819,13 @@
         <v>630</v>
       </c>
       <c r="H36" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I36" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J36" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="K36">
         <v>111</v>
@@ -4822,7 +4861,7 @@
         <v>17.9</v>
       </c>
       <c r="V36" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W36">
         <v>0.002222</v>
@@ -4851,10 +4890,10 @@
     </row>
     <row r="37" spans="1:30">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2">
         <v>45416.29266038194</v>
@@ -4872,13 +4911,13 @@
         <v>660</v>
       </c>
       <c r="H37" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J37" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="K37">
         <v>90</v>
@@ -4914,7 +4953,7 @@
         <v>20.13333333</v>
       </c>
       <c r="V37" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W37">
         <v>0.074444</v>
@@ -4943,10 +4982,10 @@
     </row>
     <row r="38" spans="1:30">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C38" s="2">
         <v>45416.292978125</v>
@@ -4964,13 +5003,13 @@
         <v>690</v>
       </c>
       <c r="H38" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I38" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J38" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="K38">
         <v>69</v>
@@ -5006,7 +5045,7 @@
         <v>18.76666667</v>
       </c>
       <c r="V38" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W38">
         <v>-0.045556</v>
@@ -5035,10 +5074,10 @@
     </row>
     <row r="39" spans="1:30">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B39" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C39" s="2">
         <v>45416.29335501158</v>
@@ -5056,13 +5095,13 @@
         <v>720</v>
       </c>
       <c r="H39" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I39" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J39" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="K39">
         <v>63</v>
@@ -5098,7 +5137,7 @@
         <v>18.03333333</v>
       </c>
       <c r="V39" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W39">
         <v>-0.024444</v>
@@ -5127,10 +5166,10 @@
     </row>
     <row r="40" spans="1:30">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C40" s="2">
         <v>45416.29367321759</v>
@@ -5148,13 +5187,13 @@
         <v>750</v>
       </c>
       <c r="H40" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I40" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="J40" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="K40">
         <v>87</v>
@@ -5190,7 +5229,7 @@
         <v>17.2</v>
       </c>
       <c r="V40" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W40">
         <v>-0.027778</v>
@@ -5219,10 +5258,10 @@
     </row>
     <row r="41" spans="1:30">
       <c r="A41" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B41" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C41" s="2">
         <v>45416.29405516203</v>
@@ -5240,13 +5279,13 @@
         <v>780</v>
       </c>
       <c r="H41" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I41" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J41" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="K41">
         <v>96</v>
@@ -5282,7 +5321,7 @@
         <v>18.43333333</v>
       </c>
       <c r="V41" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W41">
         <v>0.041111</v>
@@ -5311,10 +5350,10 @@
     </row>
     <row r="42" spans="1:30">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C42" s="2">
         <v>45416.29436784722</v>
@@ -5332,13 +5371,13 @@
         <v>810</v>
       </c>
       <c r="H42" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I42" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="J42" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="K42">
         <v>75</v>
@@ -5374,7 +5413,7 @@
         <v>19.23333333</v>
       </c>
       <c r="V42" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W42">
         <v>0.026667</v>
@@ -5403,10 +5442,10 @@
     </row>
     <row r="43" spans="1:30">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C43" s="2">
         <v>45416.29474569445</v>
@@ -5424,13 +5463,13 @@
         <v>840</v>
       </c>
       <c r="H43" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I43" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="J43" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="K43">
         <v>94</v>
@@ -5466,7 +5505,7 @@
         <v>16.4</v>
       </c>
       <c r="V43" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W43">
         <v>-0.094444</v>
@@ -5495,10 +5534,10 @@
     </row>
     <row r="44" spans="1:30">
       <c r="A44" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B44" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C44" s="2">
         <v>45416.29506273148</v>
@@ -5516,13 +5555,13 @@
         <v>870</v>
       </c>
       <c r="H44" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I44" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="J44" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="K44">
         <v>90</v>
@@ -5558,7 +5597,7 @@
         <v>18.03333333</v>
       </c>
       <c r="V44" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W44">
         <v>0.054444</v>
@@ -5587,10 +5626,10 @@
     </row>
     <row r="45" spans="1:30">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B45" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C45" s="2">
         <v>45416.29543877315</v>
@@ -5608,13 +5647,13 @@
         <v>900</v>
       </c>
       <c r="H45" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I45" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="J45" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="K45">
         <v>98</v>
@@ -5650,7 +5689,7 @@
         <v>16.83333333</v>
       </c>
       <c r="V45" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W45">
         <v>-0.04</v>
@@ -5679,10 +5718,10 @@
     </row>
     <row r="46" spans="1:30">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B46" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C46" s="2">
         <v>45416.29575668981</v>
@@ -5700,13 +5739,13 @@
         <v>930</v>
       </c>
       <c r="H46" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I46" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="J46" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="K46">
         <v>86</v>
@@ -5742,7 +5781,7 @@
         <v>20.6</v>
       </c>
       <c r="V46" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W46">
         <v>0.125556</v>
@@ -5771,10 +5810,10 @@
     </row>
     <row r="47" spans="1:30">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B47" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C47" s="2">
         <v>45416.29613241898</v>
@@ -5792,13 +5831,13 @@
         <v>960</v>
       </c>
       <c r="H47" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I47" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J47" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="K47">
         <v>93</v>
@@ -5834,7 +5873,7 @@
         <v>17.86666667</v>
       </c>
       <c r="V47" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W47">
         <v>-0.091111</v>
@@ -5863,10 +5902,10 @@
     </row>
     <row r="48" spans="1:30">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B48" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C48" s="2">
         <v>45416.29645150463</v>
@@ -5884,13 +5923,13 @@
         <v>990</v>
       </c>
       <c r="H48" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I48" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="J48" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="K48">
         <v>72</v>
@@ -5926,7 +5965,7 @@
         <v>17.36666667</v>
       </c>
       <c r="V48" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W48">
         <v>-0.016667</v>
@@ -5955,10 +5994,10 @@
     </row>
     <row r="49" spans="1:30">
       <c r="A49" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B49" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C49" s="2">
         <v>45416.29682668982</v>
@@ -5976,13 +6015,13 @@
         <v>1020</v>
       </c>
       <c r="H49" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I49" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J49" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="K49">
         <v>68</v>
@@ -6018,7 +6057,7 @@
         <v>16.36666667</v>
       </c>
       <c r="V49" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W49">
         <v>-0.033333</v>
@@ -6047,10 +6086,10 @@
     </row>
     <row r="50" spans="1:30">
       <c r="A50" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B50" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C50" s="2">
         <v>45416.29714474537</v>
@@ -6068,13 +6107,13 @@
         <v>1050</v>
       </c>
       <c r="H50" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I50" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J50" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="K50">
         <v>84</v>
@@ -6110,7 +6149,7 @@
         <v>20.1</v>
       </c>
       <c r="V50" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W50">
         <v>0.124444</v>
@@ -6139,10 +6178,10 @@
     </row>
     <row r="51" spans="1:30">
       <c r="A51" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B51" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C51" s="2">
         <v>45416.29737010417</v>
@@ -6160,13 +6199,13 @@
         <v>1069</v>
       </c>
       <c r="H51" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I51" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J51" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="K51">
         <v>83</v>
@@ -6202,7 +6241,7 @@
         <v>18.21875</v>
       </c>
       <c r="V51" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W51">
         <v>-0.003919</v>
@@ -6231,10 +6270,10 @@
     </row>
     <row r="52" spans="1:30">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B52" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2">
         <v>45416.29752219907</v>
@@ -6252,13 +6291,13 @@
         <v>1080</v>
       </c>
       <c r="H52" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I52" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="J52" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="K52">
         <v>85</v>
@@ -6294,7 +6333,7 @@
         <v>18.66666667</v>
       </c>
       <c r="V52" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W52">
         <v>0.014931</v>
@@ -6323,10 +6362,10 @@
     </row>
     <row r="53" spans="1:30">
       <c r="A53" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B53" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C53" s="2">
         <v>45416.29783983796</v>
@@ -6344,13 +6383,13 @@
         <v>1110</v>
       </c>
       <c r="H53" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I53" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="J53" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="K53">
         <v>84</v>
@@ -6386,7 +6425,7 @@
         <v>17.66666667</v>
       </c>
       <c r="V53" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W53">
         <v>-0.033333</v>
@@ -6415,10 +6454,10 @@
     </row>
     <row r="54" spans="1:30">
       <c r="A54" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B54" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C54" s="2">
         <v>45416.29821638889</v>
@@ -6436,13 +6475,13 @@
         <v>1140</v>
       </c>
       <c r="H54" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I54" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="J54" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="K54">
         <v>68</v>
@@ -6478,7 +6517,7 @@
         <v>17.46666667</v>
       </c>
       <c r="V54" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W54">
         <v>-0.006667</v>
@@ -6507,10 +6546,10 @@
     </row>
     <row r="55" spans="1:30">
       <c r="A55" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B55" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C55" s="2">
         <v>45416.29853439815</v>
@@ -6528,13 +6567,13 @@
         <v>1170</v>
       </c>
       <c r="H55" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I55" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="J55" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="K55">
         <v>78</v>
@@ -6570,7 +6609,7 @@
         <v>18.9</v>
       </c>
       <c r="V55" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W55">
         <v>0.047778</v>
@@ -6599,10 +6638,10 @@
     </row>
     <row r="56" spans="1:30">
       <c r="A56" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B56" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C56" s="2">
         <v>45416.29890998843</v>
@@ -6620,13 +6659,13 @@
         <v>1200</v>
       </c>
       <c r="H56" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I56" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="J56" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="K56">
         <v>96</v>
@@ -6662,7 +6701,7 @@
         <v>21.23333333</v>
       </c>
       <c r="V56" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W56">
         <v>0.077778</v>
@@ -6691,10 +6730,10 @@
     </row>
     <row r="57" spans="1:30">
       <c r="A57" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B57" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C57" s="2">
         <v>45416.2991312963</v>
@@ -6712,13 +6751,13 @@
         <v>1219</v>
       </c>
       <c r="H57" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I57" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="J57" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="K57">
         <v>73</v>
@@ -6754,7 +6793,7 @@
         <v>18.89333333</v>
       </c>
       <c r="V57" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W57">
         <v>-0.0156</v>
@@ -6783,10 +6822,10 @@
     </row>
     <row r="58" spans="1:30">
       <c r="A58" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C58" s="2">
         <v>45416.29922893518</v>
@@ -6804,13 +6843,13 @@
         <v>1230</v>
       </c>
       <c r="H58" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I58" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="J58" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="K58">
         <v>61</v>
@@ -6846,7 +6885,7 @@
         <v>21.63333333</v>
       </c>
       <c r="V58" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W58">
         <v>0.091333</v>
@@ -6875,10 +6914,10 @@
     </row>
     <row r="59" spans="1:30">
       <c r="A59" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B59" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C59" s="2">
         <v>45416.2996050463</v>
@@ -6896,13 +6935,13 @@
         <v>1260</v>
       </c>
       <c r="H59" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I59" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J59" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="K59">
         <v>68</v>
@@ -6938,7 +6977,7 @@
         <v>22.03333333</v>
       </c>
       <c r="V59" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W59">
         <v>0.013333</v>
@@ -6967,10 +7006,10 @@
     </row>
     <row r="60" spans="1:30">
       <c r="A60" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C60" s="2">
         <v>45416.29982586805</v>
@@ -6988,13 +7027,13 @@
         <v>1279</v>
       </c>
       <c r="H60" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I60" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="J60" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="K60">
         <v>65</v>
@@ -7030,7 +7069,7 @@
         <v>21.28333333</v>
       </c>
       <c r="V60" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W60">
         <v>-0.0125</v>
@@ -7059,10 +7098,10 @@
     </row>
     <row r="61" spans="1:30">
       <c r="A61" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B61" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C61" s="2">
         <v>45416.29992278935</v>
@@ -7080,13 +7119,13 @@
         <v>1290</v>
       </c>
       <c r="H61" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I61" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="J61" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K61">
         <v>90</v>
@@ -7122,7 +7161,7 @@
         <v>17.86666667</v>
       </c>
       <c r="V61" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W61">
         <v>-0.113889</v>
@@ -7151,10 +7190,10 @@
     </row>
     <row r="62" spans="1:30">
       <c r="A62" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B62" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C62" s="2">
         <v>45416.30029982639</v>
@@ -7172,13 +7211,13 @@
         <v>1320</v>
       </c>
       <c r="H62" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I62" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="J62" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="K62">
         <v>83</v>
@@ -7214,7 +7253,7 @@
         <v>22.16666667</v>
       </c>
       <c r="V62" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W62">
         <v>0.143333</v>
@@ -7243,10 +7282,10 @@
     </row>
     <row r="63" spans="1:30">
       <c r="A63" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C63" s="2">
         <v>45416.30061722222</v>
@@ -7264,13 +7303,13 @@
         <v>1350</v>
       </c>
       <c r="H63" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I63" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="J63" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K63">
         <v>80</v>
@@ -7306,7 +7345,7 @@
         <v>16.9</v>
       </c>
       <c r="V63" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W63">
         <v>-0.175556</v>
@@ -7335,10 +7374,10 @@
     </row>
     <row r="64" spans="1:30">
       <c r="A64" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B64" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C64" s="2">
         <v>45416.3009994213</v>
@@ -7356,13 +7395,13 @@
         <v>1380</v>
       </c>
       <c r="H64" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I64" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="J64" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="K64">
         <v>78</v>
@@ -7398,7 +7437,7 @@
         <v>15.76666667</v>
       </c>
       <c r="V64" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W64">
         <v>-0.037778</v>
@@ -7427,10 +7466,10 @@
     </row>
     <row r="65" spans="1:30">
       <c r="A65" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B65" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C65" s="2">
         <v>45416.30131277778</v>
@@ -7448,13 +7487,13 @@
         <v>1410</v>
       </c>
       <c r="H65" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I65" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="J65" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="K65">
         <v>61</v>
@@ -7490,7 +7529,7 @@
         <v>16.36666667</v>
       </c>
       <c r="V65" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W65">
         <v>0.02</v>
@@ -7519,10 +7558,10 @@
     </row>
     <row r="66" spans="1:30">
       <c r="A66" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C66" s="2">
         <v>45416.3020066551</v>
@@ -7540,13 +7579,13 @@
         <v>1470</v>
       </c>
       <c r="H66" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I66" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J66" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K66">
         <v>69</v>
@@ -7582,7 +7621,7 @@
         <v>16.83333333</v>
       </c>
       <c r="V66" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W66">
         <v>0.007778</v>
@@ -7611,10 +7650,10 @@
     </row>
     <row r="67" spans="1:30">
       <c r="A67" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C67" s="2">
         <v>45416.30270140046</v>
@@ -7632,13 +7671,13 @@
         <v>1530</v>
       </c>
       <c r="H67" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I67" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="J67" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K67">
         <v>60</v>
@@ -7674,7 +7713,7 @@
         <v>18.18333333</v>
       </c>
       <c r="V67" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W67">
         <v>0.0225</v>
@@ -7703,10 +7742,10 @@
     </row>
     <row r="68" spans="1:30">
       <c r="A68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C68" s="2">
         <v>45416.30339539352</v>
@@ -7724,13 +7763,13 @@
         <v>1590</v>
       </c>
       <c r="H68" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I68" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J68" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="K68">
         <v>82</v>
@@ -7766,7 +7805,7 @@
         <v>20.5</v>
       </c>
       <c r="V68" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W68">
         <v>0.038611</v>
@@ -7795,10 +7834,10 @@
     </row>
     <row r="69" spans="1:30">
       <c r="A69" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C69" s="2">
         <v>45416.3036171412</v>
@@ -7816,13 +7855,13 @@
         <v>1609</v>
       </c>
       <c r="H69" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I69" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="J69" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="K69">
         <v>71</v>
@@ -7858,7 +7897,7 @@
         <v>18.53939394</v>
       </c>
       <c r="V69" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W69">
         <v>-0.005941</v>
@@ -7887,10 +7926,10 @@
     </row>
     <row r="70" spans="1:30">
       <c r="A70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C70" s="2">
         <v>45416.30399307871</v>
@@ -7908,13 +7947,13 @@
         <v>1639</v>
       </c>
       <c r="H70" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I70" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="J70" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="K70">
         <v>76</v>
@@ -7950,7 +7989,7 @@
         <v>21.2</v>
       </c>
       <c r="V70" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W70">
         <v>0.088687</v>
@@ -7979,10 +8018,10 @@
     </row>
     <row r="71" spans="1:30">
       <c r="A71" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B71" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C71" s="2">
         <v>45416.30408978009</v>
@@ -8000,13 +8039,13 @@
         <v>1650</v>
       </c>
       <c r="H71" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I71" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="J71" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K71">
         <v>91</v>
@@ -8042,7 +8081,7 @@
         <v>22.08333333</v>
       </c>
       <c r="V71" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W71">
         <v>0.014722</v>
@@ -8071,10 +8110,10 @@
     </row>
     <row r="72" spans="1:30">
       <c r="A72" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B72" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C72" s="2">
         <v>45416.30478475695</v>
@@ -8092,13 +8131,13 @@
         <v>1710</v>
       </c>
       <c r="H72" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I72" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J72" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="K72">
         <v>70</v>
@@ -8134,7 +8173,7 @@
         <v>18.38333333</v>
       </c>
       <c r="V72" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W72">
         <v>-0.061667</v>
@@ -8163,10 +8202,10 @@
     </row>
     <row r="73" spans="1:30">
       <c r="A73" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B73" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C73" s="2">
         <v>45416.30538291667</v>
@@ -8184,13 +8223,13 @@
         <v>1759</v>
       </c>
       <c r="H73" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I73" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J73" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="K73">
         <v>66</v>
@@ -8226,7 +8265,7 @@
         <v>18.26666667</v>
       </c>
       <c r="V73" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W73">
         <v>-0.000972</v>
@@ -8255,10 +8294,10 @@
     </row>
     <row r="74" spans="1:30">
       <c r="A74" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B74" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C74" s="2">
         <v>45416.30547902777</v>
@@ -8276,13 +8315,13 @@
         <v>1770</v>
       </c>
       <c r="H74" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I74" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="J74" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="K74">
         <v>79</v>
@@ -8318,7 +8357,7 @@
         <v>18.06666667</v>
       </c>
       <c r="V74" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W74">
         <v>-0.003333</v>
@@ -8347,10 +8386,10 @@
     </row>
     <row r="75" spans="1:30">
       <c r="A75" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B75" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C75" s="2">
         <v>45416.30617460649</v>
@@ -8368,13 +8407,13 @@
         <v>1830</v>
       </c>
       <c r="H75" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I75" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J75" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="K75">
         <v>79</v>
@@ -8410,7 +8449,7 @@
         <v>22.1</v>
       </c>
       <c r="V75" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W75">
         <v>0.067222</v>
@@ -8439,10 +8478,10 @@
     </row>
     <row r="76" spans="1:30">
       <c r="A76" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B76" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C76" s="2">
         <v>45416.30654905093</v>
@@ -8460,13 +8499,13 @@
         <v>1860</v>
       </c>
       <c r="H76" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I76" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="J76" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="K76">
         <v>88</v>
@@ -8502,7 +8541,7 @@
         <v>20</v>
       </c>
       <c r="V76" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W76">
         <v>-0.07000000000000001</v>
@@ -8531,10 +8570,10 @@
     </row>
     <row r="77" spans="1:30">
       <c r="A77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B77" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C77" s="2">
         <v>45416.30677236111</v>
@@ -8552,13 +8591,13 @@
         <v>1879</v>
       </c>
       <c r="H77" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I77" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="J77" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="K77">
         <v>65</v>
@@ -8594,7 +8633,7 @@
         <v>21.34166667</v>
       </c>
       <c r="V77" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W77">
         <v>0.011181</v>
@@ -8623,10 +8662,10 @@
     </row>
     <row r="78" spans="1:30">
       <c r="A78" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B78" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C78" s="2">
         <v>45416.30686834491</v>
@@ -8644,13 +8683,13 @@
         <v>1890</v>
       </c>
       <c r="H78" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I78" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="J78" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="K78">
         <v>58</v>
@@ -8686,7 +8725,7 @@
         <v>20.73333333</v>
       </c>
       <c r="V78" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W78">
         <v>-0.020278</v>
@@ -8715,10 +8754,10 @@
     </row>
     <row r="79" spans="1:30">
       <c r="A79" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B79" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C79" s="2">
         <v>45416.30709079861</v>
@@ -8736,13 +8775,13 @@
         <v>1909</v>
       </c>
       <c r="H79" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I79" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="J79" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="K79">
         <v>73</v>
@@ -8778,7 +8817,7 @@
         <v>21.23333333</v>
       </c>
       <c r="V79" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W79">
         <v>0.016667</v>
@@ -8807,10 +8846,10 @@
     </row>
     <row r="80" spans="1:30">
       <c r="A80" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B80" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C80" s="2">
         <v>45416.30724446759</v>
@@ -8828,13 +8867,13 @@
         <v>1920</v>
       </c>
       <c r="H80" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I80" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="J80" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="K80">
         <v>76</v>
@@ -8870,7 +8909,7 @@
         <v>22.23333333</v>
       </c>
       <c r="V80" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W80">
         <v>0.033333</v>
@@ -8899,10 +8938,10 @@
     </row>
     <row r="81" spans="1:30">
       <c r="A81" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B81" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C81" s="2">
         <v>45416.30746599537</v>
@@ -8920,13 +8959,13 @@
         <v>1939</v>
       </c>
       <c r="H81" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I81" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="J81" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="K81">
         <v>78</v>
@@ -8962,7 +9001,7 @@
         <v>20.23333333</v>
       </c>
       <c r="V81" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W81">
         <v>-0.066667</v>
@@ -8991,10 +9030,10 @@
     </row>
     <row r="82" spans="1:30">
       <c r="A82" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B82" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C82" s="2">
         <v>45416.3075621875</v>
@@ -9012,13 +9051,13 @@
         <v>1950</v>
       </c>
       <c r="H82" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I82" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="J82" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="K82">
         <v>69</v>
@@ -9054,7 +9093,7 @@
         <v>21.26666667</v>
       </c>
       <c r="V82" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W82">
         <v>0.034444</v>
@@ -9083,10 +9122,10 @@
     </row>
     <row r="83" spans="1:30">
       <c r="A83" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B83" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C83" s="2">
         <v>45416.30825726852</v>
@@ -9104,13 +9143,13 @@
         <v>2010</v>
       </c>
       <c r="H83" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I83" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J83" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="K83">
         <v>68</v>
@@ -9146,7 +9185,7 @@
         <v>20.58333333</v>
       </c>
       <c r="V83" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W83">
         <v>-0.011389</v>
@@ -9175,10 +9214,10 @@
     </row>
     <row r="84" spans="1:30">
       <c r="A84" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B84" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C84" s="2">
         <v>45416.30863371528</v>
@@ -9196,13 +9235,13 @@
         <v>2040</v>
       </c>
       <c r="H84" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I84" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="J84" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="K84">
         <v>80</v>
@@ -9238,7 +9277,7 @@
         <v>18.5</v>
       </c>
       <c r="V84" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W84">
         <v>-0.06944400000000001</v>
@@ -9267,10 +9306,10 @@
     </row>
     <row r="85" spans="1:30">
       <c r="A85" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B85" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C85" s="2">
         <v>45416.30895127315</v>
@@ -9288,13 +9327,13 @@
         <v>2070</v>
       </c>
       <c r="H85" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I85" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="J85" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="K85">
         <v>73</v>
@@ -9330,7 +9369,7 @@
         <v>20.96666667</v>
       </c>
       <c r="V85" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W85">
         <v>0.082222</v>
@@ -9359,10 +9398,10 @@
     </row>
     <row r="86" spans="1:30">
       <c r="A86" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B86" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C86" s="2">
         <v>45416.30955096065</v>
@@ -9380,13 +9419,13 @@
         <v>2119</v>
       </c>
       <c r="H86" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I86" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="J86" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="K86">
         <v>75</v>
@@ -9422,7 +9461,7 @@
         <v>19.82222222</v>
       </c>
       <c r="V86" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W86">
         <v>-0.006358</v>
@@ -9451,10 +9490,10 @@
     </row>
     <row r="87" spans="1:30">
       <c r="A87" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B87" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C87" s="2">
         <v>45416.30964634259</v>
@@ -9472,13 +9511,13 @@
         <v>2130</v>
       </c>
       <c r="H87" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I87" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="J87" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K87">
         <v>80</v>
@@ -9514,7 +9553,7 @@
         <v>17.85</v>
       </c>
       <c r="V87" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W87">
         <v>-0.03287</v>
@@ -9543,10 +9582,10 @@
     </row>
     <row r="88" spans="1:30">
       <c r="A88" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B88" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C88" s="2">
         <v>45416.31002208334</v>
@@ -9564,13 +9603,13 @@
         <v>2160</v>
       </c>
       <c r="H88" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I88" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="J88" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K88">
         <v>50</v>
@@ -9606,7 +9645,7 @@
         <v>19.16666667</v>
       </c>
       <c r="V88" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W88">
         <v>0.043889</v>
@@ -9635,10 +9674,10 @@
     </row>
     <row r="89" spans="1:30">
       <c r="A89" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B89" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C89" s="2">
         <v>45416.31036405093</v>
@@ -9656,13 +9695,13 @@
         <v>2190</v>
       </c>
       <c r="H89" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I89" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="J89" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K89">
         <v>77</v>
@@ -9698,7 +9737,7 @@
         <v>17.56666667</v>
       </c>
       <c r="V89" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W89">
         <v>-0.053333</v>
@@ -9727,10 +9766,10 @@
     </row>
     <row r="90" spans="1:30">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B90" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C90" s="2">
         <v>45416.31103505787</v>
@@ -9748,13 +9787,13 @@
         <v>2250</v>
       </c>
       <c r="H90" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I90" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J90" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="K90">
         <v>75</v>
@@ -9790,7 +9829,7 @@
         <v>17.15</v>
       </c>
       <c r="V90" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W90">
         <v>-0.006944</v>
@@ -9819,10 +9858,10 @@
     </row>
     <row r="91" spans="1:30">
       <c r="A91" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B91" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C91" s="2">
         <v>45416.31125788194</v>
@@ -9840,13 +9879,13 @@
         <v>2269</v>
       </c>
       <c r="H91" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I91" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="J91" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="K91">
         <v>75</v>
@@ -9882,7 +9921,7 @@
         <v>17.54</v>
       </c>
       <c r="V91" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W91">
         <v>0.0026</v>
@@ -9911,10 +9950,10 @@
     </row>
     <row r="92" spans="1:30">
       <c r="A92" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B92" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C92" s="2">
         <v>45416.31163385417</v>
@@ -9932,13 +9971,13 @@
         <v>2299</v>
       </c>
       <c r="H92" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I92" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="J92" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="K92">
         <v>78</v>
@@ -9974,7 +10013,7 @@
         <v>15.6</v>
       </c>
       <c r="V92" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W92">
         <v>-0.064667</v>
@@ -10003,10 +10042,10 @@
     </row>
     <row r="93" spans="1:30">
       <c r="A93" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B93" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C93" s="2">
         <v>45416.31173046296</v>
@@ -10024,13 +10063,13 @@
         <v>2310</v>
       </c>
       <c r="H93" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I93" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="J93" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="K93">
         <v>102</v>
@@ -10066,7 +10105,7 @@
         <v>16.36666667</v>
       </c>
       <c r="V93" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W93">
         <v>0.012778</v>
@@ -10095,10 +10134,10 @@
     </row>
     <row r="94" spans="1:30">
       <c r="A94" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B94" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C94" s="2">
         <v>45416.31210621528</v>
@@ -10116,13 +10155,13 @@
         <v>2340</v>
       </c>
       <c r="H94" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I94" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="J94" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="K94">
         <v>73</v>
@@ -10158,7 +10197,7 @@
         <v>18.03333333</v>
       </c>
       <c r="V94" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W94">
         <v>0.055556</v>
@@ -10187,10 +10226,10 @@
     </row>
     <row r="95" spans="1:30">
       <c r="A95" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B95" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C95" s="2">
         <v>45416.31242394676</v>
@@ -10208,13 +10247,13 @@
         <v>2370</v>
       </c>
       <c r="H95" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I95" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="J95" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="K95">
         <v>63</v>
@@ -10250,7 +10289,7 @@
         <v>18.13333333</v>
       </c>
       <c r="V95" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W95">
         <v>0.003333</v>
@@ -10279,10 +10318,10 @@
     </row>
     <row r="96" spans="1:30">
       <c r="A96" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B96" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C96" s="2">
         <v>45416.31311875</v>
@@ -10300,13 +10339,13 @@
         <v>2430</v>
       </c>
       <c r="H96" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I96" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="J96" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="K96">
         <v>82</v>
@@ -10342,7 +10381,7 @@
         <v>18.86666667</v>
       </c>
       <c r="V96" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W96">
         <v>0.012222</v>
@@ -10371,10 +10410,10 @@
     </row>
     <row r="97" spans="1:30">
       <c r="A97" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B97" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C97" s="2">
         <v>45416.31349582176</v>
@@ -10392,13 +10431,13 @@
         <v>2460</v>
       </c>
       <c r="H97" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I97" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="J97" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="K97">
         <v>56</v>
@@ -10434,7 +10473,7 @@
         <v>18.4</v>
       </c>
       <c r="V97" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W97">
         <v>-0.015556</v>
@@ -10463,10 +10502,10 @@
     </row>
     <row r="98" spans="1:30">
       <c r="A98" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B98" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C98" s="2">
         <v>45416.31441143518</v>
@@ -10484,13 +10523,13 @@
         <v>2539</v>
       </c>
       <c r="H98" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I98" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="J98" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K98">
         <v>78</v>
@@ -10526,7 +10565,7 @@
         <v>18.30416667</v>
       </c>
       <c r="V98" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W98">
         <v>-0.000399</v>
@@ -10555,10 +10594,10 @@
     </row>
     <row r="99" spans="1:30">
       <c r="A99" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B99" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C99" s="2">
         <v>45416.31450773148</v>
@@ -10576,13 +10615,13 @@
         <v>2550</v>
       </c>
       <c r="H99" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I99" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="J99" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="K99">
         <v>84</v>
@@ -10618,7 +10657,7 @@
         <v>17.76666667</v>
       </c>
       <c r="V99" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W99">
         <v>-0.005972</v>
@@ -10647,10 +10686,10 @@
     </row>
     <row r="100" spans="1:30">
       <c r="A100" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B100" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C100" s="2">
         <v>45416.31520199074</v>
@@ -10668,13 +10707,13 @@
         <v>2610</v>
       </c>
       <c r="H100" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I100" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="J100" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K100">
         <v>63</v>
@@ -10710,7 +10749,7 @@
         <v>18.73333333</v>
       </c>
       <c r="V100" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W100">
         <v>0.016111</v>
@@ -10739,10 +10778,10 @@
     </row>
     <row r="101" spans="1:30">
       <c r="A101" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B101" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C101" s="2">
         <v>45416.31557868056</v>
@@ -10760,13 +10799,13 @@
         <v>2640</v>
       </c>
       <c r="H101" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I101" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="J101" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="K101">
         <v>36</v>
@@ -10802,7 +10841,7 @@
         <v>23.43333333</v>
       </c>
       <c r="V101" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W101">
         <v>0.156667</v>
@@ -10831,10 +10870,10 @@
     </row>
     <row r="102" spans="1:30">
       <c r="A102" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B102" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C102" s="2">
         <v>45416.31589615741</v>
@@ -10852,13 +10891,13 @@
         <v>2670</v>
       </c>
       <c r="H102" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I102" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="J102" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="K102">
         <v>77</v>
@@ -10894,7 +10933,7 @@
         <v>23.53333333</v>
       </c>
       <c r="V102" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W102">
         <v>0.003333</v>
@@ -10923,10 +10962,10 @@
     </row>
     <row r="103" spans="1:30">
       <c r="A103" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B103" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C103" s="2">
         <v>45416.31649530093</v>
@@ -10944,13 +10983,13 @@
         <v>2719</v>
       </c>
       <c r="H103" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I103" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="J103" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K103">
         <v>24</v>
@@ -10986,7 +11025,7 @@
         <v>21.82222222</v>
       </c>
       <c r="V103" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W103">
         <v>-0.009506000000000001</v>
@@ -11015,10 +11054,10 @@
     </row>
     <row r="104" spans="1:30">
       <c r="A104" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B104" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C104" s="2">
         <v>45416.31719040509</v>
@@ -11036,13 +11075,13 @@
         <v>2779</v>
       </c>
       <c r="H104" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I104" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="J104" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="K104">
         <v>49</v>
@@ -11078,7 +11117,7 @@
         <v>20.13333333</v>
       </c>
       <c r="V104" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W104">
         <v>-0.028148</v>
@@ -11107,10 +11146,10 @@
     </row>
     <row r="105" spans="1:30">
       <c r="A105" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B105" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C105" s="2">
         <v>45416.31728564815</v>
@@ -11128,13 +11167,13 @@
         <v>2790</v>
       </c>
       <c r="H105" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I105" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="J105" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="K105">
         <v>25</v>
@@ -11170,7 +11209,7 @@
         <v>21.79166667</v>
       </c>
       <c r="V105" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W105">
         <v>0.013819</v>
@@ -11199,10 +11238,10 @@
     </row>
     <row r="106" spans="1:30">
       <c r="A106" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B106" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C106" s="2">
         <v>45416.31750855324</v>
@@ -11220,13 +11259,13 @@
         <v>2809</v>
       </c>
       <c r="H106" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I106" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="J106" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="K106">
         <v>54</v>
@@ -11262,7 +11301,7 @@
         <v>18.66666667</v>
       </c>
       <c r="V106" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W106">
         <v>-0.104167</v>
@@ -11291,10 +11330,10 @@
     </row>
     <row r="107" spans="1:30">
       <c r="A107" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B107" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C107" s="2">
         <v>45416.31797965278</v>
@@ -11312,13 +11351,13 @@
         <v>2850</v>
       </c>
       <c r="H107" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I107" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="J107" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="K107">
         <v>88</v>
@@ -11354,7 +11393,7 @@
         <v>18.33333333</v>
       </c>
       <c r="V107" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W107">
         <v>-0.005556</v>
@@ -11383,10 +11422,10 @@
     </row>
     <row r="108" spans="1:30">
       <c r="A108" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B108" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C108" s="2">
         <v>45416.31835606482</v>
@@ -11404,13 +11443,13 @@
         <v>2880</v>
       </c>
       <c r="H108" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I108" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="J108" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="K108">
         <v>112</v>
@@ -11446,7 +11485,7 @@
         <v>17.73333333</v>
       </c>
       <c r="V108" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W108">
         <v>-0.02</v>
@@ -11475,10 +11514,10 @@
     </row>
     <row r="109" spans="1:30">
       <c r="A109" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B109" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C109" s="2">
         <v>45416.31867484954</v>
@@ -11496,13 +11535,13 @@
         <v>2910</v>
       </c>
       <c r="H109" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I109" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="J109" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="K109">
         <v>193</v>
@@ -11538,7 +11577,7 @@
         <v>19.73333333</v>
       </c>
       <c r="V109" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W109">
         <v>0.066667</v>
@@ -11567,10 +11606,10 @@
     </row>
     <row r="110" spans="1:30">
       <c r="A110" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B110" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C110" s="2">
         <v>45416.31936898148</v>
@@ -11588,13 +11627,13 @@
         <v>2970</v>
       </c>
       <c r="H110" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I110" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="J110" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K110">
         <v>47</v>
@@ -11630,7 +11669,7 @@
         <v>22.73333333</v>
       </c>
       <c r="V110" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W110">
         <v>0.05</v>
@@ -11659,10 +11698,10 @@
     </row>
     <row r="111" spans="1:30">
       <c r="A111" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B111" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C111" s="2">
         <v>45416.31958745371</v>
@@ -11680,13 +11719,13 @@
         <v>2989</v>
       </c>
       <c r="H111" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I111" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="J111" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="K111">
         <v>41</v>
@@ -11722,7 +11761,7 @@
         <v>19.77777778</v>
       </c>
       <c r="V111" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W111">
         <v>-0.01642</v>
@@ -11751,10 +11790,10 @@
     </row>
     <row r="112" spans="1:30">
       <c r="A112" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B112" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C112" s="2">
         <v>45416.32065864583</v>
@@ -11772,13 +11811,13 @@
         <v>3079</v>
       </c>
       <c r="H112" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I112" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="J112" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="K112">
         <v>122</v>
@@ -11814,7 +11853,7 @@
         <v>19.48888889</v>
       </c>
       <c r="V112" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W112">
         <v>-0.00321</v>
@@ -11843,10 +11882,10 @@
     </row>
     <row r="113" spans="1:30">
       <c r="A113" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B113" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C113" s="2">
         <v>45416.3207590625</v>
@@ -11864,13 +11903,13 @@
         <v>3090</v>
       </c>
       <c r="H113" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I113" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="J113" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="K113">
         <v>300</v>
@@ -11906,7 +11945,7 @@
         <v>19.38333333</v>
       </c>
       <c r="V113" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W113">
         <v>-0.00088</v>
@@ -11935,10 +11974,10 @@
     </row>
     <row r="114" spans="1:30">
       <c r="A114" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B114" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C114" s="2">
         <v>45416.32097695602</v>
@@ -11956,13 +11995,13 @@
         <v>3109</v>
       </c>
       <c r="H114" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I114" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J114" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="K114">
         <v>164</v>
@@ -11998,7 +12037,7 @@
         <v>20.96666667</v>
       </c>
       <c r="V114" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="W114">
         <v>0.052778</v>
@@ -12027,10 +12066,10 @@
     </row>
     <row r="115" spans="1:30">
       <c r="A115" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B115" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C115" s="2">
         <v>45416.3214525463</v>
@@ -12048,13 +12087,13 @@
         <v>3150</v>
       </c>
       <c r="H115" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I115" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="J115" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="K115">
         <v>112</v>
@@ -12090,7 +12129,7 @@
         <v>21.6</v>
       </c>
       <c r="V115" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W115">
         <v>0.010556</v>
@@ -12119,10 +12158,10 @@
     </row>
     <row r="116" spans="1:30">
       <c r="A116" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B116" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C116" s="2">
         <v>45416.32182875</v>
@@ -12140,13 +12179,13 @@
         <v>3180</v>
       </c>
       <c r="H116" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I116" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="J116" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="K116">
         <v>191</v>
@@ -12182,7 +12221,7 @@
         <v>17.83333333</v>
       </c>
       <c r="V116" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W116">
         <v>-0.125556</v>
@@ -12211,10 +12250,10 @@
     </row>
     <row r="117" spans="1:30">
       <c r="A117" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B117" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C117" s="2">
         <v>45416.32204784722</v>
@@ -12232,13 +12271,13 @@
         <v>3199</v>
       </c>
       <c r="H117" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I117" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="J117" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K117">
         <v>28</v>
@@ -12274,7 +12313,7 @@
         <v>19.77777778</v>
       </c>
       <c r="V117" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W117">
         <v>0.021605</v>
@@ -12303,10 +12342,10 @@
     </row>
     <row r="118" spans="1:30">
       <c r="A118" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B118" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C118" s="2">
         <v>45416.32214707176</v>
@@ -12324,13 +12363,13 @@
         <v>3210</v>
       </c>
       <c r="H118" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I118" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="J118" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="K118">
         <v>321</v>
@@ -12366,7 +12405,7 @@
         <v>18.33333333</v>
       </c>
       <c r="V118" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W118">
         <v>-0.048148</v>
@@ -12395,10 +12434,10 @@
     </row>
     <row r="119" spans="1:30">
       <c r="A119" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B119" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C119" s="2">
         <v>45416.32284148148</v>
@@ -12416,13 +12455,13 @@
         <v>3270</v>
       </c>
       <c r="H119" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I119" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J119" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K119">
         <v>24</v>
@@ -12458,7 +12497,7 @@
         <v>16.53333333</v>
       </c>
       <c r="V119" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W119">
         <v>-0.03</v>
@@ -12487,10 +12526,10 @@
     </row>
     <row r="120" spans="1:30">
       <c r="A120" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B120" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C120" s="2">
         <v>45416.32353576389</v>
@@ -12508,13 +12547,13 @@
         <v>3330</v>
       </c>
       <c r="H120" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I120" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="J120" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="K120">
         <v>88</v>
@@ -12550,7 +12589,7 @@
         <v>17.9</v>
       </c>
       <c r="V120" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W120">
         <v>0.022778</v>
@@ -12579,10 +12618,10 @@
     </row>
     <row r="121" spans="1:30">
       <c r="A121" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B121" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C121" s="2">
         <v>45416.32423038194</v>
@@ -12600,13 +12639,13 @@
         <v>3390</v>
       </c>
       <c r="H121" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I121" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="J121" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="K121">
         <v>221</v>
@@ -12642,7 +12681,7 @@
         <v>18.96666667</v>
       </c>
       <c r="V121" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W121">
         <v>0.017778</v>
@@ -12671,10 +12710,10 @@
     </row>
     <row r="122" spans="1:30">
       <c r="A122" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B122" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C122" s="2">
         <v>45416.32492571759</v>
@@ -12692,13 +12731,13 @@
         <v>3450</v>
       </c>
       <c r="H122" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I122" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="J122" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K122">
         <v>289</v>
@@ -12734,7 +12773,7 @@
         <v>18.63333333</v>
       </c>
       <c r="V122" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W122">
         <v>-0.005556</v>
@@ -12763,10 +12802,10 @@
     </row>
     <row r="123" spans="1:30">
       <c r="A123" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B123" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C123" s="2">
         <v>45416.32561967592</v>
@@ -12784,13 +12823,13 @@
         <v>3510</v>
       </c>
       <c r="H123" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I123" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="J123" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K123">
         <v>341</v>
@@ -12826,7 +12865,7 @@
         <v>18.58333333</v>
       </c>
       <c r="V123" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W123">
         <v>-0.000833</v>
@@ -12855,10 +12894,10 @@
     </row>
     <row r="124" spans="1:30">
       <c r="A124" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B124" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C124" s="2">
         <v>45416.32631473379</v>
@@ -12876,13 +12915,13 @@
         <v>3570</v>
       </c>
       <c r="H124" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I124" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="J124" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="K124">
         <v>203</v>
@@ -12918,7 +12957,7 @@
         <v>17.96666667</v>
       </c>
       <c r="V124" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W124">
         <v>-0.010278</v>
@@ -12947,10 +12986,10 @@
     </row>
     <row r="125" spans="1:30">
       <c r="A125" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B125" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C125" s="2">
         <v>45416.32669028935</v>
@@ -12968,13 +13007,13 @@
         <v>3600</v>
       </c>
       <c r="H125" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I125" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="J125" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="K125">
         <v>293</v>
@@ -13010,7 +13049,7 @@
         <v>18.33333333</v>
       </c>
       <c r="V125" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W125">
         <v>0.012222</v>
@@ -13039,10 +13078,10 @@
     </row>
     <row r="126" spans="1:30">
       <c r="A126" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B126" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C126" s="2">
         <v>45416.32700880787</v>
@@ -13060,13 +13099,13 @@
         <v>3630</v>
       </c>
       <c r="H126" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I126" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="J126" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="K126">
         <v>216</v>
@@ -13102,7 +13141,7 @@
         <v>18.93333333</v>
       </c>
       <c r="V126" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W126">
         <v>0.02</v>
@@ -13131,10 +13170,10 @@
     </row>
     <row r="127" spans="1:30">
       <c r="A127" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B127" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C127" s="2">
         <v>45416.32770253472</v>
@@ -13152,13 +13191,13 @@
         <v>3690</v>
       </c>
       <c r="H127" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I127" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="J127" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="K127">
         <v>47</v>
@@ -13194,7 +13233,7 @@
         <v>18.68333333</v>
       </c>
       <c r="V127" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W127">
         <v>-0.004167</v>
@@ -13223,10 +13262,10 @@
     </row>
     <row r="128" spans="1:30">
       <c r="A128" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B128" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C128" s="2">
         <v>45416.3279222338</v>
@@ -13244,13 +13283,13 @@
         <v>3709</v>
       </c>
       <c r="H128" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I128" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="J128" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K128">
         <v>353</v>
@@ -13286,7 +13325,7 @@
         <v>18.29215686</v>
       </c>
       <c r="V128" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W128">
         <v>-0.000767</v>
@@ -13315,10 +13354,10 @@
     </row>
     <row r="129" spans="1:30">
       <c r="A129" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B129" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C129" s="2">
         <v>45416.32807935185</v>
@@ -13336,13 +13375,13 @@
         <v>3720</v>
       </c>
       <c r="H129" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I129" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="J129" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="K129">
         <v>5</v>
@@ -13378,7 +13417,7 @@
         <v>18.96666667</v>
       </c>
       <c r="V129" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W129">
         <v>0.022484</v>
@@ -13407,10 +13446,10 @@
     </row>
     <row r="130" spans="1:30">
       <c r="A130" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B130" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C130" s="2">
         <v>45416.32909188658</v>
@@ -13428,13 +13467,13 @@
         <v>3810</v>
       </c>
       <c r="H130" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I130" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="J130" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="K130">
         <v>303</v>
@@ -13470,7 +13509,7 @@
         <v>19.14444444</v>
       </c>
       <c r="V130" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W130">
         <v>0.001975</v>
@@ -13499,10 +13538,10 @@
     </row>
     <row r="131" spans="1:30">
       <c r="A131" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B131" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C131" s="2">
         <v>45416.32978655092</v>
@@ -13520,13 +13559,13 @@
         <v>3870</v>
       </c>
       <c r="H131" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I131" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="J131" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="K131">
         <v>3</v>
@@ -13562,7 +13601,7 @@
         <v>18.55</v>
       </c>
       <c r="V131" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W131">
         <v>-0.009906999999999999</v>
@@ -13591,10 +13630,10 @@
     </row>
     <row r="132" spans="1:30">
       <c r="A132" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B132" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C132" s="2">
         <v>45416.33048126158</v>
@@ -13612,13 +13651,13 @@
         <v>3930</v>
       </c>
       <c r="H132" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I132" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="J132" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="K132">
         <v>102</v>
@@ -13654,7 +13693,7 @@
         <v>17.71666667</v>
       </c>
       <c r="V132" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W132">
         <v>-0.013889</v>
@@ -13683,10 +13722,10 @@
     </row>
     <row r="133" spans="1:30">
       <c r="A133" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B133" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C133" s="2">
         <v>45416.33117584491</v>
@@ -13704,13 +13743,13 @@
         <v>3990</v>
       </c>
       <c r="H133" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I133" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="J133" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="K133">
         <v>159</v>
@@ -13746,7 +13785,7 @@
         <v>18.46666667</v>
       </c>
       <c r="V133" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W133">
         <v>0.0125</v>
@@ -13775,10 +13814,10 @@
     </row>
     <row r="134" spans="1:30">
       <c r="A134" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B134" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C134" s="2">
         <v>45416.33187099537</v>
@@ -13796,13 +13835,13 @@
         <v>4050</v>
       </c>
       <c r="H134" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I134" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J134" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K134">
         <v>48</v>
@@ -13838,7 +13877,7 @@
         <v>18.93333333</v>
       </c>
       <c r="V134" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W134">
         <v>0.007778</v>
@@ -13867,10 +13906,10 @@
     </row>
     <row r="135" spans="1:30">
       <c r="A135" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B135" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C135" s="2">
         <v>45416.33256486111</v>
@@ -13888,13 +13927,13 @@
         <v>4110</v>
       </c>
       <c r="H135" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I135" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="J135" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="K135">
         <v>104</v>
@@ -13930,7 +13969,7 @@
         <v>18.03333333</v>
       </c>
       <c r="V135" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W135">
         <v>-0.015</v>
@@ -13959,10 +13998,10 @@
     </row>
     <row r="136" spans="1:30">
       <c r="A136" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B136" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C136" s="2">
         <v>45416.33325940972</v>
@@ -13980,13 +14019,13 @@
         <v>4170</v>
       </c>
       <c r="H136" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I136" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="J136" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="K136">
         <v>236</v>
@@ -14022,7 +14061,7 @@
         <v>17.56666667</v>
       </c>
       <c r="V136" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W136">
         <v>-0.007778</v>
@@ -14051,10 +14090,10 @@
     </row>
     <row r="137" spans="1:30">
       <c r="A137" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B137" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C137" s="2">
         <v>45416.33395407407</v>
@@ -14072,13 +14111,13 @@
         <v>4230</v>
       </c>
       <c r="H137" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I137" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="J137" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="K137">
         <v>173</v>
@@ -14114,7 +14153,7 @@
         <v>18.33333333</v>
       </c>
       <c r="V137" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W137">
         <v>0.012778</v>
@@ -14143,10 +14182,10 @@
     </row>
     <row r="138" spans="1:30">
       <c r="A138" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B138" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C138" s="2">
         <v>45416.33464820602</v>
@@ -14164,13 +14203,13 @@
         <v>4290</v>
       </c>
       <c r="H138" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I138" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="J138" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="K138">
         <v>135</v>
@@ -14206,7 +14245,7 @@
         <v>19.58333333</v>
       </c>
       <c r="V138" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W138">
         <v>0.020833</v>
@@ -14235,10 +14274,10 @@
     </row>
     <row r="139" spans="1:30">
       <c r="A139" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B139" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C139" s="2">
         <v>45416.33534385417</v>
@@ -14256,13 +14295,13 @@
         <v>4350</v>
       </c>
       <c r="H139" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I139" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J139" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="K139">
         <v>55</v>
@@ -14298,7 +14337,7 @@
         <v>20.3</v>
       </c>
       <c r="V139" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W139">
         <v>0.011944</v>
@@ -14327,10 +14366,10 @@
     </row>
     <row r="140" spans="1:30">
       <c r="A140" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B140" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C140" s="2">
         <v>45416.33603737268</v>
@@ -14348,13 +14387,13 @@
         <v>4410</v>
       </c>
       <c r="H140" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="I140" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="J140" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="K140">
         <v>36</v>
@@ -14390,7 +14429,7 @@
         <v>19.03333333</v>
       </c>
       <c r="V140" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="W140">
         <v>-0.021111</v>
@@ -14429,102 +14468,102 @@
   <sheetData>
     <row r="1" spans="1:30">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:30">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C2" s="2">
         <v>45416.3367315625</v>
@@ -14542,13 +14581,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="K2">
         <v>189</v>
@@ -14584,7 +14623,7 @@
         <v>-63.55</v>
       </c>
       <c r="V2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="X2">
         <v>-63.55</v>
@@ -14595,10 +14634,10 @@
     </row>
     <row r="3" spans="1:30">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C3" s="2">
         <v>45416.33834126157</v>
@@ -14616,13 +14655,13 @@
         <v>139</v>
       </c>
       <c r="H3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I3" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="J3" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="K3">
         <v>278</v>
@@ -14658,7 +14697,7 @@
         <v>-2.51666667</v>
       </c>
       <c r="V3" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="W3">
         <v>0.067815</v>
@@ -14681,10 +14720,10 @@
     </row>
     <row r="4" spans="1:30">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C4" s="2">
         <v>45416.33849724537</v>
@@ -14702,13 +14741,13 @@
         <v>150</v>
       </c>
       <c r="H4" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I4" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="J4" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="K4">
         <v>94</v>
@@ -14744,7 +14783,7 @@
         <v>-82.30666667</v>
       </c>
       <c r="V4" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="W4">
         <v>-0.531933</v>
@@ -14773,10 +14812,10 @@
     </row>
     <row r="5" spans="1:30">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C5" s="2">
         <v>45416.33882717592</v>
@@ -14794,13 +14833,13 @@
         <v>180</v>
       </c>
       <c r="H5" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I5" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J5" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="K5">
         <v>314</v>
@@ -14836,7 +14875,7 @@
         <v>-69.46666667</v>
       </c>
       <c r="V5" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="W5">
         <v>0.428</v>
@@ -14865,10 +14904,10 @@
     </row>
     <row r="6" spans="1:30">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C6" s="2">
         <v>45416.33919136574</v>
@@ -14886,13 +14925,13 @@
         <v>210</v>
       </c>
       <c r="H6" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I6" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="J6" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="K6">
         <v>229</v>
@@ -14928,7 +14967,7 @@
         <v>-63.4</v>
       </c>
       <c r="V6" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="W6">
         <v>0.202222</v>
@@ -14957,10 +14996,10 @@
     </row>
     <row r="7" spans="1:30">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2">
         <v>45416.33950978009</v>
@@ -14978,13 +15017,13 @@
         <v>240</v>
       </c>
       <c r="H7" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I7" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="J7" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="K7">
         <v>58</v>
@@ -15020,7 +15059,7 @@
         <v>-55.8</v>
       </c>
       <c r="V7" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="W7">
         <v>0.253333</v>
@@ -15049,10 +15088,10 @@
     </row>
     <row r="8" spans="1:30">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2">
         <v>45416.33988663195</v>
@@ -15070,13 +15109,13 @@
         <v>270</v>
       </c>
       <c r="H8" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I8" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="J8" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="K8">
         <v>63</v>
@@ -15112,7 +15151,7 @@
         <v>-50.33333333</v>
       </c>
       <c r="V8" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="W8">
         <v>0.182222</v>
@@ -15141,10 +15180,10 @@
     </row>
     <row r="9" spans="1:30">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C9" s="2">
         <v>45416.34020414352</v>
@@ -15162,13 +15201,13 @@
         <v>300</v>
       </c>
       <c r="H9" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I9" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="J9" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="K9">
         <v>26</v>
@@ -15204,7 +15243,7 @@
         <v>-53.3</v>
       </c>
       <c r="V9" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="W9">
         <v>-0.098889</v>
@@ -15233,10 +15272,10 @@
     </row>
     <row r="10" spans="1:30">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C10" s="2">
         <v>45416.34111480324</v>
@@ -15254,13 +15293,13 @@
         <v>379</v>
       </c>
       <c r="H10" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I10" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="J10" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="K10">
         <v>74</v>
@@ -15296,7 +15335,7 @@
         <v>-55.93333333</v>
       </c>
       <c r="V10" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="W10">
         <v>-0.010972</v>
@@ -15325,10 +15364,10 @@
     </row>
     <row r="11" spans="1:30">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C11" s="2">
         <v>45416.34197019676</v>
@@ -15346,13 +15385,13 @@
         <v>450</v>
       </c>
       <c r="H11" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I11" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J11" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="K11">
         <v>11</v>
@@ -15388,7 +15427,7 @@
         <v>-46.19333333</v>
       </c>
       <c r="V11" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="W11">
         <v>0.064933</v>
@@ -15417,10 +15456,10 @@
     </row>
     <row r="12" spans="1:30">
       <c r="A12" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C12" s="2">
         <v>45416.34597724537</v>
@@ -15438,13 +15477,13 @@
         <v>799</v>
       </c>
       <c r="H12" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="I12" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="J12" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="K12">
         <v>59</v>
@@ -15480,7 +15519,7 @@
         <v>-35.93571429</v>
       </c>
       <c r="V12" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="W12">
         <v>0.024423</v>

--- a/www/flightdata/xlsx/eoss-358.xlsx
+++ b/www/flightdata/xlsx/eoss-358.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1001" uniqueCount="377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="379">
   <si>
     <t>flight</t>
   </si>
@@ -228,6 +228,9 @@
     <t>velocity_curvefit</t>
   </si>
   <si>
+    <t>reynolds_transition</t>
+  </si>
+  <si>
     <t>AE0SS-4</t>
   </si>
   <si>
@@ -1075,6 +1078,9 @@
   </si>
   <si>
     <t>low Re</t>
+  </si>
+  <si>
+    <t>high_to_low</t>
   </si>
   <si>
     <t>descending</t>
@@ -1672,10 +1678,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE140"/>
+  <dimension ref="A1:AF140"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -1769,13 +1775,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2">
         <v>45416.28501981482</v>
@@ -1793,13 +1802,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="J2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="K2">
         <v>20</v>
@@ -1838,7 +1847,7 @@
         <v>5.13333333</v>
       </c>
       <c r="W2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="Y2">
         <v>5.133333</v>
@@ -1847,12 +1856,12 @@
         <v>11.200583</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>45416.28524439815</v>
@@ -1870,13 +1879,13 @@
         <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="K3">
         <v>59</v>
@@ -1915,7 +1924,7 @@
         <v>18.13333333</v>
       </c>
       <c r="W3" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X3">
         <v>0.433333</v>
@@ -1936,12 +1945,12 @@
         <v>14.669533</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2">
         <v>45416.28533979167</v>
@@ -1959,13 +1968,13 @@
         <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="K4">
         <v>116</v>
@@ -2004,7 +2013,7 @@
         <v>19.6</v>
       </c>
       <c r="W4" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X4">
         <v>0.048889</v>
@@ -2031,12 +2040,12 @@
         <v>15.83798</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>45416.28556251158</v>
@@ -2054,13 +2063,13 @@
         <v>49</v>
       </c>
       <c r="H5" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J5" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="K5">
         <v>298</v>
@@ -2099,7 +2108,7 @@
         <v>21.63333333</v>
       </c>
       <c r="W5" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X5">
         <v>0.067778</v>
@@ -2126,12 +2135,12 @@
         <v>18.3466</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
         <v>45416.28571474537</v>
@@ -2149,13 +2158,13 @@
         <v>60</v>
       </c>
       <c r="H6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="K6">
         <v>314</v>
@@ -2194,7 +2203,7 @@
         <v>21</v>
       </c>
       <c r="W6" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X6">
         <v>-0.021111</v>
@@ -2221,12 +2230,12 @@
         <v>18.965331</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="2">
         <v>45416.28593912037</v>
@@ -2244,13 +2253,13 @@
         <v>79</v>
       </c>
       <c r="H7" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I7" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J7" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="K7">
         <v>275</v>
@@ -2289,7 +2298,7 @@
         <v>18.63333333</v>
       </c>
       <c r="W7" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X7">
         <v>-0.078889</v>
@@ -2316,12 +2325,12 @@
         <v>20.219916</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2">
         <v>45416.28603229167</v>
@@ -2339,13 +2348,13 @@
         <v>90</v>
       </c>
       <c r="H8" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J8" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="K8">
         <v>271</v>
@@ -2384,7 +2393,7 @@
         <v>19.16666667</v>
       </c>
       <c r="W8" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X8">
         <v>0.017778</v>
@@ -2411,12 +2420,12 @@
         <v>20.60655</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2">
         <v>45416.28625826389</v>
@@ -2434,13 +2443,13 @@
         <v>109</v>
       </c>
       <c r="H9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J9" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K9">
         <v>271</v>
@@ -2479,7 +2488,7 @@
         <v>19.56666667</v>
       </c>
       <c r="W9" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X9">
         <v>0.013333</v>
@@ -2506,12 +2515,12 @@
         <v>21.267748</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="2">
         <v>45416.28640918982</v>
@@ -2529,13 +2538,13 @@
         <v>120</v>
       </c>
       <c r="H10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="J10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="K10">
         <v>244</v>
@@ -2574,7 +2583,7 @@
         <v>19.86666667</v>
       </c>
       <c r="W10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X10">
         <v>0.01</v>
@@ -2601,12 +2610,12 @@
         <v>21.445225</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" s="2">
         <v>45416.28663488426</v>
@@ -2624,13 +2633,13 @@
         <v>139</v>
       </c>
       <c r="H11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J11" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="K11">
         <v>246</v>
@@ -2669,7 +2678,7 @@
         <v>21</v>
       </c>
       <c r="W11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X11">
         <v>0.037778</v>
@@ -2696,12 +2705,12 @@
         <v>21.669151</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C12" s="2">
         <v>45416.28672798611</v>
@@ -2719,13 +2728,13 @@
         <v>150</v>
       </c>
       <c r="H12" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J12" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="K12">
         <v>210</v>
@@ -2764,7 +2773,7 @@
         <v>21.4</v>
       </c>
       <c r="W12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X12">
         <v>0.013333</v>
@@ -2791,12 +2800,12 @@
         <v>21.685264</v>
       </c>
     </row>
-    <row r="13" spans="1:31">
+    <row r="13" spans="1:32">
       <c r="A13" t="s">
         <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" s="2">
         <v>45416.28695288194</v>
@@ -2814,13 +2823,13 @@
         <v>169</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="K13">
         <v>183</v>
@@ -2859,7 +2868,7 @@
         <v>21.43333333</v>
       </c>
       <c r="W13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X13">
         <v>0.001111</v>
@@ -2886,12 +2895,12 @@
         <v>21.584677</v>
       </c>
     </row>
-    <row r="14" spans="1:31">
+    <row r="14" spans="1:32">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C14" s="2">
         <v>45416.28710354167</v>
@@ -2909,13 +2918,13 @@
         <v>180</v>
       </c>
       <c r="H14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I14" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K14">
         <v>234</v>
@@ -2954,7 +2963,7 @@
         <v>20.1</v>
       </c>
       <c r="W14" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X14">
         <v>-0.044444</v>
@@ -2981,12 +2990,12 @@
         <v>21.516924</v>
       </c>
     </row>
-    <row r="15" spans="1:31">
+    <row r="15" spans="1:32">
       <c r="A15" t="s">
         <v>25</v>
       </c>
       <c r="B15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C15" s="2">
         <v>45416.2874396412</v>
@@ -3004,13 +3013,13 @@
         <v>210</v>
       </c>
       <c r="H15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J15" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="K15">
         <v>149</v>
@@ -3049,7 +3058,7 @@
         <v>21.03333333</v>
       </c>
       <c r="W15" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X15">
         <v>0.031111</v>
@@ -3076,12 +3085,12 @@
         <v>21.113838</v>
       </c>
     </row>
-    <row r="16" spans="1:31">
+    <row r="16" spans="1:32">
       <c r="A16" t="s">
         <v>25</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C16" s="2">
         <v>45416.28764791667</v>
@@ -3099,13 +3108,13 @@
         <v>229</v>
       </c>
       <c r="H16" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J16" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="K16">
         <v>66</v>
@@ -3144,7 +3153,7 @@
         <v>20.88333333</v>
       </c>
       <c r="W16" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X16">
         <v>-0.0025</v>
@@ -3176,7 +3185,7 @@
         <v>25</v>
       </c>
       <c r="B17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C17" s="2">
         <v>45416.28779834491</v>
@@ -3194,13 +3203,13 @@
         <v>240</v>
       </c>
       <c r="H17" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I17" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="J17" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K17">
         <v>109</v>
@@ -3239,7 +3248,7 @@
         <v>20.5</v>
       </c>
       <c r="W17" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X17">
         <v>-0.012778</v>
@@ -3271,7 +3280,7 @@
         <v>25</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C18" s="2">
         <v>45416.28811732639</v>
@@ -3289,13 +3298,13 @@
         <v>270</v>
       </c>
       <c r="H18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I18" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J18" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="K18">
         <v>34</v>
@@ -3334,7 +3343,7 @@
         <v>21.5</v>
       </c>
       <c r="W18" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X18">
         <v>0.033333</v>
@@ -3366,7 +3375,7 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C19" s="2">
         <v>45416.28834163195</v>
@@ -3384,13 +3393,13 @@
         <v>289</v>
       </c>
       <c r="H19" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I19" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J19" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K19">
         <v>42</v>
@@ -3429,7 +3438,7 @@
         <v>20.15</v>
       </c>
       <c r="W19" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X19">
         <v>-0.0225</v>
@@ -3461,7 +3470,7 @@
         <v>25</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C20" s="2">
         <v>45416.28849383102</v>
@@ -3479,13 +3488,13 @@
         <v>300</v>
       </c>
       <c r="H20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J20" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="K20">
         <v>65</v>
@@ -3524,7 +3533,7 @@
         <v>20.63333333</v>
       </c>
       <c r="W20" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X20">
         <v>0.016111</v>
@@ -3556,7 +3565,7 @@
         <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C21" s="2">
         <v>45416.28881193287</v>
@@ -3574,13 +3583,13 @@
         <v>330</v>
       </c>
       <c r="H21" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J21" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="K21">
         <v>56</v>
@@ -3619,7 +3628,7 @@
         <v>17.86666667</v>
       </c>
       <c r="W21" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X21">
         <v>-0.092222</v>
@@ -3651,7 +3660,7 @@
         <v>25</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C22" s="2">
         <v>45416.28903572917</v>
@@ -3669,13 +3678,13 @@
         <v>349</v>
       </c>
       <c r="H22" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="K22">
         <v>72</v>
@@ -3714,7 +3723,7 @@
         <v>19.18333333</v>
       </c>
       <c r="W22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X22">
         <v>0.021944</v>
@@ -3746,7 +3755,7 @@
         <v>25</v>
       </c>
       <c r="B23" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C23" s="2">
         <v>45416.28918784722</v>
@@ -3764,13 +3773,13 @@
         <v>360</v>
       </c>
       <c r="H23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J23" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K23">
         <v>95</v>
@@ -3809,7 +3818,7 @@
         <v>19.03333333</v>
       </c>
       <c r="W23" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X23">
         <v>-0.005</v>
@@ -3841,7 +3850,7 @@
         <v>25</v>
       </c>
       <c r="B24" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C24" s="2">
         <v>45416.28950773148</v>
@@ -3859,13 +3868,13 @@
         <v>390</v>
       </c>
       <c r="H24" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I24" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J24" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K24">
         <v>80</v>
@@ -3904,7 +3913,7 @@
         <v>18.83333333</v>
       </c>
       <c r="W24" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X24">
         <v>-0.006667</v>
@@ -3936,7 +3945,7 @@
         <v>25</v>
       </c>
       <c r="B25" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C25" s="2">
         <v>45416.28972934028</v>
@@ -3954,13 +3963,13 @@
         <v>409</v>
       </c>
       <c r="H25" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I25" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J25" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="K25">
         <v>89</v>
@@ -3999,7 +4008,7 @@
         <v>18.76666667</v>
       </c>
       <c r="W25" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X25">
         <v>-0.001111</v>
@@ -4031,7 +4040,7 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C26" s="2">
         <v>45416.28988243055</v>
@@ -4049,13 +4058,13 @@
         <v>420</v>
       </c>
       <c r="H26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J26" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K26">
         <v>81</v>
@@ -4094,7 +4103,7 @@
         <v>19.5</v>
       </c>
       <c r="W26" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X26">
         <v>0.024444</v>
@@ -4126,7 +4135,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C27" s="2">
         <v>45416.2902003125</v>
@@ -4144,13 +4153,13 @@
         <v>450</v>
       </c>
       <c r="H27" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J27" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K27">
         <v>84</v>
@@ -4189,7 +4198,7 @@
         <v>19.66666667</v>
       </c>
       <c r="W27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X27">
         <v>0.005556</v>
@@ -4221,7 +4230,7 @@
         <v>25</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="2">
         <v>45416.29042340278</v>
@@ -4239,13 +4248,13 @@
         <v>469</v>
       </c>
       <c r="H28" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I28" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J28" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K28">
         <v>82</v>
@@ -4284,7 +4293,7 @@
         <v>19.38333333</v>
       </c>
       <c r="W28" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X28">
         <v>-0.004722</v>
@@ -4316,7 +4325,7 @@
         <v>25</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" s="2">
         <v>45416.29057700231</v>
@@ -4334,13 +4343,13 @@
         <v>480</v>
       </c>
       <c r="H29" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J29" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K29">
         <v>99</v>
@@ -4379,7 +4388,7 @@
         <v>18.13333333</v>
       </c>
       <c r="W29" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X29">
         <v>-0.041667</v>
@@ -4411,7 +4420,7 @@
         <v>25</v>
       </c>
       <c r="B30" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C30" s="2">
         <v>45416.29089520833</v>
@@ -4429,13 +4438,13 @@
         <v>510</v>
       </c>
       <c r="H30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J30" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K30">
         <v>96</v>
@@ -4474,7 +4483,7 @@
         <v>18.4</v>
       </c>
       <c r="W30" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X30">
         <v>0.008888999999999999</v>
@@ -4506,7 +4515,7 @@
         <v>25</v>
       </c>
       <c r="B31" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C31" s="2">
         <v>45416.29111777778</v>
@@ -4524,13 +4533,13 @@
         <v>529</v>
       </c>
       <c r="H31" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I31" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="J31" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="K31">
         <v>106</v>
@@ -4569,7 +4578,7 @@
         <v>18.25</v>
       </c>
       <c r="W31" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X31">
         <v>-0.0025</v>
@@ -4601,7 +4610,7 @@
         <v>25</v>
       </c>
       <c r="B32" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C32" s="2">
         <v>45416.29127113426</v>
@@ -4619,13 +4628,13 @@
         <v>540</v>
       </c>
       <c r="H32" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J32" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K32">
         <v>97</v>
@@ -4664,7 +4673,7 @@
         <v>17.23333333</v>
       </c>
       <c r="W32" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X32">
         <v>-0.033889</v>
@@ -4696,7 +4705,7 @@
         <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2">
         <v>45416.29158898148</v>
@@ -4714,13 +4723,13 @@
         <v>570</v>
       </c>
       <c r="H33" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I33" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J33" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K33">
         <v>95</v>
@@ -4759,7 +4768,7 @@
         <v>21.13333333</v>
       </c>
       <c r="W33" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X33">
         <v>0.13</v>
@@ -4791,7 +4800,7 @@
         <v>25</v>
       </c>
       <c r="B34" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2">
         <v>45416.29181238426</v>
@@ -4809,13 +4818,13 @@
         <v>589</v>
       </c>
       <c r="H34" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I34" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J34" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K34">
         <v>88</v>
@@ -4854,7 +4863,7 @@
         <v>19.26666667</v>
       </c>
       <c r="W34" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X34">
         <v>-0.031111</v>
@@ -4886,7 +4895,7 @@
         <v>25</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C35" s="2">
         <v>45416.29196631945</v>
@@ -4904,13 +4913,13 @@
         <v>600</v>
       </c>
       <c r="H35" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J35" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K35">
         <v>105</v>
@@ -4949,7 +4958,7 @@
         <v>17.83333333</v>
       </c>
       <c r="W35" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X35">
         <v>-0.047778</v>
@@ -4981,7 +4990,7 @@
         <v>25</v>
       </c>
       <c r="B36" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C36" s="2">
         <v>45416.2922846875</v>
@@ -4999,13 +5008,13 @@
         <v>630</v>
       </c>
       <c r="H36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I36" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J36" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K36">
         <v>111</v>
@@ -5044,7 +5053,7 @@
         <v>17.9</v>
       </c>
       <c r="W36" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X36">
         <v>0.002222</v>
@@ -5076,7 +5085,7 @@
         <v>25</v>
       </c>
       <c r="B37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2">
         <v>45416.29266038194</v>
@@ -5094,13 +5103,13 @@
         <v>660</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I37" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J37" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K37">
         <v>90</v>
@@ -5139,7 +5148,7 @@
         <v>20.13333333</v>
       </c>
       <c r="W37" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X37">
         <v>0.074444</v>
@@ -5171,7 +5180,7 @@
         <v>25</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C38" s="2">
         <v>45416.292978125</v>
@@ -5189,13 +5198,13 @@
         <v>690</v>
       </c>
       <c r="H38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I38" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J38" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="K38">
         <v>69</v>
@@ -5234,7 +5243,7 @@
         <v>18.76666667</v>
       </c>
       <c r="W38" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X38">
         <v>-0.045556</v>
@@ -5266,7 +5275,7 @@
         <v>25</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C39" s="2">
         <v>45416.29335501158</v>
@@ -5284,13 +5293,13 @@
         <v>720</v>
       </c>
       <c r="H39" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J39" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K39">
         <v>63</v>
@@ -5329,7 +5338,7 @@
         <v>18.03333333</v>
       </c>
       <c r="W39" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X39">
         <v>-0.024444</v>
@@ -5361,7 +5370,7 @@
         <v>25</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C40" s="2">
         <v>45416.29367321759</v>
@@ -5379,13 +5388,13 @@
         <v>750</v>
       </c>
       <c r="H40" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J40" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K40">
         <v>87</v>
@@ -5424,7 +5433,7 @@
         <v>17.2</v>
       </c>
       <c r="W40" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X40">
         <v>-0.027778</v>
@@ -5456,7 +5465,7 @@
         <v>25</v>
       </c>
       <c r="B41" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C41" s="2">
         <v>45416.29405516203</v>
@@ -5474,13 +5483,13 @@
         <v>780</v>
       </c>
       <c r="H41" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I41" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J41" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K41">
         <v>96</v>
@@ -5519,7 +5528,7 @@
         <v>18.43333333</v>
       </c>
       <c r="W41" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X41">
         <v>0.041111</v>
@@ -5551,7 +5560,7 @@
         <v>25</v>
       </c>
       <c r="B42" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C42" s="2">
         <v>45416.29436784722</v>
@@ -5569,13 +5578,13 @@
         <v>810</v>
       </c>
       <c r="H42" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I42" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J42" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K42">
         <v>75</v>
@@ -5614,7 +5623,7 @@
         <v>19.23333333</v>
       </c>
       <c r="W42" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X42">
         <v>0.026667</v>
@@ -5646,7 +5655,7 @@
         <v>25</v>
       </c>
       <c r="B43" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C43" s="2">
         <v>45416.29474569445</v>
@@ -5664,13 +5673,13 @@
         <v>840</v>
       </c>
       <c r="H43" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I43" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J43" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K43">
         <v>94</v>
@@ -5709,7 +5718,7 @@
         <v>16.4</v>
       </c>
       <c r="W43" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X43">
         <v>-0.094444</v>
@@ -5741,7 +5750,7 @@
         <v>25</v>
       </c>
       <c r="B44" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C44" s="2">
         <v>45416.29506273148</v>
@@ -5759,13 +5768,13 @@
         <v>870</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I44" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J44" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="K44">
         <v>90</v>
@@ -5804,7 +5813,7 @@
         <v>18.03333333</v>
       </c>
       <c r="W44" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X44">
         <v>0.054444</v>
@@ -5836,7 +5845,7 @@
         <v>25</v>
       </c>
       <c r="B45" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C45" s="2">
         <v>45416.29543877315</v>
@@ -5854,13 +5863,13 @@
         <v>900</v>
       </c>
       <c r="H45" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I45" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J45" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="K45">
         <v>98</v>
@@ -5899,7 +5908,7 @@
         <v>16.83333333</v>
       </c>
       <c r="W45" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X45">
         <v>-0.04</v>
@@ -5931,7 +5940,7 @@
         <v>25</v>
       </c>
       <c r="B46" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C46" s="2">
         <v>45416.29575668981</v>
@@ -5949,13 +5958,13 @@
         <v>930</v>
       </c>
       <c r="H46" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I46" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J46" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="K46">
         <v>86</v>
@@ -5994,7 +6003,7 @@
         <v>20.6</v>
       </c>
       <c r="W46" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X46">
         <v>0.125556</v>
@@ -6026,7 +6035,7 @@
         <v>25</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C47" s="2">
         <v>45416.29613241898</v>
@@ -6044,13 +6053,13 @@
         <v>960</v>
       </c>
       <c r="H47" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I47" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J47" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K47">
         <v>93</v>
@@ -6089,7 +6098,7 @@
         <v>17.86666667</v>
       </c>
       <c r="W47" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X47">
         <v>-0.091111</v>
@@ -6121,7 +6130,7 @@
         <v>25</v>
       </c>
       <c r="B48" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C48" s="2">
         <v>45416.29645150463</v>
@@ -6139,13 +6148,13 @@
         <v>990</v>
       </c>
       <c r="H48" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I48" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J48" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="K48">
         <v>72</v>
@@ -6184,7 +6193,7 @@
         <v>17.36666667</v>
       </c>
       <c r="W48" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X48">
         <v>-0.016667</v>
@@ -6216,7 +6225,7 @@
         <v>25</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C49" s="2">
         <v>45416.29682668982</v>
@@ -6234,13 +6243,13 @@
         <v>1020</v>
       </c>
       <c r="H49" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I49" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J49" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K49">
         <v>68</v>
@@ -6279,7 +6288,7 @@
         <v>16.36666667</v>
       </c>
       <c r="W49" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X49">
         <v>-0.033333</v>
@@ -6311,7 +6320,7 @@
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C50" s="2">
         <v>45416.29714474537</v>
@@ -6329,13 +6338,13 @@
         <v>1050</v>
       </c>
       <c r="H50" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I50" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="J50" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K50">
         <v>84</v>
@@ -6374,7 +6383,7 @@
         <v>20.1</v>
       </c>
       <c r="W50" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X50">
         <v>0.124444</v>
@@ -6406,7 +6415,7 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C51" s="2">
         <v>45416.29737010417</v>
@@ -6424,13 +6433,13 @@
         <v>1069</v>
       </c>
       <c r="H51" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I51" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J51" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="K51">
         <v>83</v>
@@ -6469,7 +6478,7 @@
         <v>18.21875</v>
       </c>
       <c r="W51" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X51">
         <v>-0.003919</v>
@@ -6501,7 +6510,7 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C52" s="2">
         <v>45416.29752219907</v>
@@ -6519,13 +6528,13 @@
         <v>1080</v>
       </c>
       <c r="H52" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I52" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J52" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K52">
         <v>85</v>
@@ -6564,7 +6573,7 @@
         <v>18.66666667</v>
       </c>
       <c r="W52" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X52">
         <v>0.014931</v>
@@ -6596,7 +6605,7 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C53" s="2">
         <v>45416.29783983796</v>
@@ -6614,13 +6623,13 @@
         <v>1110</v>
       </c>
       <c r="H53" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I53" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J53" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K53">
         <v>84</v>
@@ -6659,7 +6668,7 @@
         <v>17.66666667</v>
       </c>
       <c r="W53" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X53">
         <v>-0.033333</v>
@@ -6691,7 +6700,7 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C54" s="2">
         <v>45416.29821638889</v>
@@ -6709,13 +6718,13 @@
         <v>1140</v>
       </c>
       <c r="H54" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I54" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J54" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="K54">
         <v>68</v>
@@ -6754,7 +6763,7 @@
         <v>17.46666667</v>
       </c>
       <c r="W54" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X54">
         <v>-0.006667</v>
@@ -6786,7 +6795,7 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C55" s="2">
         <v>45416.29853439815</v>
@@ -6804,13 +6813,13 @@
         <v>1170</v>
       </c>
       <c r="H55" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I55" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J55" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="K55">
         <v>78</v>
@@ -6849,7 +6858,7 @@
         <v>18.9</v>
       </c>
       <c r="W55" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X55">
         <v>0.047778</v>
@@ -6881,7 +6890,7 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C56" s="2">
         <v>45416.29890998843</v>
@@ -6899,13 +6908,13 @@
         <v>1200</v>
       </c>
       <c r="H56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I56" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J56" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K56">
         <v>96</v>
@@ -6944,7 +6953,7 @@
         <v>21.23333333</v>
       </c>
       <c r="W56" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X56">
         <v>0.077778</v>
@@ -6976,7 +6985,7 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2">
         <v>45416.2991312963</v>
@@ -6994,13 +7003,13 @@
         <v>1219</v>
       </c>
       <c r="H57" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I57" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J57" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="K57">
         <v>73</v>
@@ -7039,7 +7048,7 @@
         <v>18.89333333</v>
       </c>
       <c r="W57" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X57">
         <v>-0.0156</v>
@@ -7071,7 +7080,7 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C58" s="2">
         <v>45416.29922893518</v>
@@ -7089,13 +7098,13 @@
         <v>1230</v>
       </c>
       <c r="H58" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I58" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J58" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K58">
         <v>61</v>
@@ -7134,7 +7143,7 @@
         <v>21.63333333</v>
       </c>
       <c r="W58" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X58">
         <v>0.091333</v>
@@ -7166,7 +7175,7 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C59" s="2">
         <v>45416.2996050463</v>
@@ -7184,13 +7193,13 @@
         <v>1260</v>
       </c>
       <c r="H59" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I59" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J59" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="K59">
         <v>68</v>
@@ -7229,7 +7238,7 @@
         <v>22.03333333</v>
       </c>
       <c r="W59" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X59">
         <v>0.013333</v>
@@ -7261,7 +7270,7 @@
         <v>25</v>
       </c>
       <c r="B60" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C60" s="2">
         <v>45416.29982586805</v>
@@ -7279,13 +7288,13 @@
         <v>1279</v>
       </c>
       <c r="H60" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I60" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J60" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K60">
         <v>65</v>
@@ -7324,7 +7333,7 @@
         <v>21.28333333</v>
       </c>
       <c r="W60" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X60">
         <v>-0.0125</v>
@@ -7356,7 +7365,7 @@
         <v>25</v>
       </c>
       <c r="B61" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C61" s="2">
         <v>45416.29992278935</v>
@@ -7374,13 +7383,13 @@
         <v>1290</v>
       </c>
       <c r="H61" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I61" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J61" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K61">
         <v>90</v>
@@ -7419,7 +7428,7 @@
         <v>17.86666667</v>
       </c>
       <c r="W61" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X61">
         <v>-0.113889</v>
@@ -7451,7 +7460,7 @@
         <v>25</v>
       </c>
       <c r="B62" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C62" s="2">
         <v>45416.30029982639</v>
@@ -7469,13 +7478,13 @@
         <v>1320</v>
       </c>
       <c r="H62" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I62" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J62" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="K62">
         <v>83</v>
@@ -7514,7 +7523,7 @@
         <v>22.16666667</v>
       </c>
       <c r="W62" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X62">
         <v>0.143333</v>
@@ -7546,7 +7555,7 @@
         <v>25</v>
       </c>
       <c r="B63" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C63" s="2">
         <v>45416.30061722222</v>
@@ -7564,13 +7573,13 @@
         <v>1350</v>
       </c>
       <c r="H63" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I63" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J63" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K63">
         <v>80</v>
@@ -7609,7 +7618,7 @@
         <v>16.9</v>
       </c>
       <c r="W63" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X63">
         <v>-0.175556</v>
@@ -7641,7 +7650,7 @@
         <v>25</v>
       </c>
       <c r="B64" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="2">
         <v>45416.3009994213</v>
@@ -7659,13 +7668,13 @@
         <v>1380</v>
       </c>
       <c r="H64" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I64" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J64" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="K64">
         <v>78</v>
@@ -7704,7 +7713,7 @@
         <v>15.76666667</v>
       </c>
       <c r="W64" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X64">
         <v>-0.037778</v>
@@ -7736,7 +7745,7 @@
         <v>25</v>
       </c>
       <c r="B65" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C65" s="2">
         <v>45416.30131277778</v>
@@ -7754,13 +7763,13 @@
         <v>1410</v>
       </c>
       <c r="H65" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J65" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K65">
         <v>61</v>
@@ -7799,7 +7808,7 @@
         <v>16.36666667</v>
       </c>
       <c r="W65" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X65">
         <v>0.02</v>
@@ -7831,7 +7840,7 @@
         <v>25</v>
       </c>
       <c r="B66" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C66" s="2">
         <v>45416.3020066551</v>
@@ -7849,13 +7858,13 @@
         <v>1470</v>
       </c>
       <c r="H66" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I66" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J66" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="K66">
         <v>69</v>
@@ -7894,7 +7903,7 @@
         <v>16.83333333</v>
       </c>
       <c r="W66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X66">
         <v>0.007778</v>
@@ -7926,7 +7935,7 @@
         <v>25</v>
       </c>
       <c r="B67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C67" s="2">
         <v>45416.30270140046</v>
@@ -7944,13 +7953,13 @@
         <v>1530</v>
       </c>
       <c r="H67" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I67" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J67" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="K67">
         <v>60</v>
@@ -7989,7 +7998,7 @@
         <v>18.18333333</v>
       </c>
       <c r="W67" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X67">
         <v>0.0225</v>
@@ -8021,7 +8030,7 @@
         <v>25</v>
       </c>
       <c r="B68" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C68" s="2">
         <v>45416.30339539352</v>
@@ -8039,13 +8048,13 @@
         <v>1590</v>
       </c>
       <c r="H68" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I68" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J68" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K68">
         <v>82</v>
@@ -8084,7 +8093,7 @@
         <v>20.5</v>
       </c>
       <c r="W68" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X68">
         <v>0.038611</v>
@@ -8116,7 +8125,7 @@
         <v>25</v>
       </c>
       <c r="B69" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C69" s="2">
         <v>45416.3036171412</v>
@@ -8134,13 +8143,13 @@
         <v>1609</v>
       </c>
       <c r="H69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I69" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J69" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K69">
         <v>71</v>
@@ -8179,7 +8188,7 @@
         <v>18.53939394</v>
       </c>
       <c r="W69" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X69">
         <v>-0.005941</v>
@@ -8211,7 +8220,7 @@
         <v>25</v>
       </c>
       <c r="B70" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C70" s="2">
         <v>45416.30399307871</v>
@@ -8229,13 +8238,13 @@
         <v>1639</v>
       </c>
       <c r="H70" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I70" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J70" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K70">
         <v>76</v>
@@ -8274,7 +8283,7 @@
         <v>21.2</v>
       </c>
       <c r="W70" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X70">
         <v>0.088687</v>
@@ -8306,7 +8315,7 @@
         <v>25</v>
       </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C71" s="2">
         <v>45416.30408978009</v>
@@ -8324,13 +8333,13 @@
         <v>1650</v>
       </c>
       <c r="H71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I71" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J71" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K71">
         <v>91</v>
@@ -8369,7 +8378,7 @@
         <v>22.08333333</v>
       </c>
       <c r="W71" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X71">
         <v>0.014722</v>
@@ -8401,7 +8410,7 @@
         <v>25</v>
       </c>
       <c r="B72" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C72" s="2">
         <v>45416.30478475695</v>
@@ -8419,13 +8428,13 @@
         <v>1710</v>
       </c>
       <c r="H72" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I72" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J72" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K72">
         <v>70</v>
@@ -8464,7 +8473,7 @@
         <v>18.38333333</v>
       </c>
       <c r="W72" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X72">
         <v>-0.061667</v>
@@ -8496,7 +8505,7 @@
         <v>25</v>
       </c>
       <c r="B73" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C73" s="2">
         <v>45416.30538291667</v>
@@ -8514,13 +8523,13 @@
         <v>1759</v>
       </c>
       <c r="H73" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I73" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J73" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K73">
         <v>66</v>
@@ -8559,7 +8568,7 @@
         <v>18.26666667</v>
       </c>
       <c r="W73" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X73">
         <v>-0.000972</v>
@@ -8591,7 +8600,7 @@
         <v>25</v>
       </c>
       <c r="B74" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C74" s="2">
         <v>45416.30547902777</v>
@@ -8609,13 +8618,13 @@
         <v>1770</v>
       </c>
       <c r="H74" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I74" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J74" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="K74">
         <v>79</v>
@@ -8654,7 +8663,7 @@
         <v>18.06666667</v>
       </c>
       <c r="W74" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X74">
         <v>-0.003333</v>
@@ -8686,7 +8695,7 @@
         <v>25</v>
       </c>
       <c r="B75" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C75" s="2">
         <v>45416.30617460649</v>
@@ -8704,13 +8713,13 @@
         <v>1830</v>
       </c>
       <c r="H75" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I75" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J75" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K75">
         <v>79</v>
@@ -8749,7 +8758,7 @@
         <v>22.1</v>
       </c>
       <c r="W75" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X75">
         <v>0.067222</v>
@@ -8781,7 +8790,7 @@
         <v>25</v>
       </c>
       <c r="B76" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C76" s="2">
         <v>45416.30654905093</v>
@@ -8799,13 +8808,13 @@
         <v>1860</v>
       </c>
       <c r="H76" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I76" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J76" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K76">
         <v>88</v>
@@ -8844,7 +8853,7 @@
         <v>20</v>
       </c>
       <c r="W76" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X76">
         <v>-0.07000000000000001</v>
@@ -8876,7 +8885,7 @@
         <v>25</v>
       </c>
       <c r="B77" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C77" s="2">
         <v>45416.30677236111</v>
@@ -8894,13 +8903,13 @@
         <v>1879</v>
       </c>
       <c r="H77" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I77" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="J77" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K77">
         <v>65</v>
@@ -8939,7 +8948,7 @@
         <v>21.34166667</v>
       </c>
       <c r="W77" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X77">
         <v>0.011181</v>
@@ -8971,7 +8980,7 @@
         <v>25</v>
       </c>
       <c r="B78" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C78" s="2">
         <v>45416.30686834491</v>
@@ -8989,13 +8998,13 @@
         <v>1890</v>
       </c>
       <c r="H78" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I78" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J78" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="K78">
         <v>58</v>
@@ -9034,7 +9043,7 @@
         <v>20.73333333</v>
       </c>
       <c r="W78" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X78">
         <v>-0.020278</v>
@@ -9066,7 +9075,7 @@
         <v>25</v>
       </c>
       <c r="B79" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C79" s="2">
         <v>45416.30709079861</v>
@@ -9084,13 +9093,13 @@
         <v>1909</v>
       </c>
       <c r="H79" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I79" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J79" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="K79">
         <v>73</v>
@@ -9129,7 +9138,7 @@
         <v>21.23333333</v>
       </c>
       <c r="W79" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X79">
         <v>0.016667</v>
@@ -9161,7 +9170,7 @@
         <v>25</v>
       </c>
       <c r="B80" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C80" s="2">
         <v>45416.30724446759</v>
@@ -9179,13 +9188,13 @@
         <v>1920</v>
       </c>
       <c r="H80" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I80" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J80" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K80">
         <v>76</v>
@@ -9224,7 +9233,7 @@
         <v>22.23333333</v>
       </c>
       <c r="W80" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X80">
         <v>0.033333</v>
@@ -9256,7 +9265,7 @@
         <v>25</v>
       </c>
       <c r="B81" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C81" s="2">
         <v>45416.30746599537</v>
@@ -9274,13 +9283,13 @@
         <v>1939</v>
       </c>
       <c r="H81" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I81" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="J81" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="K81">
         <v>78</v>
@@ -9319,7 +9328,7 @@
         <v>20.23333333</v>
       </c>
       <c r="W81" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X81">
         <v>-0.066667</v>
@@ -9351,7 +9360,7 @@
         <v>25</v>
       </c>
       <c r="B82" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C82" s="2">
         <v>45416.3075621875</v>
@@ -9369,13 +9378,13 @@
         <v>1950</v>
       </c>
       <c r="H82" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I82" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J82" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K82">
         <v>69</v>
@@ -9414,7 +9423,7 @@
         <v>21.26666667</v>
       </c>
       <c r="W82" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X82">
         <v>0.034444</v>
@@ -9446,7 +9455,7 @@
         <v>25</v>
       </c>
       <c r="B83" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C83" s="2">
         <v>45416.30825726852</v>
@@ -9464,13 +9473,13 @@
         <v>2010</v>
       </c>
       <c r="H83" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I83" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="J83" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K83">
         <v>68</v>
@@ -9509,7 +9518,7 @@
         <v>20.58333333</v>
       </c>
       <c r="W83" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X83">
         <v>-0.011389</v>
@@ -9541,7 +9550,7 @@
         <v>25</v>
       </c>
       <c r="B84" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C84" s="2">
         <v>45416.30863371528</v>
@@ -9559,13 +9568,13 @@
         <v>2040</v>
       </c>
       <c r="H84" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I84" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J84" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="K84">
         <v>80</v>
@@ -9604,7 +9613,7 @@
         <v>18.5</v>
       </c>
       <c r="W84" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X84">
         <v>-0.06944400000000001</v>
@@ -9636,7 +9645,7 @@
         <v>25</v>
       </c>
       <c r="B85" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C85" s="2">
         <v>45416.30895127315</v>
@@ -9654,13 +9663,13 @@
         <v>2070</v>
       </c>
       <c r="H85" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I85" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J85" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K85">
         <v>73</v>
@@ -9699,7 +9708,7 @@
         <v>20.96666667</v>
       </c>
       <c r="W85" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X85">
         <v>0.082222</v>
@@ -9731,7 +9740,7 @@
         <v>25</v>
       </c>
       <c r="B86" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C86" s="2">
         <v>45416.30955096065</v>
@@ -9749,13 +9758,13 @@
         <v>2119</v>
       </c>
       <c r="H86" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I86" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J86" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K86">
         <v>75</v>
@@ -9794,7 +9803,7 @@
         <v>19.82222222</v>
       </c>
       <c r="W86" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X86">
         <v>-0.006358</v>
@@ -9826,7 +9835,7 @@
         <v>25</v>
       </c>
       <c r="B87" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C87" s="2">
         <v>45416.30964634259</v>
@@ -9844,13 +9853,13 @@
         <v>2130</v>
       </c>
       <c r="H87" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I87" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="J87" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="K87">
         <v>80</v>
@@ -9889,7 +9898,7 @@
         <v>17.85</v>
       </c>
       <c r="W87" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X87">
         <v>-0.03287</v>
@@ -9921,7 +9930,7 @@
         <v>25</v>
       </c>
       <c r="B88" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C88" s="2">
         <v>45416.31002208334</v>
@@ -9939,13 +9948,13 @@
         <v>2160</v>
       </c>
       <c r="H88" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I88" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="J88" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="K88">
         <v>50</v>
@@ -9984,7 +9993,7 @@
         <v>19.16666667</v>
       </c>
       <c r="W88" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X88">
         <v>0.043889</v>
@@ -10016,7 +10025,7 @@
         <v>25</v>
       </c>
       <c r="B89" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C89" s="2">
         <v>45416.31036405093</v>
@@ -10034,13 +10043,13 @@
         <v>2190</v>
       </c>
       <c r="H89" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I89" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J89" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K89">
         <v>77</v>
@@ -10079,7 +10088,7 @@
         <v>17.56666667</v>
       </c>
       <c r="W89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X89">
         <v>-0.053333</v>
@@ -10111,7 +10120,7 @@
         <v>25</v>
       </c>
       <c r="B90" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C90" s="2">
         <v>45416.31103505787</v>
@@ -10129,13 +10138,13 @@
         <v>2250</v>
       </c>
       <c r="H90" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I90" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J90" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K90">
         <v>75</v>
@@ -10174,7 +10183,7 @@
         <v>17.15</v>
       </c>
       <c r="W90" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X90">
         <v>-0.006944</v>
@@ -10206,7 +10215,7 @@
         <v>25</v>
       </c>
       <c r="B91" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C91" s="2">
         <v>45416.31125788194</v>
@@ -10224,13 +10233,13 @@
         <v>2269</v>
       </c>
       <c r="H91" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I91" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J91" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K91">
         <v>75</v>
@@ -10269,7 +10278,7 @@
         <v>17.54</v>
       </c>
       <c r="W91" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X91">
         <v>0.0026</v>
@@ -10301,7 +10310,7 @@
         <v>25</v>
       </c>
       <c r="B92" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C92" s="2">
         <v>45416.31163385417</v>
@@ -10319,13 +10328,13 @@
         <v>2299</v>
       </c>
       <c r="H92" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I92" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="J92" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="K92">
         <v>78</v>
@@ -10364,7 +10373,7 @@
         <v>15.6</v>
       </c>
       <c r="W92" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X92">
         <v>-0.064667</v>
@@ -10396,7 +10405,7 @@
         <v>25</v>
       </c>
       <c r="B93" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C93" s="2">
         <v>45416.31173046296</v>
@@ -10414,13 +10423,13 @@
         <v>2310</v>
       </c>
       <c r="H93" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I93" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J93" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K93">
         <v>102</v>
@@ -10459,7 +10468,7 @@
         <v>16.36666667</v>
       </c>
       <c r="W93" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X93">
         <v>0.012778</v>
@@ -10491,7 +10500,7 @@
         <v>25</v>
       </c>
       <c r="B94" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C94" s="2">
         <v>45416.31210621528</v>
@@ -10509,13 +10518,13 @@
         <v>2340</v>
       </c>
       <c r="H94" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I94" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J94" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="K94">
         <v>73</v>
@@ -10554,7 +10563,7 @@
         <v>18.03333333</v>
       </c>
       <c r="W94" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X94">
         <v>0.055556</v>
@@ -10586,7 +10595,7 @@
         <v>25</v>
       </c>
       <c r="B95" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C95" s="2">
         <v>45416.31242394676</v>
@@ -10604,13 +10613,13 @@
         <v>2370</v>
       </c>
       <c r="H95" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I95" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="J95" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K95">
         <v>63</v>
@@ -10649,7 +10658,7 @@
         <v>18.13333333</v>
       </c>
       <c r="W95" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X95">
         <v>0.003333</v>
@@ -10681,7 +10690,7 @@
         <v>25</v>
       </c>
       <c r="B96" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C96" s="2">
         <v>45416.31311875</v>
@@ -10699,13 +10708,13 @@
         <v>2430</v>
       </c>
       <c r="H96" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I96" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J96" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K96">
         <v>82</v>
@@ -10744,7 +10753,7 @@
         <v>18.86666667</v>
       </c>
       <c r="W96" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X96">
         <v>0.012222</v>
@@ -10776,7 +10785,7 @@
         <v>25</v>
       </c>
       <c r="B97" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C97" s="2">
         <v>45416.31349582176</v>
@@ -10794,13 +10803,13 @@
         <v>2460</v>
       </c>
       <c r="H97" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I97" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J97" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="K97">
         <v>56</v>
@@ -10839,7 +10848,7 @@
         <v>18.4</v>
       </c>
       <c r="W97" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X97">
         <v>-0.015556</v>
@@ -10871,7 +10880,7 @@
         <v>25</v>
       </c>
       <c r="B98" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C98" s="2">
         <v>45416.31441143518</v>
@@ -10889,13 +10898,13 @@
         <v>2539</v>
       </c>
       <c r="H98" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I98" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J98" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K98">
         <v>78</v>
@@ -10934,7 +10943,7 @@
         <v>18.30416667</v>
       </c>
       <c r="W98" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X98">
         <v>-0.000399</v>
@@ -10966,7 +10975,7 @@
         <v>25</v>
       </c>
       <c r="B99" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C99" s="2">
         <v>45416.31450773148</v>
@@ -10984,13 +10993,13 @@
         <v>2550</v>
       </c>
       <c r="H99" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I99" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J99" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K99">
         <v>84</v>
@@ -11029,7 +11038,7 @@
         <v>17.76666667</v>
       </c>
       <c r="W99" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X99">
         <v>-0.005972</v>
@@ -11061,7 +11070,7 @@
         <v>25</v>
       </c>
       <c r="B100" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C100" s="2">
         <v>45416.31520199074</v>
@@ -11079,13 +11088,13 @@
         <v>2610</v>
       </c>
       <c r="H100" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I100" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J100" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K100">
         <v>63</v>
@@ -11124,7 +11133,7 @@
         <v>18.73333333</v>
       </c>
       <c r="W100" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X100">
         <v>0.016111</v>
@@ -11156,7 +11165,7 @@
         <v>25</v>
       </c>
       <c r="B101" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C101" s="2">
         <v>45416.31557868056</v>
@@ -11174,13 +11183,13 @@
         <v>2640</v>
       </c>
       <c r="H101" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I101" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="J101" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="K101">
         <v>36</v>
@@ -11219,7 +11228,7 @@
         <v>23.43333333</v>
       </c>
       <c r="W101" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X101">
         <v>0.156667</v>
@@ -11251,7 +11260,7 @@
         <v>25</v>
       </c>
       <c r="B102" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C102" s="2">
         <v>45416.31589615741</v>
@@ -11269,13 +11278,13 @@
         <v>2670</v>
       </c>
       <c r="H102" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I102" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J102" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="K102">
         <v>77</v>
@@ -11314,7 +11323,7 @@
         <v>23.53333333</v>
       </c>
       <c r="W102" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X102">
         <v>0.003333</v>
@@ -11346,7 +11355,7 @@
         <v>25</v>
       </c>
       <c r="B103" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C103" s="2">
         <v>45416.31649530093</v>
@@ -11364,13 +11373,13 @@
         <v>2719</v>
       </c>
       <c r="H103" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I103" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="J103" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K103">
         <v>24</v>
@@ -11409,7 +11418,7 @@
         <v>21.82222222</v>
       </c>
       <c r="W103" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X103">
         <v>-0.009506000000000001</v>
@@ -11441,7 +11450,7 @@
         <v>25</v>
       </c>
       <c r="B104" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C104" s="2">
         <v>45416.31719040509</v>
@@ -11459,13 +11468,13 @@
         <v>2779</v>
       </c>
       <c r="H104" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I104" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J104" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K104">
         <v>49</v>
@@ -11504,7 +11513,7 @@
         <v>20.13333333</v>
       </c>
       <c r="W104" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X104">
         <v>-0.028148</v>
@@ -11536,7 +11545,7 @@
         <v>25</v>
       </c>
       <c r="B105" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C105" s="2">
         <v>45416.31728564815</v>
@@ -11554,13 +11563,13 @@
         <v>2790</v>
       </c>
       <c r="H105" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I105" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J105" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="K105">
         <v>25</v>
@@ -11599,7 +11608,7 @@
         <v>21.79166667</v>
       </c>
       <c r="W105" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X105">
         <v>0.013819</v>
@@ -11631,7 +11640,7 @@
         <v>25</v>
       </c>
       <c r="B106" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C106" s="2">
         <v>45416.31750855324</v>
@@ -11649,13 +11658,13 @@
         <v>2809</v>
       </c>
       <c r="H106" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I106" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J106" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K106">
         <v>54</v>
@@ -11694,7 +11703,7 @@
         <v>18.66666667</v>
       </c>
       <c r="W106" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X106">
         <v>-0.104167</v>
@@ -11726,7 +11735,7 @@
         <v>25</v>
       </c>
       <c r="B107" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C107" s="2">
         <v>45416.31797965278</v>
@@ -11744,13 +11753,13 @@
         <v>2850</v>
       </c>
       <c r="H107" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I107" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J107" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K107">
         <v>88</v>
@@ -11789,7 +11798,7 @@
         <v>18.33333333</v>
       </c>
       <c r="W107" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X107">
         <v>-0.005556</v>
@@ -11821,7 +11830,7 @@
         <v>25</v>
       </c>
       <c r="B108" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C108" s="2">
         <v>45416.31835606482</v>
@@ -11839,13 +11848,13 @@
         <v>2880</v>
       </c>
       <c r="H108" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I108" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J108" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="K108">
         <v>112</v>
@@ -11884,7 +11893,7 @@
         <v>17.73333333</v>
       </c>
       <c r="W108" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X108">
         <v>-0.02</v>
@@ -11916,7 +11925,7 @@
         <v>25</v>
       </c>
       <c r="B109" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C109" s="2">
         <v>45416.31867484954</v>
@@ -11934,13 +11943,13 @@
         <v>2910</v>
       </c>
       <c r="H109" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I109" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J109" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K109">
         <v>193</v>
@@ -11979,7 +11988,7 @@
         <v>19.73333333</v>
       </c>
       <c r="W109" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X109">
         <v>0.066667</v>
@@ -12011,7 +12020,7 @@
         <v>25</v>
       </c>
       <c r="B110" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C110" s="2">
         <v>45416.31936898148</v>
@@ -12029,13 +12038,13 @@
         <v>2970</v>
       </c>
       <c r="H110" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I110" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J110" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K110">
         <v>47</v>
@@ -12074,7 +12083,7 @@
         <v>22.73333333</v>
       </c>
       <c r="W110" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X110">
         <v>0.05</v>
@@ -12106,7 +12115,7 @@
         <v>25</v>
       </c>
       <c r="B111" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C111" s="2">
         <v>45416.31958745371</v>
@@ -12124,13 +12133,13 @@
         <v>2989</v>
       </c>
       <c r="H111" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I111" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J111" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="K111">
         <v>41</v>
@@ -12169,7 +12178,7 @@
         <v>19.77777778</v>
       </c>
       <c r="W111" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X111">
         <v>-0.01642</v>
@@ -12201,7 +12210,7 @@
         <v>25</v>
       </c>
       <c r="B112" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C112" s="2">
         <v>45416.32065864583</v>
@@ -12219,13 +12228,13 @@
         <v>3079</v>
       </c>
       <c r="H112" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I112" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="J112" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="K112">
         <v>122</v>
@@ -12264,7 +12273,7 @@
         <v>19.48888889</v>
       </c>
       <c r="W112" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X112">
         <v>-0.00321</v>
@@ -12291,12 +12300,12 @@
         <v>19.79772</v>
       </c>
     </row>
-    <row r="113" spans="1:31">
+    <row r="113" spans="1:32">
       <c r="A113" t="s">
         <v>25</v>
       </c>
       <c r="B113" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C113" s="2">
         <v>45416.3207590625</v>
@@ -12314,13 +12323,13 @@
         <v>3090</v>
       </c>
       <c r="H113" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I113" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J113" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K113">
         <v>300</v>
@@ -12359,7 +12368,7 @@
         <v>19.38333333</v>
       </c>
       <c r="W113" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X113">
         <v>-0.00088</v>
@@ -12386,12 +12395,12 @@
         <v>19.742861</v>
       </c>
     </row>
-    <row r="114" spans="1:31">
+    <row r="114" spans="1:32">
       <c r="A114" t="s">
         <v>25</v>
       </c>
       <c r="B114" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C114" s="2">
         <v>45416.32097695602</v>
@@ -12409,13 +12418,13 @@
         <v>3109</v>
       </c>
       <c r="H114" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I114" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J114" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K114">
         <v>164</v>
@@ -12454,7 +12463,7 @@
         <v>20.96666667</v>
       </c>
       <c r="W114" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="X114">
         <v>0.052778</v>
@@ -12481,12 +12490,12 @@
         <v>19.608803</v>
       </c>
     </row>
-    <row r="115" spans="1:31">
+    <row r="115" spans="1:32">
       <c r="A115" t="s">
         <v>25</v>
       </c>
       <c r="B115" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C115" s="2">
         <v>45416.3214525463</v>
@@ -12504,13 +12513,13 @@
         <v>3150</v>
       </c>
       <c r="H115" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I115" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J115" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="K115">
         <v>112</v>
@@ -12549,7 +12558,7 @@
         <v>21.6</v>
       </c>
       <c r="W115" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X115">
         <v>0.010556</v>
@@ -12575,13 +12584,16 @@
       <c r="AE115">
         <v>19.339064</v>
       </c>
+      <c r="AF115" t="s">
+        <v>354</v>
+      </c>
     </row>
-    <row r="116" spans="1:31">
+    <row r="116" spans="1:32">
       <c r="A116" t="s">
         <v>25</v>
       </c>
       <c r="B116" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C116" s="2">
         <v>45416.32182875</v>
@@ -12599,13 +12611,13 @@
         <v>3180</v>
       </c>
       <c r="H116" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I116" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="J116" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="K116">
         <v>191</v>
@@ -12644,7 +12656,7 @@
         <v>17.83333333</v>
       </c>
       <c r="W116" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X116">
         <v>-0.125556</v>
@@ -12671,12 +12683,12 @@
         <v>19.168703</v>
       </c>
     </row>
-    <row r="117" spans="1:31">
+    <row r="117" spans="1:32">
       <c r="A117" t="s">
         <v>25</v>
       </c>
       <c r="B117" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C117" s="2">
         <v>45416.32204784722</v>
@@ -12694,13 +12706,13 @@
         <v>3199</v>
       </c>
       <c r="H117" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I117" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="J117" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K117">
         <v>28</v>
@@ -12739,7 +12751,7 @@
         <v>19.77777778</v>
       </c>
       <c r="W117" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X117">
         <v>0.021605</v>
@@ -12766,12 +12778,12 @@
         <v>19.046324</v>
       </c>
     </row>
-    <row r="118" spans="1:31">
+    <row r="118" spans="1:32">
       <c r="A118" t="s">
         <v>25</v>
       </c>
       <c r="B118" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C118" s="2">
         <v>45416.32214707176</v>
@@ -12789,13 +12801,13 @@
         <v>3210</v>
       </c>
       <c r="H118" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I118" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="J118" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K118">
         <v>321</v>
@@ -12834,7 +12846,7 @@
         <v>18.33333333</v>
       </c>
       <c r="W118" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X118">
         <v>-0.048148</v>
@@ -12861,12 +12873,12 @@
         <v>18.997483</v>
       </c>
     </row>
-    <row r="119" spans="1:31">
+    <row r="119" spans="1:32">
       <c r="A119" t="s">
         <v>25</v>
       </c>
       <c r="B119" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C119" s="2">
         <v>45416.32284148148</v>
@@ -12884,13 +12896,13 @@
         <v>3270</v>
       </c>
       <c r="H119" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I119" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J119" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K119">
         <v>24</v>
@@ -12929,7 +12941,7 @@
         <v>16.53333333</v>
       </c>
       <c r="W119" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X119">
         <v>-0.03</v>
@@ -12956,12 +12968,12 @@
         <v>18.712101</v>
       </c>
     </row>
-    <row r="120" spans="1:31">
+    <row r="120" spans="1:32">
       <c r="A120" t="s">
         <v>25</v>
       </c>
       <c r="B120" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C120" s="2">
         <v>45416.32353576389</v>
@@ -12979,13 +12991,13 @@
         <v>3330</v>
       </c>
       <c r="H120" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I120" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J120" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="K120">
         <v>88</v>
@@ -13024,7 +13036,7 @@
         <v>17.9</v>
       </c>
       <c r="W120" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X120">
         <v>0.022778</v>
@@ -13051,12 +13063,12 @@
         <v>18.45922</v>
       </c>
     </row>
-    <row r="121" spans="1:31">
+    <row r="121" spans="1:32">
       <c r="A121" t="s">
         <v>25</v>
       </c>
       <c r="B121" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C121" s="2">
         <v>45416.32423038194</v>
@@ -13074,13 +13086,13 @@
         <v>3390</v>
       </c>
       <c r="H121" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I121" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="J121" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K121">
         <v>221</v>
@@ -13119,7 +13131,7 @@
         <v>18.96666667</v>
       </c>
       <c r="W121" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X121">
         <v>0.017778</v>
@@ -13146,12 +13158,12 @@
         <v>18.278878</v>
       </c>
     </row>
-    <row r="122" spans="1:31">
+    <row r="122" spans="1:32">
       <c r="A122" t="s">
         <v>25</v>
       </c>
       <c r="B122" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C122" s="2">
         <v>45416.32492571759</v>
@@ -13169,13 +13181,13 @@
         <v>3450</v>
       </c>
       <c r="H122" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I122" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="J122" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="K122">
         <v>289</v>
@@ -13214,7 +13226,7 @@
         <v>18.63333333</v>
       </c>
       <c r="W122" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X122">
         <v>-0.005556</v>
@@ -13241,12 +13253,12 @@
         <v>18.203023</v>
       </c>
     </row>
-    <row r="123" spans="1:31">
+    <row r="123" spans="1:32">
       <c r="A123" t="s">
         <v>25</v>
       </c>
       <c r="B123" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C123" s="2">
         <v>45416.32561967592</v>
@@ -13264,13 +13276,13 @@
         <v>3510</v>
       </c>
       <c r="H123" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I123" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J123" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="K123">
         <v>341</v>
@@ -13309,7 +13321,7 @@
         <v>18.58333333</v>
       </c>
       <c r="W123" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X123">
         <v>-0.000833</v>
@@ -13336,12 +13348,12 @@
         <v>18.226248</v>
       </c>
     </row>
-    <row r="124" spans="1:31">
+    <row r="124" spans="1:32">
       <c r="A124" t="s">
         <v>25</v>
       </c>
       <c r="B124" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C124" s="2">
         <v>45416.32631473379</v>
@@ -13359,13 +13371,13 @@
         <v>3570</v>
       </c>
       <c r="H124" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I124" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J124" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="K124">
         <v>203</v>
@@ -13404,7 +13416,7 @@
         <v>17.96666667</v>
       </c>
       <c r="W124" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X124">
         <v>-0.010278</v>
@@ -13431,12 +13443,12 @@
         <v>18.326594</v>
       </c>
     </row>
-    <row r="125" spans="1:31">
+    <row r="125" spans="1:32">
       <c r="A125" t="s">
         <v>25</v>
       </c>
       <c r="B125" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C125" s="2">
         <v>45416.32669028935</v>
@@ -13454,13 +13466,13 @@
         <v>3600</v>
       </c>
       <c r="H125" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I125" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J125" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K125">
         <v>293</v>
@@ -13499,7 +13511,7 @@
         <v>18.33333333</v>
       </c>
       <c r="W125" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X125">
         <v>0.012222</v>
@@ -13526,12 +13538,12 @@
         <v>18.398368</v>
       </c>
     </row>
-    <row r="126" spans="1:31">
+    <row r="126" spans="1:32">
       <c r="A126" t="s">
         <v>25</v>
       </c>
       <c r="B126" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C126" s="2">
         <v>45416.32700880787</v>
@@ -13549,13 +13561,13 @@
         <v>3630</v>
       </c>
       <c r="H126" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I126" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="J126" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K126">
         <v>216</v>
@@ -13594,7 +13606,7 @@
         <v>18.93333333</v>
       </c>
       <c r="W126" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X126">
         <v>0.02</v>
@@ -13621,12 +13633,12 @@
         <v>18.480406</v>
       </c>
     </row>
-    <row r="127" spans="1:31">
+    <row r="127" spans="1:32">
       <c r="A127" t="s">
         <v>25</v>
       </c>
       <c r="B127" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C127" s="2">
         <v>45416.32770253472</v>
@@ -13644,13 +13656,13 @@
         <v>3690</v>
       </c>
       <c r="H127" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I127" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J127" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="K127">
         <v>47</v>
@@ -13689,7 +13701,7 @@
         <v>18.68333333</v>
       </c>
       <c r="W127" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X127">
         <v>-0.004167</v>
@@ -13716,12 +13728,12 @@
         <v>18.642334</v>
       </c>
     </row>
-    <row r="128" spans="1:31">
+    <row r="128" spans="1:32">
       <c r="A128" t="s">
         <v>25</v>
       </c>
       <c r="B128" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C128" s="2">
         <v>45416.3279222338</v>
@@ -13739,13 +13751,13 @@
         <v>3709</v>
       </c>
       <c r="H128" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I128" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J128" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="K128">
         <v>353</v>
@@ -13784,7 +13796,7 @@
         <v>18.29215686</v>
       </c>
       <c r="W128" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X128">
         <v>-0.000767</v>
@@ -13816,7 +13828,7 @@
         <v>25</v>
       </c>
       <c r="B129" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C129" s="2">
         <v>45416.32807935185</v>
@@ -13834,13 +13846,13 @@
         <v>3720</v>
       </c>
       <c r="H129" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I129" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J129" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K129">
         <v>5</v>
@@ -13879,7 +13891,7 @@
         <v>18.96666667</v>
       </c>
       <c r="W129" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X129">
         <v>0.022484</v>
@@ -13911,7 +13923,7 @@
         <v>25</v>
       </c>
       <c r="B130" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C130" s="2">
         <v>45416.32909188658</v>
@@ -13929,13 +13941,13 @@
         <v>3810</v>
       </c>
       <c r="H130" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I130" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="J130" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="K130">
         <v>303</v>
@@ -13974,7 +13986,7 @@
         <v>19.14444444</v>
       </c>
       <c r="W130" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X130">
         <v>0.001975</v>
@@ -14006,7 +14018,7 @@
         <v>25</v>
       </c>
       <c r="B131" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C131" s="2">
         <v>45416.32978655092</v>
@@ -14024,13 +14036,13 @@
         <v>3870</v>
       </c>
       <c r="H131" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I131" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J131" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="K131">
         <v>3</v>
@@ -14069,7 +14081,7 @@
         <v>18.55</v>
       </c>
       <c r="W131" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X131">
         <v>-0.009906999999999999</v>
@@ -14101,7 +14113,7 @@
         <v>25</v>
       </c>
       <c r="B132" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C132" s="2">
         <v>45416.33048126158</v>
@@ -14119,13 +14131,13 @@
         <v>3930</v>
       </c>
       <c r="H132" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I132" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="J132" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K132">
         <v>102</v>
@@ -14164,7 +14176,7 @@
         <v>17.71666667</v>
       </c>
       <c r="W132" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X132">
         <v>-0.013889</v>
@@ -14196,7 +14208,7 @@
         <v>25</v>
       </c>
       <c r="B133" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C133" s="2">
         <v>45416.33117584491</v>
@@ -14214,13 +14226,13 @@
         <v>3990</v>
       </c>
       <c r="H133" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I133" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="J133" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K133">
         <v>159</v>
@@ -14259,7 +14271,7 @@
         <v>18.46666667</v>
       </c>
       <c r="W133" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X133">
         <v>0.0125</v>
@@ -14291,7 +14303,7 @@
         <v>25</v>
       </c>
       <c r="B134" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C134" s="2">
         <v>45416.33187099537</v>
@@ -14309,13 +14321,13 @@
         <v>4050</v>
       </c>
       <c r="H134" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I134" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J134" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="K134">
         <v>48</v>
@@ -14354,7 +14366,7 @@
         <v>18.93333333</v>
       </c>
       <c r="W134" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X134">
         <v>0.007778</v>
@@ -14386,7 +14398,7 @@
         <v>25</v>
       </c>
       <c r="B135" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C135" s="2">
         <v>45416.33256486111</v>
@@ -14404,13 +14416,13 @@
         <v>4110</v>
       </c>
       <c r="H135" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I135" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="J135" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K135">
         <v>104</v>
@@ -14449,7 +14461,7 @@
         <v>18.03333333</v>
       </c>
       <c r="W135" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X135">
         <v>-0.015</v>
@@ -14481,7 +14493,7 @@
         <v>25</v>
       </c>
       <c r="B136" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C136" s="2">
         <v>45416.33325940972</v>
@@ -14499,13 +14511,13 @@
         <v>4170</v>
       </c>
       <c r="H136" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I136" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J136" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K136">
         <v>236</v>
@@ -14544,7 +14556,7 @@
         <v>17.56666667</v>
       </c>
       <c r="W136" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X136">
         <v>-0.007778</v>
@@ -14576,7 +14588,7 @@
         <v>25</v>
       </c>
       <c r="B137" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C137" s="2">
         <v>45416.33395407407</v>
@@ -14594,13 +14606,13 @@
         <v>4230</v>
       </c>
       <c r="H137" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I137" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="J137" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K137">
         <v>173</v>
@@ -14639,7 +14651,7 @@
         <v>18.33333333</v>
       </c>
       <c r="W137" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X137">
         <v>0.012778</v>
@@ -14671,7 +14683,7 @@
         <v>25</v>
       </c>
       <c r="B138" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C138" s="2">
         <v>45416.33464820602</v>
@@ -14689,13 +14701,13 @@
         <v>4290</v>
       </c>
       <c r="H138" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I138" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="J138" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K138">
         <v>135</v>
@@ -14734,7 +14746,7 @@
         <v>19.58333333</v>
       </c>
       <c r="W138" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X138">
         <v>0.020833</v>
@@ -14766,7 +14778,7 @@
         <v>25</v>
       </c>
       <c r="B139" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C139" s="2">
         <v>45416.33534385417</v>
@@ -14784,13 +14796,13 @@
         <v>4350</v>
       </c>
       <c r="H139" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I139" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J139" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K139">
         <v>55</v>
@@ -14829,7 +14841,7 @@
         <v>20.3</v>
       </c>
       <c r="W139" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X139">
         <v>0.011944</v>
@@ -14861,7 +14873,7 @@
         <v>25</v>
       </c>
       <c r="B140" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C140" s="2">
         <v>45416.33603737268</v>
@@ -14879,13 +14891,13 @@
         <v>4410</v>
       </c>
       <c r="H140" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I140" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="J140" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="K140">
         <v>36</v>
@@ -14924,7 +14936,7 @@
         <v>19.03333333</v>
       </c>
       <c r="W140" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="X140">
         <v>-0.021111</v>
@@ -14958,10 +14970,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE12"/>
+  <dimension ref="A1:AF12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:31">
+    <row r="1" spans="1:32">
       <c r="A1" s="1" t="s">
         <v>39</v>
       </c>
@@ -15055,13 +15067,16 @@
       <c r="AE1" s="1" t="s">
         <v>69</v>
       </c>
+      <c r="AF1" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="2" spans="1:31">
+    <row r="2" spans="1:32">
       <c r="A2" t="s">
         <v>25</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C2" s="2">
         <v>45416.3367315625</v>
@@ -15079,13 +15094,13 @@
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="K2">
         <v>189</v>
@@ -15124,7 +15139,7 @@
         <v>-63.55</v>
       </c>
       <c r="W2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Y2">
         <v>-63.55</v>
@@ -15133,12 +15148,12 @@
         <v>-63.55</v>
       </c>
     </row>
-    <row r="3" spans="1:31">
+    <row r="3" spans="1:32">
       <c r="A3" t="s">
         <v>25</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C3" s="2">
         <v>45416.33834126157</v>
@@ -15156,13 +15171,13 @@
         <v>139</v>
       </c>
       <c r="H3" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="J3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="K3">
         <v>278</v>
@@ -15201,7 +15216,7 @@
         <v>-2.51666667</v>
       </c>
       <c r="W3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X3">
         <v>0.067815</v>
@@ -15222,12 +15237,12 @@
         <v>-2.516667</v>
       </c>
     </row>
-    <row r="4" spans="1:31">
+    <row r="4" spans="1:32">
       <c r="A4" t="s">
         <v>25</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C4" s="2">
         <v>45416.33849724537</v>
@@ -15245,13 +15260,13 @@
         <v>150</v>
       </c>
       <c r="H4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I4" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="J4" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="K4">
         <v>94</v>
@@ -15290,7 +15305,7 @@
         <v>-82.30666667</v>
       </c>
       <c r="W4" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X4">
         <v>-0.531933</v>
@@ -15317,12 +15332,12 @@
         <v>-82.306667</v>
       </c>
     </row>
-    <row r="5" spans="1:31">
+    <row r="5" spans="1:32">
       <c r="A5" t="s">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" s="2">
         <v>45416.33882717592</v>
@@ -15340,13 +15355,13 @@
         <v>180</v>
       </c>
       <c r="H5" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I5" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J5" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="K5">
         <v>314</v>
@@ -15385,7 +15400,7 @@
         <v>-69.46666667</v>
       </c>
       <c r="W5" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X5">
         <v>0.428</v>
@@ -15412,12 +15427,12 @@
         <v>-69.466667</v>
       </c>
     </row>
-    <row r="6" spans="1:31">
+    <row r="6" spans="1:32">
       <c r="A6" t="s">
         <v>25</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C6" s="2">
         <v>45416.33919136574</v>
@@ -15435,13 +15450,13 @@
         <v>210</v>
       </c>
       <c r="H6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="J6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="K6">
         <v>229</v>
@@ -15480,7 +15495,7 @@
         <v>-63.4</v>
       </c>
       <c r="W6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X6">
         <v>0.202222</v>
@@ -15507,12 +15522,12 @@
         <v>-63.4</v>
       </c>
     </row>
-    <row r="7" spans="1:31">
+    <row r="7" spans="1:32">
       <c r="A7" t="s">
         <v>25</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" s="2">
         <v>45416.33950978009</v>
@@ -15530,13 +15545,13 @@
         <v>240</v>
       </c>
       <c r="H7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I7" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="J7" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="K7">
         <v>58</v>
@@ -15575,7 +15590,7 @@
         <v>-55.8</v>
       </c>
       <c r="W7" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X7">
         <v>0.253333</v>
@@ -15602,12 +15617,12 @@
         <v>-55.8</v>
       </c>
     </row>
-    <row r="8" spans="1:31">
+    <row r="8" spans="1:32">
       <c r="A8" t="s">
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C8" s="2">
         <v>45416.33988663195</v>
@@ -15625,13 +15640,13 @@
         <v>270</v>
       </c>
       <c r="H8" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I8" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="K8">
         <v>63</v>
@@ -15670,7 +15685,7 @@
         <v>-50.33333333</v>
       </c>
       <c r="W8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X8">
         <v>0.182222</v>
@@ -15697,12 +15712,12 @@
         <v>-50.333333</v>
       </c>
     </row>
-    <row r="9" spans="1:31">
+    <row r="9" spans="1:32">
       <c r="A9" t="s">
         <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C9" s="2">
         <v>45416.34020414352</v>
@@ -15720,13 +15735,13 @@
         <v>300</v>
       </c>
       <c r="H9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="J9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="K9">
         <v>26</v>
@@ -15765,7 +15780,7 @@
         <v>-53.3</v>
       </c>
       <c r="W9" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X9">
         <v>-0.098889</v>
@@ -15792,12 +15807,12 @@
         <v>-53.3</v>
       </c>
     </row>
-    <row r="10" spans="1:31">
+    <row r="10" spans="1:32">
       <c r="A10" t="s">
         <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" s="2">
         <v>45416.34111480324</v>
@@ -15815,13 +15830,13 @@
         <v>379</v>
       </c>
       <c r="H10" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I10" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="J10" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K10">
         <v>74</v>
@@ -15860,7 +15875,7 @@
         <v>-55.93333333</v>
       </c>
       <c r="W10" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X10">
         <v>-0.010972</v>
@@ -15887,12 +15902,12 @@
         <v>-55.933333</v>
       </c>
     </row>
-    <row r="11" spans="1:31">
+    <row r="11" spans="1:32">
       <c r="A11" t="s">
         <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" s="2">
         <v>45416.34197019676</v>
@@ -15910,13 +15925,13 @@
         <v>450</v>
       </c>
       <c r="H11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I11" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J11" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="K11">
         <v>11</v>
@@ -15955,7 +15970,7 @@
         <v>-46.19333333</v>
       </c>
       <c r="W11" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X11">
         <v>0.064933</v>
@@ -15982,12 +15997,12 @@
         <v>-46.193333</v>
       </c>
     </row>
-    <row r="12" spans="1:31">
+    <row r="12" spans="1:32">
       <c r="A12" t="s">
         <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C12" s="2">
         <v>45416.34597724537</v>
@@ -16005,13 +16020,13 @@
         <v>799</v>
       </c>
       <c r="H12" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="I12" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="J12" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K12">
         <v>59</v>
@@ -16050,7 +16065,7 @@
         <v>-35.93571429</v>
       </c>
       <c r="W12" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="X12">
         <v>0.024423</v>

--- a/www/flightdata/xlsx/eoss-358.xlsx
+++ b/www/flightdata/xlsx/eoss-358.xlsx
@@ -1734,7 +1734,7 @@
         <v>27275.03</v>
       </c>
       <c r="I2">
-        <v>250</v>
+        <v>152</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>

--- a/www/flightdata/xlsx/eoss-358.xlsx
+++ b/www/flightdata/xlsx/eoss-358.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="415">
   <si>
     <t>flight</t>
   </si>
@@ -57,6 +57,21 @@
     <t>range_distance_traveled_km</t>
   </si>
   <si>
+    <t>parachute.description</t>
+  </si>
+  <si>
+    <t>parachute.size_ft</t>
+  </si>
+  <si>
+    <t>parachute.size_m</t>
+  </si>
+  <si>
+    <t>parachute.weight_lb</t>
+  </si>
+  <si>
+    <t>parachute.weight_kg</t>
+  </si>
+  <si>
     <t>weights.client_lb</t>
   </si>
   <si>
@@ -99,6 +114,15 @@
     <t>weights.necklift_kg</t>
   </si>
   <si>
+    <t>detected_burst.detected</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_ft</t>
+  </si>
+  <si>
+    <t>detected_burst.burst_m</t>
+  </si>
+  <si>
     <t>launch_location.latitude</t>
   </si>
   <si>
@@ -148,6 +172,12 @@
   </si>
   <si>
     <t>1hrs 28mins 19secs</t>
+  </si>
+  <si>
+    <t>Rocketman</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>flightid</t>
@@ -1592,10 +1622,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK2"/>
+  <dimension ref="A1:AS2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:37">
+    <row r="1" spans="1:45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1707,25 +1737,49 @@
       <c r="AK1" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
     </row>
-    <row r="2" spans="1:37">
+    <row r="2" spans="1:45">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G2">
         <v>89485</v>
@@ -1737,7 +1791,7 @@
         <v>152</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K2">
         <v>5299</v>
@@ -1748,76 +1802,100 @@
       <c r="M2">
         <v>60.13</v>
       </c>
-      <c r="N2">
+      <c r="N2" t="s">
+        <v>52</v>
+      </c>
+      <c r="O2" t="s">
+        <v>53</v>
+      </c>
+      <c r="P2">
+        <v>3.66</v>
+      </c>
+      <c r="Q2">
+        <v>1.81</v>
+      </c>
+      <c r="R2">
+        <v>0.82</v>
+      </c>
+      <c r="S2">
         <v>6.64</v>
       </c>
-      <c r="O2">
+      <c r="T2">
         <v>3.01</v>
       </c>
-      <c r="P2">
+      <c r="U2">
         <v>3.44</v>
       </c>
-      <c r="Q2">
+      <c r="V2">
         <v>1.56</v>
       </c>
-      <c r="R2">
+      <c r="W2">
         <v>1.81</v>
       </c>
-      <c r="S2">
+      <c r="X2">
         <v>0.82</v>
       </c>
-      <c r="T2">
+      <c r="Y2">
         <v>11.89</v>
       </c>
-      <c r="U2">
+      <c r="Z2">
         <v>5.39</v>
       </c>
-      <c r="V2">
+      <c r="AA2">
         <v>3.31</v>
       </c>
-      <c r="W2">
+      <c r="AB2">
         <v>1.5</v>
       </c>
-      <c r="X2">
+      <c r="AC2">
         <v>15.19</v>
       </c>
-      <c r="Y2">
+      <c r="AD2">
         <v>6.89</v>
       </c>
-      <c r="Z2">
+      <c r="AE2">
         <v>16.45</v>
       </c>
-      <c r="AA2">
+      <c r="AF2">
         <v>7.46</v>
       </c>
-      <c r="AB2">
+      <c r="AG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AH2">
+        <v>89727</v>
+      </c>
+      <c r="AI2">
+        <v>27348.79</v>
+      </c>
+      <c r="AJ2">
         <v>39.6081666667</v>
       </c>
-      <c r="AC2">
+      <c r="AK2">
         <v>-104.0421666667</v>
       </c>
-      <c r="AD2">
+      <c r="AL2">
         <v>5213</v>
       </c>
-      <c r="AE2">
+      <c r="AM2">
         <v>1588.92</v>
       </c>
-      <c r="AF2">
+      <c r="AN2">
         <v>39.7646666667</v>
       </c>
-      <c r="AG2">
+      <c r="AO2">
         <v>-103.369</v>
       </c>
-      <c r="AH2">
+      <c r="AP2">
         <v>37.36</v>
       </c>
-      <c r="AI2">
+      <c r="AQ2">
         <v>60.13</v>
       </c>
-      <c r="AJ2">
+      <c r="AR2">
         <v>45636</v>
       </c>
-      <c r="AK2">
+      <c r="AS2">
         <v>13909.85</v>
       </c>
     </row>
@@ -1833,156 +1911,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2">
         <v>45416.28464461806</v>
@@ -2003,16 +2081,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="L2" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="M2">
         <v>86</v>
@@ -2069,7 +2147,7 @@
         <v>-0.051</v>
       </c>
       <c r="AE2" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AG2">
         <v>-0.166667</v>
@@ -2086,10 +2164,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C3" s="2">
         <v>45416.28486782408</v>
@@ -2110,16 +2188,16 @@
         <v>19</v>
       </c>
       <c r="I3" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="L3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="M3">
         <v>43</v>
@@ -2176,7 +2254,7 @@
         <v>0.21333333</v>
       </c>
       <c r="AE3" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF3">
         <v>0.028889</v>
@@ -2217,10 +2295,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2">
         <v>45416.28501981482</v>
@@ -2241,16 +2319,16 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="L4" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="M4">
         <v>20</v>
@@ -2307,7 +2385,7 @@
         <v>1.56466667</v>
       </c>
       <c r="AE4" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF4">
         <v>0.147778</v>
@@ -2360,10 +2438,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2">
         <v>45416.28524439815</v>
@@ -2384,16 +2462,16 @@
         <v>49</v>
       </c>
       <c r="I5" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="L5" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="M5">
         <v>59</v>
@@ -2450,7 +2528,7 @@
         <v>5.527</v>
       </c>
       <c r="AE5" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF5">
         <v>0.433333</v>
@@ -2503,10 +2581,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2">
         <v>45416.28533979167</v>
@@ -2527,16 +2605,16 @@
         <v>60</v>
       </c>
       <c r="I6" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="L6" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="M6">
         <v>116</v>
@@ -2593,7 +2671,7 @@
         <v>5.974</v>
       </c>
       <c r="AE6" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF6">
         <v>0.048889</v>
@@ -2646,10 +2724,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2">
         <v>45416.28556251158</v>
@@ -2670,16 +2748,16 @@
         <v>79</v>
       </c>
       <c r="I7" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L7" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="M7">
         <v>298</v>
@@ -2736,7 +2814,7 @@
         <v>6.594</v>
       </c>
       <c r="AE7" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF7">
         <v>0.067778</v>
@@ -2789,10 +2867,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2">
         <v>45416.28571474537</v>
@@ -2813,16 +2891,16 @@
         <v>90</v>
       </c>
       <c r="I8" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="L8" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="M8">
         <v>314</v>
@@ -2879,7 +2957,7 @@
         <v>6.401</v>
       </c>
       <c r="AE8" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF8">
         <v>-0.021111</v>
@@ -2932,10 +3010,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2">
         <v>45416.28593912037</v>
@@ -2956,16 +3034,16 @@
         <v>109</v>
       </c>
       <c r="I9" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="L9" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="M9">
         <v>275</v>
@@ -3022,7 +3100,7 @@
         <v>5.67933333</v>
       </c>
       <c r="AE9" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF9">
         <v>-0.078889</v>
@@ -3075,10 +3153,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C10" s="2">
         <v>45416.28603229167</v>
@@ -3099,16 +3177,16 @@
         <v>120</v>
       </c>
       <c r="I10" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L10" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="M10">
         <v>271</v>
@@ -3165,7 +3243,7 @@
         <v>5.842</v>
       </c>
       <c r="AE10" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF10">
         <v>0.017778</v>
@@ -3218,10 +3296,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2">
         <v>45416.28625826389</v>
@@ -3242,16 +3320,16 @@
         <v>139</v>
       </c>
       <c r="I11" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="L11" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="M11">
         <v>271</v>
@@ -3308,7 +3386,7 @@
         <v>5.964</v>
       </c>
       <c r="AE11" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF11">
         <v>0.013333</v>
@@ -3361,10 +3439,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C12" s="2">
         <v>45416.28640918982</v>
@@ -3385,16 +3463,16 @@
         <v>150</v>
       </c>
       <c r="I12" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="L12" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="M12">
         <v>244</v>
@@ -3451,7 +3529,7 @@
         <v>6.05533333</v>
       </c>
       <c r="AE12" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF12">
         <v>0.01</v>
@@ -3504,10 +3582,10 @@
     </row>
     <row r="13" spans="1:48">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C13" s="2">
         <v>45416.28663488426</v>
@@ -3528,16 +3606,16 @@
         <v>169</v>
       </c>
       <c r="I13" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J13" t="b">
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="L13" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="M13">
         <v>246</v>
@@ -3594,7 +3672,7 @@
         <v>6.40066667</v>
       </c>
       <c r="AE13" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF13">
         <v>0.037778</v>
@@ -3647,10 +3725,10 @@
     </row>
     <row r="14" spans="1:48">
       <c r="A14" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C14" s="2">
         <v>45416.28672798611</v>
@@ -3671,16 +3749,16 @@
         <v>180</v>
       </c>
       <c r="I14" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J14" t="b">
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="L14" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="M14">
         <v>210</v>
@@ -3737,7 +3815,7 @@
         <v>6.52266667</v>
       </c>
       <c r="AE14" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF14">
         <v>0.013333</v>
@@ -3790,10 +3868,10 @@
     </row>
     <row r="15" spans="1:48">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B15" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C15" s="2">
         <v>45416.28695288194</v>
@@ -3814,16 +3892,16 @@
         <v>199</v>
       </c>
       <c r="I15" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J15" t="b">
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="L15" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="M15">
         <v>183</v>
@@ -3880,7 +3958,7 @@
         <v>6.533</v>
       </c>
       <c r="AE15" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF15">
         <v>0.001111</v>
@@ -3933,10 +4011,10 @@
     </row>
     <row r="16" spans="1:48">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C16" s="2">
         <v>45416.28710354167</v>
@@ -3957,16 +4035,16 @@
         <v>210</v>
       </c>
       <c r="I16" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J16" t="b">
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="L16" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="M16">
         <v>234</v>
@@ -4023,7 +4101,7 @@
         <v>6.12633333</v>
       </c>
       <c r="AE16" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF16">
         <v>-0.044444</v>
@@ -4076,10 +4154,10 @@
     </row>
     <row r="17" spans="1:47">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B17" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C17" s="2">
         <v>45416.2874396412</v>
@@ -4100,16 +4178,16 @@
         <v>240</v>
       </c>
       <c r="I17" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J17" t="b">
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="L17" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="M17">
         <v>149</v>
@@ -4166,7 +4244,7 @@
         <v>6.411</v>
       </c>
       <c r="AE17" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF17">
         <v>0.031111</v>
@@ -4219,10 +4297,10 @@
     </row>
     <row r="18" spans="1:47">
       <c r="A18" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C18" s="2">
         <v>45416.28764791667</v>
@@ -4243,16 +4321,16 @@
         <v>259</v>
       </c>
       <c r="I18" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J18" t="b">
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="L18" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="M18">
         <v>66</v>
@@ -4309,7 +4387,7 @@
         <v>6.36516667</v>
       </c>
       <c r="AE18" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF18">
         <v>-0.0025</v>
@@ -4362,10 +4440,10 @@
     </row>
     <row r="19" spans="1:47">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C19" s="2">
         <v>45416.28779834491</v>
@@ -4386,16 +4464,16 @@
         <v>270</v>
       </c>
       <c r="I19" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J19" t="b">
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="M19">
         <v>109</v>
@@ -4452,7 +4530,7 @@
         <v>6.24866667</v>
       </c>
       <c r="AE19" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF19">
         <v>-0.012778</v>
@@ -4505,10 +4583,10 @@
     </row>
     <row r="20" spans="1:47">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C20" s="2">
         <v>45416.28811732639</v>
@@ -4529,16 +4607,16 @@
         <v>300</v>
       </c>
       <c r="I20" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J20" t="b">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="L20" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="M20">
         <v>34</v>
@@ -4595,7 +4673,7 @@
         <v>6.553</v>
       </c>
       <c r="AE20" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF20">
         <v>0.033333</v>
@@ -4648,10 +4726,10 @@
     </row>
     <row r="21" spans="1:47">
       <c r="A21" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C21" s="2">
         <v>45416.28834163195</v>
@@ -4672,16 +4750,16 @@
         <v>319</v>
       </c>
       <c r="I21" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J21" t="b">
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="L21" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="M21">
         <v>42</v>
@@ -4738,7 +4816,7 @@
         <v>6.14183333</v>
       </c>
       <c r="AE21" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF21">
         <v>-0.0225</v>
@@ -4791,10 +4869,10 @@
     </row>
     <row r="22" spans="1:47">
       <c r="A22" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C22" s="2">
         <v>45416.28849383102</v>
@@ -4815,16 +4893,16 @@
         <v>330</v>
       </c>
       <c r="I22" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J22" t="b">
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="L22" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="M22">
         <v>65</v>
@@ -4881,7 +4959,7 @@
         <v>6.289</v>
       </c>
       <c r="AE22" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF22">
         <v>0.016111</v>
@@ -4934,10 +5012,10 @@
     </row>
     <row r="23" spans="1:47">
       <c r="A23" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2">
         <v>45416.28881193287</v>
@@ -4958,16 +5036,16 @@
         <v>360</v>
       </c>
       <c r="I23" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J23" t="b">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="L23" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="M23">
         <v>56</v>
@@ -5024,7 +5102,7 @@
         <v>5.446</v>
       </c>
       <c r="AE23" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF23">
         <v>-0.092222</v>
@@ -5077,10 +5155,10 @@
     </row>
     <row r="24" spans="1:47">
       <c r="A24" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C24" s="2">
         <v>45416.28903572917</v>
@@ -5101,16 +5179,16 @@
         <v>379</v>
       </c>
       <c r="I24" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J24" t="b">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="L24" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="M24">
         <v>72</v>
@@ -5167,7 +5245,7 @@
         <v>5.847</v>
       </c>
       <c r="AE24" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF24">
         <v>0.021944</v>
@@ -5220,10 +5298,10 @@
     </row>
     <row r="25" spans="1:47">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C25" s="2">
         <v>45416.28918784722</v>
@@ -5244,16 +5322,16 @@
         <v>390</v>
       </c>
       <c r="I25" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J25" t="b">
         <v>1</v>
       </c>
       <c r="K25" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="L25" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="M25">
         <v>95</v>
@@ -5310,7 +5388,7 @@
         <v>5.80133333</v>
       </c>
       <c r="AE25" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF25">
         <v>-0.005</v>
@@ -5363,10 +5441,10 @@
     </row>
     <row r="26" spans="1:47">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C26" s="2">
         <v>45416.28950773148</v>
@@ -5387,16 +5465,16 @@
         <v>420</v>
       </c>
       <c r="I26" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J26" t="b">
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="L26" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="M26">
         <v>80</v>
@@ -5453,7 +5531,7 @@
         <v>5.74033333</v>
       </c>
       <c r="AE26" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF26">
         <v>-0.006667</v>
@@ -5506,10 +5584,10 @@
     </row>
     <row r="27" spans="1:47">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C27" s="2">
         <v>45416.28972934028</v>
@@ -5530,16 +5608,16 @@
         <v>439</v>
       </c>
       <c r="I27" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J27" t="b">
         <v>1</v>
       </c>
       <c r="K27" t="s">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="L27" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="M27">
         <v>89</v>
@@ -5596,7 +5674,7 @@
         <v>5.72016667</v>
       </c>
       <c r="AE27" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF27">
         <v>-0.001111</v>
@@ -5649,10 +5727,10 @@
     </row>
     <row r="28" spans="1:47">
       <c r="A28" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C28" s="2">
         <v>45416.28988243055</v>
@@ -5673,16 +5751,16 @@
         <v>450</v>
       </c>
       <c r="I28" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J28" t="b">
         <v>1</v>
       </c>
       <c r="K28" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="L28" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="M28">
         <v>81</v>
@@ -5739,7 +5817,7 @@
         <v>5.94366667</v>
       </c>
       <c r="AE28" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF28">
         <v>0.024444</v>
@@ -5792,10 +5870,10 @@
     </row>
     <row r="29" spans="1:47">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C29" s="2">
         <v>45416.2902003125</v>
@@ -5816,16 +5894,16 @@
         <v>480</v>
       </c>
       <c r="I29" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J29" t="b">
         <v>1</v>
       </c>
       <c r="K29" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="L29" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="M29">
         <v>84</v>
@@ -5882,7 +5960,7 @@
         <v>5.99433333</v>
       </c>
       <c r="AE29" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF29">
         <v>0.005556</v>
@@ -5935,10 +6013,10 @@
     </row>
     <row r="30" spans="1:47">
       <c r="A30" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C30" s="2">
         <v>45416.29042340278</v>
@@ -5959,16 +6037,16 @@
         <v>499</v>
       </c>
       <c r="I30" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J30" t="b">
         <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="L30" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="M30">
         <v>82</v>
@@ -6025,7 +6103,7 @@
         <v>5.908</v>
       </c>
       <c r="AE30" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF30">
         <v>-0.004722</v>
@@ -6078,10 +6156,10 @@
     </row>
     <row r="31" spans="1:47">
       <c r="A31" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C31" s="2">
         <v>45416.29057700231</v>
@@ -6102,16 +6180,16 @@
         <v>510</v>
       </c>
       <c r="I31" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J31" t="b">
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="M31">
         <v>99</v>
@@ -6168,7 +6246,7 @@
         <v>5.527</v>
       </c>
       <c r="AE31" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF31">
         <v>-0.041667</v>
@@ -6221,10 +6299,10 @@
     </row>
     <row r="32" spans="1:47">
       <c r="A32" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B32" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C32" s="2">
         <v>45416.29089520833</v>
@@ -6245,16 +6323,16 @@
         <v>540</v>
       </c>
       <c r="I32" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J32" t="b">
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="L32" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="M32">
         <v>96</v>
@@ -6311,7 +6389,7 @@
         <v>5.60833333</v>
       </c>
       <c r="AE32" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF32">
         <v>0.008888999999999999</v>
@@ -6364,10 +6442,10 @@
     </row>
     <row r="33" spans="1:47">
       <c r="A33" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B33" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C33" s="2">
         <v>45416.29111777778</v>
@@ -6388,16 +6466,16 @@
         <v>559</v>
       </c>
       <c r="I33" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J33" t="b">
         <v>1</v>
       </c>
       <c r="K33" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="M33">
         <v>106</v>
@@ -6454,7 +6532,7 @@
         <v>5.56266667</v>
       </c>
       <c r="AE33" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF33">
         <v>-0.0025</v>
@@ -6507,10 +6585,10 @@
     </row>
     <row r="34" spans="1:47">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B34" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C34" s="2">
         <v>45416.29127113426</v>
@@ -6531,16 +6609,16 @@
         <v>570</v>
       </c>
       <c r="I34" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J34" t="b">
         <v>1</v>
       </c>
       <c r="K34" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="L34" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="M34">
         <v>97</v>
@@ -6597,7 +6675,7 @@
         <v>5.25266667</v>
       </c>
       <c r="AE34" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF34">
         <v>-0.033889</v>
@@ -6650,10 +6728,10 @@
     </row>
     <row r="35" spans="1:47">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B35" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C35" s="2">
         <v>45416.29158898148</v>
@@ -6674,16 +6752,16 @@
         <v>600</v>
       </c>
       <c r="I35" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J35" t="b">
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="L35" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="M35">
         <v>95</v>
@@ -6740,7 +6818,7 @@
         <v>6.44133333</v>
       </c>
       <c r="AE35" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF35">
         <v>0.13</v>
@@ -6793,10 +6871,10 @@
     </row>
     <row r="36" spans="1:47">
       <c r="A36" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B36" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C36" s="2">
         <v>45416.29181238426</v>
@@ -6817,16 +6895,16 @@
         <v>619</v>
       </c>
       <c r="I36" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J36" t="b">
         <v>1</v>
       </c>
       <c r="K36" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="L36" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="M36">
         <v>88</v>
@@ -6883,7 +6961,7 @@
         <v>5.87233333</v>
       </c>
       <c r="AE36" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF36">
         <v>-0.031111</v>
@@ -6936,10 +7014,10 @@
     </row>
     <row r="37" spans="1:47">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C37" s="2">
         <v>45416.29196631945</v>
@@ -6960,16 +7038,16 @@
         <v>630</v>
       </c>
       <c r="I37" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J37" t="b">
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="L37" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="M37">
         <v>105</v>
@@ -7026,7 +7104,7 @@
         <v>5.43566667</v>
       </c>
       <c r="AE37" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF37">
         <v>-0.047778</v>
@@ -7079,10 +7157,10 @@
     </row>
     <row r="38" spans="1:47">
       <c r="A38" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B38" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C38" s="2">
         <v>45416.2922846875</v>
@@ -7103,16 +7181,16 @@
         <v>660</v>
       </c>
       <c r="I38" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J38" t="b">
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="L38" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="M38">
         <v>111</v>
@@ -7169,7 +7247,7 @@
         <v>5.456</v>
       </c>
       <c r="AE38" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF38">
         <v>0.002222</v>
@@ -7222,10 +7300,10 @@
     </row>
     <row r="39" spans="1:47">
       <c r="A39" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C39" s="2">
         <v>45416.29266038194</v>
@@ -7246,16 +7324,16 @@
         <v>690</v>
       </c>
       <c r="I39" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J39" t="b">
         <v>1</v>
       </c>
       <c r="K39" t="s">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="L39" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="M39">
         <v>90</v>
@@ -7312,7 +7390,7 @@
         <v>6.13666667</v>
       </c>
       <c r="AE39" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF39">
         <v>0.074444</v>
@@ -7365,10 +7443,10 @@
     </row>
     <row r="40" spans="1:47">
       <c r="A40" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B40" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C40" s="2">
         <v>45416.292978125</v>
@@ -7389,16 +7467,16 @@
         <v>720</v>
       </c>
       <c r="I40" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J40" t="b">
         <v>1</v>
       </c>
       <c r="K40" t="s">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="L40" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M40">
         <v>69</v>
@@ -7455,7 +7533,7 @@
         <v>5.72</v>
       </c>
       <c r="AE40" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF40">
         <v>-0.045556</v>
@@ -7508,10 +7586,10 @@
     </row>
     <row r="41" spans="1:47">
       <c r="A41" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C41" s="2">
         <v>45416.29335501158</v>
@@ -7532,16 +7610,16 @@
         <v>750</v>
       </c>
       <c r="I41" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J41" t="b">
         <v>1</v>
       </c>
       <c r="K41" t="s">
-        <v>134</v>
+        <v>144</v>
       </c>
       <c r="L41" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="M41">
         <v>63</v>
@@ -7598,7 +7676,7 @@
         <v>5.49666667</v>
       </c>
       <c r="AE41" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF41">
         <v>-0.024444</v>
@@ -7651,10 +7729,10 @@
     </row>
     <row r="42" spans="1:47">
       <c r="A42" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B42" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C42" s="2">
         <v>45416.29367321759</v>
@@ -7675,16 +7753,16 @@
         <v>780</v>
       </c>
       <c r="I42" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J42" t="b">
         <v>1</v>
       </c>
       <c r="K42" t="s">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="L42" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="M42">
         <v>87</v>
@@ -7741,7 +7819,7 @@
         <v>5.24233333</v>
       </c>
       <c r="AE42" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF42">
         <v>-0.027778</v>
@@ -7794,10 +7872,10 @@
     </row>
     <row r="43" spans="1:47">
       <c r="A43" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B43" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C43" s="2">
         <v>45416.29405516203</v>
@@ -7818,16 +7896,16 @@
         <v>810</v>
       </c>
       <c r="I43" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J43" t="b">
         <v>1</v>
       </c>
       <c r="K43" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="L43" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="M43">
         <v>96</v>
@@ -7884,7 +7962,7 @@
         <v>5.61866667</v>
       </c>
       <c r="AE43" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF43">
         <v>0.041111</v>
@@ -7937,10 +8015,10 @@
     </row>
     <row r="44" spans="1:47">
       <c r="A44" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B44" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C44" s="2">
         <v>45416.29436784722</v>
@@ -7961,16 +8039,16 @@
         <v>840</v>
       </c>
       <c r="I44" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J44" t="b">
         <v>1</v>
       </c>
       <c r="K44" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="L44" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="M44">
         <v>75</v>
@@ -8027,7 +8105,7 @@
         <v>5.86233333</v>
       </c>
       <c r="AE44" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF44">
         <v>0.026667</v>
@@ -8080,10 +8158,10 @@
     </row>
     <row r="45" spans="1:47">
       <c r="A45" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B45" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C45" s="2">
         <v>45416.29474569445</v>
@@ -8104,16 +8182,16 @@
         <v>870</v>
       </c>
       <c r="I45" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J45" t="b">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>138</v>
+        <v>148</v>
       </c>
       <c r="L45" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="M45">
         <v>94</v>
@@ -8170,7 +8248,7 @@
         <v>4.99866667</v>
       </c>
       <c r="AE45" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF45">
         <v>-0.094444</v>
@@ -8223,10 +8301,10 @@
     </row>
     <row r="46" spans="1:47">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C46" s="2">
         <v>45416.29506273148</v>
@@ -8247,16 +8325,16 @@
         <v>900</v>
       </c>
       <c r="I46" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J46" t="b">
         <v>1</v>
       </c>
       <c r="K46" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="L46" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="M46">
         <v>90</v>
@@ -8313,7 +8391,7 @@
         <v>5.49666667</v>
       </c>
       <c r="AE46" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF46">
         <v>0.054444</v>
@@ -8366,10 +8444,10 @@
     </row>
     <row r="47" spans="1:47">
       <c r="A47" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C47" s="2">
         <v>45416.29543877315</v>
@@ -8390,16 +8468,16 @@
         <v>930</v>
       </c>
       <c r="I47" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J47" t="b">
         <v>1</v>
       </c>
       <c r="K47" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="L47" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="M47">
         <v>98</v>
@@ -8456,7 +8534,7 @@
         <v>5.13066667</v>
       </c>
       <c r="AE47" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF47">
         <v>-0.04</v>
@@ -8509,10 +8587,10 @@
     </row>
     <row r="48" spans="1:47">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B48" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C48" s="2">
         <v>45416.29575668981</v>
@@ -8533,16 +8611,16 @@
         <v>960</v>
       </c>
       <c r="I48" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J48" t="b">
         <v>1</v>
       </c>
       <c r="K48" t="s">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="L48" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="M48">
         <v>86</v>
@@ -8599,7 +8677,7 @@
         <v>6.279</v>
       </c>
       <c r="AE48" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF48">
         <v>0.125556</v>
@@ -8652,10 +8730,10 @@
     </row>
     <row r="49" spans="1:47">
       <c r="A49" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C49" s="2">
         <v>45416.29613241898</v>
@@ -8676,16 +8754,16 @@
         <v>990</v>
       </c>
       <c r="I49" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J49" t="b">
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="L49" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="M49">
         <v>93</v>
@@ -8742,7 +8820,7 @@
         <v>5.44566667</v>
       </c>
       <c r="AE49" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF49">
         <v>-0.091111</v>
@@ -8795,10 +8873,10 @@
     </row>
     <row r="50" spans="1:47">
       <c r="A50" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C50" s="2">
         <v>45416.29645150463</v>
@@ -8819,16 +8897,16 @@
         <v>1020</v>
       </c>
       <c r="I50" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J50" t="b">
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="L50" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="M50">
         <v>72</v>
@@ -8885,7 +8963,7 @@
         <v>5.29333333</v>
       </c>
       <c r="AE50" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF50">
         <v>-0.016667</v>
@@ -8938,10 +9016,10 @@
     </row>
     <row r="51" spans="1:47">
       <c r="A51" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C51" s="2">
         <v>45416.29682668982</v>
@@ -8962,16 +9040,16 @@
         <v>1050</v>
       </c>
       <c r="I51" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J51" t="b">
         <v>1</v>
       </c>
       <c r="K51" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="L51" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="M51">
         <v>68</v>
@@ -9028,7 +9106,7 @@
         <v>4.98866667</v>
       </c>
       <c r="AE51" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF51">
         <v>-0.033333</v>
@@ -9081,10 +9159,10 @@
     </row>
     <row r="52" spans="1:47">
       <c r="A52" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B52" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C52" s="2">
         <v>45416.29714474537</v>
@@ -9105,16 +9183,16 @@
         <v>1080</v>
       </c>
       <c r="I52" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J52" t="b">
         <v>1</v>
       </c>
       <c r="K52" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="L52" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="M52">
         <v>84</v>
@@ -9171,7 +9249,7 @@
         <v>6.12633333</v>
       </c>
       <c r="AE52" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF52">
         <v>0.124444</v>
@@ -9224,10 +9302,10 @@
     </row>
     <row r="53" spans="1:47">
       <c r="A53" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B53" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C53" s="2">
         <v>45416.29737010417</v>
@@ -9248,16 +9326,16 @@
         <v>1099</v>
       </c>
       <c r="I53" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J53" t="b">
         <v>1</v>
       </c>
       <c r="K53" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="L53" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="M53">
         <v>83</v>
@@ -9314,7 +9392,7 @@
         <v>5.55308333</v>
       </c>
       <c r="AE53" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF53">
         <v>-0.003919</v>
@@ -9367,10 +9445,10 @@
     </row>
     <row r="54" spans="1:47">
       <c r="A54" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C54" s="2">
         <v>45416.29752219907</v>
@@ -9391,16 +9469,16 @@
         <v>1110</v>
       </c>
       <c r="I54" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J54" t="b">
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="L54" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="M54">
         <v>85</v>
@@ -9457,7 +9535,7 @@
         <v>5.68966667</v>
       </c>
       <c r="AE54" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF54">
         <v>0.014931</v>
@@ -9510,10 +9588,10 @@
     </row>
     <row r="55" spans="1:47">
       <c r="A55" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B55" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C55" s="2">
         <v>45416.29783983796</v>
@@ -9534,16 +9612,16 @@
         <v>1140</v>
       </c>
       <c r="I55" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J55" t="b">
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="L55" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="M55">
         <v>84</v>
@@ -9600,7 +9678,7 @@
         <v>5.38466667</v>
       </c>
       <c r="AE55" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF55">
         <v>-0.033333</v>
@@ -9653,10 +9731,10 @@
     </row>
     <row r="56" spans="1:47">
       <c r="A56" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B56" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C56" s="2">
         <v>45416.29821638889</v>
@@ -9677,16 +9755,16 @@
         <v>1170</v>
       </c>
       <c r="I56" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J56" t="b">
         <v>1</v>
       </c>
       <c r="K56" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="L56" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="M56">
         <v>68</v>
@@ -9743,7 +9821,7 @@
         <v>5.324</v>
       </c>
       <c r="AE56" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF56">
         <v>-0.006667</v>
@@ -9796,10 +9874,10 @@
     </row>
     <row r="57" spans="1:47">
       <c r="A57" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B57" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C57" s="2">
         <v>45416.29853439815</v>
@@ -9820,16 +9898,16 @@
         <v>1200</v>
       </c>
       <c r="I57" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J57" t="b">
         <v>1</v>
       </c>
       <c r="K57" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="L57" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="M57">
         <v>78</v>
@@ -9886,7 +9964,7 @@
         <v>5.76066667</v>
       </c>
       <c r="AE57" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF57">
         <v>0.047778</v>
@@ -9939,10 +10017,10 @@
     </row>
     <row r="58" spans="1:47">
       <c r="A58" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B58" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C58" s="2">
         <v>45416.29890998843</v>
@@ -9963,16 +10041,16 @@
         <v>1230</v>
       </c>
       <c r="I58" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J58" t="b">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="L58" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="M58">
         <v>96</v>
@@ -10029,7 +10107,7 @@
         <v>6.472</v>
       </c>
       <c r="AE58" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF58">
         <v>0.077778</v>
@@ -10082,10 +10160,10 @@
     </row>
     <row r="59" spans="1:47">
       <c r="A59" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B59" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C59" s="2">
         <v>45416.2991312963</v>
@@ -10106,16 +10184,16 @@
         <v>1249</v>
       </c>
       <c r="I59" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J59" t="b">
         <v>1</v>
       </c>
       <c r="K59" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="L59" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="M59">
         <v>73</v>
@@ -10172,7 +10250,7 @@
         <v>5.75866667</v>
       </c>
       <c r="AE59" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF59">
         <v>-0.0156</v>
@@ -10225,10 +10303,10 @@
     </row>
     <row r="60" spans="1:47">
       <c r="A60" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B60" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C60" s="2">
         <v>45416.29922893518</v>
@@ -10249,16 +10327,16 @@
         <v>1260</v>
       </c>
       <c r="I60" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J60" t="b">
         <v>1</v>
       </c>
       <c r="K60" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="L60" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="M60">
         <v>61</v>
@@ -10315,7 +10393,7 @@
         <v>6.59366667</v>
       </c>
       <c r="AE60" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF60">
         <v>0.091333</v>
@@ -10368,10 +10446,10 @@
     </row>
     <row r="61" spans="1:47">
       <c r="A61" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B61" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C61" s="2">
         <v>45416.2996050463</v>
@@ -10392,16 +10470,16 @@
         <v>1290</v>
       </c>
       <c r="I61" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J61" t="b">
         <v>1</v>
       </c>
       <c r="K61" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="L61" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="M61">
         <v>68</v>
@@ -10458,7 +10536,7 @@
         <v>6.716</v>
       </c>
       <c r="AE61" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF61">
         <v>0.013333</v>
@@ -10511,10 +10589,10 @@
     </row>
     <row r="62" spans="1:47">
       <c r="A62" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B62" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C62" s="2">
         <v>45416.29982586805</v>
@@ -10535,16 +10613,16 @@
         <v>1309</v>
       </c>
       <c r="I62" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J62" t="b">
         <v>1</v>
       </c>
       <c r="K62" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="L62" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="M62">
         <v>65</v>
@@ -10601,7 +10679,7 @@
         <v>6.48716667</v>
       </c>
       <c r="AE62" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF62">
         <v>-0.0125</v>
@@ -10654,10 +10732,10 @@
     </row>
     <row r="63" spans="1:47">
       <c r="A63" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B63" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C63" s="2">
         <v>45416.29992278935</v>
@@ -10678,16 +10756,16 @@
         <v>1320</v>
       </c>
       <c r="I63" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J63" t="b">
         <v>1</v>
       </c>
       <c r="K63" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="L63" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="M63">
         <v>90</v>
@@ -10744,7 +10822,7 @@
         <v>5.44566667</v>
       </c>
       <c r="AE63" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF63">
         <v>-0.113889</v>
@@ -10797,10 +10875,10 @@
     </row>
     <row r="64" spans="1:47">
       <c r="A64" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C64" s="2">
         <v>45416.30029982639</v>
@@ -10821,16 +10899,16 @@
         <v>1350</v>
       </c>
       <c r="I64" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J64" t="b">
         <v>1</v>
       </c>
       <c r="K64" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="L64" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="M64">
         <v>83</v>
@@ -10887,7 +10965,7 @@
         <v>6.75633333</v>
       </c>
       <c r="AE64" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF64">
         <v>0.143333</v>
@@ -10940,10 +11018,10 @@
     </row>
     <row r="65" spans="1:48">
       <c r="A65" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B65" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C65" s="2">
         <v>45416.30061722222</v>
@@ -10964,16 +11042,16 @@
         <v>1380</v>
       </c>
       <c r="I65" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J65" t="b">
         <v>1</v>
       </c>
       <c r="K65" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="L65" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="M65">
         <v>80</v>
@@ -11030,7 +11108,7 @@
         <v>5.15133333</v>
       </c>
       <c r="AE65" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF65">
         <v>-0.175556</v>
@@ -11083,10 +11161,10 @@
     </row>
     <row r="66" spans="1:48">
       <c r="A66" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B66" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C66" s="2">
         <v>45416.3009994213</v>
@@ -11107,16 +11185,16 @@
         <v>1410</v>
       </c>
       <c r="I66" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J66" t="b">
         <v>1</v>
       </c>
       <c r="K66" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="L66" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="M66">
         <v>78</v>
@@ -11173,7 +11251,7 @@
         <v>4.80566667</v>
       </c>
       <c r="AE66" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF66">
         <v>-0.037778</v>
@@ -11226,10 +11304,10 @@
     </row>
     <row r="67" spans="1:48">
       <c r="A67" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C67" s="2">
         <v>45416.30131277778</v>
@@ -11250,16 +11328,16 @@
         <v>1440</v>
       </c>
       <c r="I67" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J67" t="b">
         <v>1</v>
       </c>
       <c r="K67" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="L67" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="M67">
         <v>61</v>
@@ -11316,7 +11394,7 @@
         <v>4.98833333</v>
       </c>
       <c r="AE67" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF67">
         <v>0.02</v>
@@ -11369,10 +11447,10 @@
     </row>
     <row r="68" spans="1:48">
       <c r="A68" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C68" s="2">
         <v>45416.3020066551</v>
@@ -11393,16 +11471,16 @@
         <v>1500</v>
       </c>
       <c r="I68" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J68" t="b">
         <v>1</v>
       </c>
       <c r="K68" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="L68" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="M68">
         <v>69</v>
@@ -11459,7 +11537,7 @@
         <v>5.13083333</v>
       </c>
       <c r="AE68" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF68">
         <v>0.007778</v>
@@ -11512,10 +11590,10 @@
     </row>
     <row r="69" spans="1:48">
       <c r="A69" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B69" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C69" s="2">
         <v>45416.30270140046</v>
@@ -11536,16 +11614,16 @@
         <v>1560</v>
       </c>
       <c r="I69" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J69" t="b">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="L69" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="M69">
         <v>60</v>
@@ -11602,7 +11680,7 @@
         <v>5.54233333</v>
       </c>
       <c r="AE69" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF69">
         <v>0.0225</v>
@@ -11653,15 +11731,15 @@
         <v>6.141126</v>
       </c>
       <c r="AV69" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="70" spans="1:48">
       <c r="A70" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B70" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C70" s="2">
         <v>45416.30339539352</v>
@@ -11682,16 +11760,16 @@
         <v>1620</v>
       </c>
       <c r="I70" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J70" t="b">
         <v>1</v>
       </c>
       <c r="K70" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="L70" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="M70">
         <v>82</v>
@@ -11748,7 +11826,7 @@
         <v>6.24833333</v>
       </c>
       <c r="AE70" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF70">
         <v>0.038611</v>
@@ -11801,10 +11879,10 @@
     </row>
     <row r="71" spans="1:48">
       <c r="A71" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C71" s="2">
         <v>45416.3036171412</v>
@@ -11825,16 +11903,16 @@
         <v>1639</v>
       </c>
       <c r="I71" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J71" t="b">
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L71" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="M71">
         <v>71</v>
@@ -11891,7 +11969,7 @@
         <v>5.65081818</v>
       </c>
       <c r="AE71" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF71">
         <v>-0.005941</v>
@@ -11944,10 +12022,10 @@
     </row>
     <row r="72" spans="1:48">
       <c r="A72" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B72" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C72" s="2">
         <v>45416.30399307871</v>
@@ -11968,16 +12046,16 @@
         <v>1669</v>
       </c>
       <c r="I72" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J72" t="b">
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>165</v>
+        <v>175</v>
       </c>
       <c r="L72" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="M72">
         <v>76</v>
@@ -12034,7 +12112,7 @@
         <v>6.46166667</v>
       </c>
       <c r="AE72" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF72">
         <v>0.088687</v>
@@ -12087,10 +12165,10 @@
     </row>
     <row r="73" spans="1:48">
       <c r="A73" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C73" s="2">
         <v>45416.30408978009</v>
@@ -12111,16 +12189,16 @@
         <v>1680</v>
       </c>
       <c r="I73" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J73" t="b">
         <v>1</v>
       </c>
       <c r="K73" t="s">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="L73" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="M73">
         <v>91</v>
@@ -12177,7 +12255,7 @@
         <v>6.731</v>
       </c>
       <c r="AE73" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF73">
         <v>0.014722</v>
@@ -12230,10 +12308,10 @@
     </row>
     <row r="74" spans="1:48">
       <c r="A74" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C74" s="2">
         <v>45416.30478475695</v>
@@ -12254,16 +12332,16 @@
         <v>1740</v>
       </c>
       <c r="I74" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J74" t="b">
         <v>1</v>
       </c>
       <c r="K74" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="L74" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="M74">
         <v>70</v>
@@ -12320,7 +12398,7 @@
         <v>5.60333333</v>
       </c>
       <c r="AE74" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF74">
         <v>-0.061667</v>
@@ -12373,10 +12451,10 @@
     </row>
     <row r="75" spans="1:48">
       <c r="A75" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C75" s="2">
         <v>45416.30538291667</v>
@@ -12397,16 +12475,16 @@
         <v>1789</v>
       </c>
       <c r="I75" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J75" t="b">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="L75" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="M75">
         <v>66</v>
@@ -12463,7 +12541,7 @@
         <v>5.56766667</v>
       </c>
       <c r="AE75" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF75">
         <v>-0.000972</v>
@@ -12516,10 +12594,10 @@
     </row>
     <row r="76" spans="1:48">
       <c r="A76" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B76" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C76" s="2">
         <v>45416.30547902777</v>
@@ -12540,16 +12618,16 @@
         <v>1800</v>
       </c>
       <c r="I76" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J76" t="b">
         <v>1</v>
       </c>
       <c r="K76" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="L76" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="M76">
         <v>79</v>
@@ -12606,7 +12684,7 @@
         <v>5.50666667</v>
       </c>
       <c r="AE76" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF76">
         <v>-0.003333</v>
@@ -12659,10 +12737,10 @@
     </row>
     <row r="77" spans="1:48">
       <c r="A77" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B77" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C77" s="2">
         <v>45416.30617460649</v>
@@ -12683,16 +12761,16 @@
         <v>1860</v>
       </c>
       <c r="I77" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J77" t="b">
         <v>1</v>
       </c>
       <c r="K77" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="L77" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="M77">
         <v>79</v>
@@ -12749,7 +12827,7 @@
         <v>6.736</v>
       </c>
       <c r="AE77" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF77">
         <v>0.067222</v>
@@ -12802,10 +12880,10 @@
     </row>
     <row r="78" spans="1:48">
       <c r="A78" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B78" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C78" s="2">
         <v>45416.30654905093</v>
@@ -12826,16 +12904,16 @@
         <v>1890</v>
       </c>
       <c r="I78" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J78" t="b">
         <v>1</v>
       </c>
       <c r="K78" t="s">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="L78" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="M78">
         <v>88</v>
@@ -12892,7 +12970,7 @@
         <v>6.096</v>
       </c>
       <c r="AE78" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF78">
         <v>-0.07000000000000001</v>
@@ -12945,10 +13023,10 @@
     </row>
     <row r="79" spans="1:48">
       <c r="A79" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C79" s="2">
         <v>45416.30677236111</v>
@@ -12969,16 +13047,16 @@
         <v>1909</v>
       </c>
       <c r="I79" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J79" t="b">
         <v>1</v>
       </c>
       <c r="K79" t="s">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="L79" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M79">
         <v>65</v>
@@ -13035,7 +13113,7 @@
         <v>6.505</v>
       </c>
       <c r="AE79" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF79">
         <v>0.011181</v>
@@ -13088,10 +13166,10 @@
     </row>
     <row r="80" spans="1:48">
       <c r="A80" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B80" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C80" s="2">
         <v>45416.30686834491</v>
@@ -13112,16 +13190,16 @@
         <v>1920</v>
       </c>
       <c r="I80" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J80" t="b">
         <v>1</v>
       </c>
       <c r="K80" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="L80" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="M80">
         <v>58</v>
@@ -13178,7 +13256,7 @@
         <v>6.31966667</v>
       </c>
       <c r="AE80" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF80">
         <v>-0.020278</v>
@@ -13231,10 +13309,10 @@
     </row>
     <row r="81" spans="1:47">
       <c r="A81" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C81" s="2">
         <v>45416.30709079861</v>
@@ -13255,16 +13333,16 @@
         <v>1939</v>
       </c>
       <c r="I81" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J81" t="b">
         <v>1</v>
       </c>
       <c r="K81" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="L81" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="M81">
         <v>73</v>
@@ -13321,7 +13399,7 @@
         <v>6.47166667</v>
       </c>
       <c r="AE81" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF81">
         <v>0.016667</v>
@@ -13374,10 +13452,10 @@
     </row>
     <row r="82" spans="1:47">
       <c r="A82" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C82" s="2">
         <v>45416.30724446759</v>
@@ -13398,16 +13476,16 @@
         <v>1950</v>
       </c>
       <c r="I82" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J82" t="b">
         <v>1</v>
       </c>
       <c r="K82" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="L82" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
       <c r="M82">
         <v>76</v>
@@ -13464,7 +13542,7 @@
         <v>6.77666667</v>
       </c>
       <c r="AE82" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF82">
         <v>0.033333</v>
@@ -13517,10 +13595,10 @@
     </row>
     <row r="83" spans="1:47">
       <c r="A83" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B83" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C83" s="2">
         <v>45416.30746599537</v>
@@ -13541,16 +13619,16 @@
         <v>1969</v>
       </c>
       <c r="I83" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J83" t="b">
         <v>1</v>
       </c>
       <c r="K83" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="L83" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="M83">
         <v>78</v>
@@ -13607,7 +13685,7 @@
         <v>6.16733333</v>
       </c>
       <c r="AE83" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF83">
         <v>-0.066667</v>
@@ -13660,10 +13738,10 @@
     </row>
     <row r="84" spans="1:47">
       <c r="A84" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B84" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C84" s="2">
         <v>45416.3075621875</v>
@@ -13684,16 +13762,16 @@
         <v>1980</v>
       </c>
       <c r="I84" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J84" t="b">
         <v>1</v>
       </c>
       <c r="K84" t="s">
-        <v>177</v>
+        <v>187</v>
       </c>
       <c r="L84" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="M84">
         <v>69</v>
@@ -13750,7 +13828,7 @@
         <v>6.482</v>
       </c>
       <c r="AE84" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF84">
         <v>0.034444</v>
@@ -13803,10 +13881,10 @@
     </row>
     <row r="85" spans="1:47">
       <c r="A85" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B85" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C85" s="2">
         <v>45416.30825726852</v>
@@ -13827,16 +13905,16 @@
         <v>2040</v>
       </c>
       <c r="I85" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J85" t="b">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="L85" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="M85">
         <v>68</v>
@@ -13893,7 +13971,7 @@
         <v>6.27383333</v>
       </c>
       <c r="AE85" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF85">
         <v>-0.011389</v>
@@ -13946,10 +14024,10 @@
     </row>
     <row r="86" spans="1:47">
       <c r="A86" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C86" s="2">
         <v>45416.30863371528</v>
@@ -13970,16 +14048,16 @@
         <v>2070</v>
       </c>
       <c r="I86" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J86" t="b">
         <v>1</v>
       </c>
       <c r="K86" t="s">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="L86" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="M86">
         <v>80</v>
@@ -14036,7 +14114,7 @@
         <v>5.639</v>
       </c>
       <c r="AE86" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF86">
         <v>-0.06944400000000001</v>
@@ -14089,10 +14167,10 @@
     </row>
     <row r="87" spans="1:47">
       <c r="A87" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B87" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C87" s="2">
         <v>45416.30895127315</v>
@@ -14113,16 +14191,16 @@
         <v>2100</v>
       </c>
       <c r="I87" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J87" t="b">
         <v>1</v>
       </c>
       <c r="K87" t="s">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="L87" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="M87">
         <v>73</v>
@@ -14179,7 +14257,7 @@
         <v>6.39033333</v>
       </c>
       <c r="AE87" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF87">
         <v>0.082222</v>
@@ -14232,10 +14310,10 @@
     </row>
     <row r="88" spans="1:47">
       <c r="A88" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C88" s="2">
         <v>45416.30955096065</v>
@@ -14256,16 +14334,16 @@
         <v>2149</v>
       </c>
       <c r="I88" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J88" t="b">
         <v>1</v>
       </c>
       <c r="K88" t="s">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="L88" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="M88">
         <v>75</v>
@@ -14322,7 +14400,7 @@
         <v>6.04177778</v>
       </c>
       <c r="AE88" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF88">
         <v>-0.006358</v>
@@ -14375,10 +14453,10 @@
     </row>
     <row r="89" spans="1:47">
       <c r="A89" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B89" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C89" s="2">
         <v>45416.30964634259</v>
@@ -14399,16 +14477,16 @@
         <v>2160</v>
       </c>
       <c r="I89" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J89" t="b">
         <v>1</v>
       </c>
       <c r="K89" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L89" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="M89">
         <v>80</v>
@@ -14465,7 +14543,7 @@
         <v>5.44083333</v>
       </c>
       <c r="AE89" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF89">
         <v>-0.03287</v>
@@ -14518,10 +14596,10 @@
     </row>
     <row r="90" spans="1:47">
       <c r="A90" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B90" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C90" s="2">
         <v>45416.31002208334</v>
@@ -14542,16 +14620,16 @@
         <v>2190</v>
       </c>
       <c r="I90" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J90" t="b">
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="L90" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="M90">
         <v>50</v>
@@ -14608,7 +14686,7 @@
         <v>5.842</v>
       </c>
       <c r="AE90" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF90">
         <v>0.043889</v>
@@ -14661,10 +14739,10 @@
     </row>
     <row r="91" spans="1:47">
       <c r="A91" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B91" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C91" s="2">
         <v>45416.31036405093</v>
@@ -14685,16 +14763,16 @@
         <v>2220</v>
       </c>
       <c r="I91" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J91" t="b">
         <v>1</v>
       </c>
       <c r="K91" t="s">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="L91" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="M91">
         <v>77</v>
@@ -14751,7 +14829,7 @@
         <v>5.354</v>
       </c>
       <c r="AE91" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF91">
         <v>-0.053333</v>
@@ -14804,10 +14882,10 @@
     </row>
     <row r="92" spans="1:47">
       <c r="A92" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B92" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C92" s="2">
         <v>45416.31103505787</v>
@@ -14828,16 +14906,16 @@
         <v>2280</v>
       </c>
       <c r="I92" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J92" t="b">
         <v>1</v>
       </c>
       <c r="K92" t="s">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="L92" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="M92">
         <v>75</v>
@@ -14894,7 +14972,7 @@
         <v>5.22733333</v>
       </c>
       <c r="AE92" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF92">
         <v>-0.006944</v>
@@ -14947,10 +15025,10 @@
     </row>
     <row r="93" spans="1:47">
       <c r="A93" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B93" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C93" s="2">
         <v>45416.31125788194</v>
@@ -14971,16 +15049,16 @@
         <v>2299</v>
       </c>
       <c r="I93" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J93" t="b">
         <v>1</v>
       </c>
       <c r="K93" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="L93" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="M93">
         <v>75</v>
@@ -15037,7 +15115,7 @@
         <v>5.3462</v>
       </c>
       <c r="AE93" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF93">
         <v>0.0026</v>
@@ -15090,10 +15168,10 @@
     </row>
     <row r="94" spans="1:47">
       <c r="A94" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B94" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C94" s="2">
         <v>45416.31163385417</v>
@@ -15114,16 +15192,16 @@
         <v>2329</v>
       </c>
       <c r="I94" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J94" t="b">
         <v>1</v>
       </c>
       <c r="K94" t="s">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c r="L94" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
       <c r="M94">
         <v>78</v>
@@ -15180,7 +15258,7 @@
         <v>4.755</v>
       </c>
       <c r="AE94" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF94">
         <v>-0.064667</v>
@@ -15233,10 +15311,10 @@
     </row>
     <row r="95" spans="1:47">
       <c r="A95" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B95" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C95" s="2">
         <v>45416.31173046296</v>
@@ -15257,16 +15335,16 @@
         <v>2340</v>
       </c>
       <c r="I95" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J95" t="b">
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="L95" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="M95">
         <v>102</v>
@@ -15323,7 +15401,7 @@
         <v>4.98866667</v>
       </c>
       <c r="AE95" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF95">
         <v>0.012778</v>
@@ -15376,10 +15454,10 @@
     </row>
     <row r="96" spans="1:47">
       <c r="A96" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B96" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C96" s="2">
         <v>45416.31210621528</v>
@@ -15400,16 +15478,16 @@
         <v>2370</v>
       </c>
       <c r="I96" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J96" t="b">
         <v>1</v>
       </c>
       <c r="K96" t="s">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="L96" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="M96">
         <v>73</v>
@@ -15466,7 +15544,7 @@
         <v>5.49633333</v>
       </c>
       <c r="AE96" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF96">
         <v>0.055556</v>
@@ -15519,10 +15597,10 @@
     </row>
     <row r="97" spans="1:47">
       <c r="A97" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C97" s="2">
         <v>45416.31242394676</v>
@@ -15543,16 +15621,16 @@
         <v>2400</v>
       </c>
       <c r="I97" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J97" t="b">
         <v>1</v>
       </c>
       <c r="K97" t="s">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="L97" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="M97">
         <v>63</v>
@@ -15609,7 +15687,7 @@
         <v>5.52733333</v>
       </c>
       <c r="AE97" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF97">
         <v>0.003333</v>
@@ -15662,10 +15740,10 @@
     </row>
     <row r="98" spans="1:47">
       <c r="A98" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B98" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C98" s="2">
         <v>45416.31311875</v>
@@ -15686,16 +15764,16 @@
         <v>2460</v>
       </c>
       <c r="I98" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J98" t="b">
         <v>1</v>
       </c>
       <c r="K98" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="L98" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="M98">
         <v>82</v>
@@ -15752,7 +15830,7 @@
         <v>5.7505</v>
       </c>
       <c r="AE98" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF98">
         <v>0.012222</v>
@@ -15805,10 +15883,10 @@
     </row>
     <row r="99" spans="1:47">
       <c r="A99" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B99" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C99" s="2">
         <v>45416.31349582176</v>
@@ -15829,16 +15907,16 @@
         <v>2490</v>
       </c>
       <c r="I99" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J99" t="b">
         <v>1</v>
       </c>
       <c r="K99" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="L99" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="M99">
         <v>56</v>
@@ -15895,7 +15973,7 @@
         <v>5.60833333</v>
       </c>
       <c r="AE99" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF99">
         <v>-0.015556</v>
@@ -15948,10 +16026,10 @@
     </row>
     <row r="100" spans="1:47">
       <c r="A100" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B100" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C100" s="2">
         <v>45416.31441143518</v>
@@ -15972,16 +16050,16 @@
         <v>2569</v>
       </c>
       <c r="I100" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J100" t="b">
         <v>1</v>
       </c>
       <c r="K100" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="L100" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
       <c r="M100">
         <v>78</v>
@@ -16038,7 +16116,7 @@
         <v>5.579125</v>
       </c>
       <c r="AE100" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF100">
         <v>-0.000399</v>
@@ -16091,10 +16169,10 @@
     </row>
     <row r="101" spans="1:47">
       <c r="A101" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B101" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C101" s="2">
         <v>45416.31450773148</v>
@@ -16115,16 +16193,16 @@
         <v>2580</v>
       </c>
       <c r="I101" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J101" t="b">
         <v>1</v>
       </c>
       <c r="K101" t="s">
-        <v>194</v>
+        <v>204</v>
       </c>
       <c r="L101" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="M101">
         <v>84</v>
@@ -16181,7 +16259,7 @@
         <v>5.41522222</v>
       </c>
       <c r="AE101" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF101">
         <v>-0.005972</v>
@@ -16234,10 +16312,10 @@
     </row>
     <row r="102" spans="1:47">
       <c r="A102" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B102" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C102" s="2">
         <v>45416.31520199074</v>
@@ -16258,16 +16336,16 @@
         <v>2640</v>
       </c>
       <c r="I102" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J102" t="b">
         <v>1</v>
       </c>
       <c r="K102" t="s">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="L102" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="M102">
         <v>63</v>
@@ -16324,7 +16402,7 @@
         <v>5.71</v>
       </c>
       <c r="AE102" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF102">
         <v>0.016111</v>
@@ -16377,10 +16455,10 @@
     </row>
     <row r="103" spans="1:47">
       <c r="A103" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B103" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C103" s="2">
         <v>45416.31557868056</v>
@@ -16401,16 +16479,16 @@
         <v>2670</v>
       </c>
       <c r="I103" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J103" t="b">
         <v>1</v>
       </c>
       <c r="K103" t="s">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="L103" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="M103">
         <v>36</v>
@@ -16467,7 +16545,7 @@
         <v>7.14233333</v>
       </c>
       <c r="AE103" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF103">
         <v>0.156667</v>
@@ -16520,10 +16598,10 @@
     </row>
     <row r="104" spans="1:47">
       <c r="A104" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B104" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C104" s="2">
         <v>45416.31589615741</v>
@@ -16544,16 +16622,16 @@
         <v>2700</v>
       </c>
       <c r="I104" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J104" t="b">
         <v>1</v>
       </c>
       <c r="K104" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="L104" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="M104">
         <v>77</v>
@@ -16610,7 +16688,7 @@
         <v>7.173</v>
       </c>
       <c r="AE104" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF104">
         <v>0.003333</v>
@@ -16663,10 +16741,10 @@
     </row>
     <row r="105" spans="1:47">
       <c r="A105" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B105" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C105" s="2">
         <v>45416.31649530093</v>
@@ -16687,16 +16765,16 @@
         <v>2749</v>
       </c>
       <c r="I105" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J105" t="b">
         <v>1</v>
       </c>
       <c r="K105" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="L105" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="M105">
         <v>24</v>
@@ -16753,7 +16831,7 @@
         <v>6.65138889</v>
       </c>
       <c r="AE105" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF105">
         <v>-0.009506000000000001</v>
@@ -16806,10 +16884,10 @@
     </row>
     <row r="106" spans="1:47">
       <c r="A106" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B106" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C106" s="2">
         <v>45416.31719040509</v>
@@ -16830,16 +16908,16 @@
         <v>2809</v>
       </c>
       <c r="I106" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J106" t="b">
         <v>1</v>
       </c>
       <c r="K106" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="L106" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="M106">
         <v>49</v>
@@ -16896,7 +16974,7 @@
         <v>6.13666667</v>
       </c>
       <c r="AE106" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF106">
         <v>-0.028148</v>
@@ -16949,10 +17027,10 @@
     </row>
     <row r="107" spans="1:47">
       <c r="A107" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B107" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C107" s="2">
         <v>45416.31728564815</v>
@@ -16973,16 +17051,16 @@
         <v>2820</v>
       </c>
       <c r="I107" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J107" t="b">
         <v>1</v>
       </c>
       <c r="K107" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="L107" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="M107">
         <v>25</v>
@@ -17039,7 +17117,7 @@
         <v>6.64208333</v>
       </c>
       <c r="AE107" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF107">
         <v>0.013819</v>
@@ -17092,10 +17170,10 @@
     </row>
     <row r="108" spans="1:47">
       <c r="A108" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B108" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C108" s="2">
         <v>45416.31750855324</v>
@@ -17116,16 +17194,16 @@
         <v>2839</v>
       </c>
       <c r="I108" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J108" t="b">
         <v>1</v>
       </c>
       <c r="K108" t="s">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="L108" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="M108">
         <v>54</v>
@@ -17182,7 +17260,7 @@
         <v>5.68966667</v>
       </c>
       <c r="AE108" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF108">
         <v>-0.104167</v>
@@ -17235,10 +17313,10 @@
     </row>
     <row r="109" spans="1:47">
       <c r="A109" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B109" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C109" s="2">
         <v>45416.31797965278</v>
@@ -17259,16 +17337,16 @@
         <v>2880</v>
       </c>
       <c r="I109" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J109" t="b">
         <v>1</v>
       </c>
       <c r="K109" t="s">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="L109" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="M109">
         <v>88</v>
@@ -17325,7 +17403,7 @@
         <v>5.588</v>
       </c>
       <c r="AE109" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF109">
         <v>-0.005556</v>
@@ -17378,10 +17456,10 @@
     </row>
     <row r="110" spans="1:47">
       <c r="A110" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B110" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C110" s="2">
         <v>45416.31835606482</v>
@@ -17402,16 +17480,16 @@
         <v>2910</v>
       </c>
       <c r="I110" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J110" t="b">
         <v>1</v>
       </c>
       <c r="K110" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="L110" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="M110">
         <v>112</v>
@@ -17468,7 +17546,7 @@
         <v>5.40533333</v>
       </c>
       <c r="AE110" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF110">
         <v>-0.02</v>
@@ -17521,10 +17599,10 @@
     </row>
     <row r="111" spans="1:47">
       <c r="A111" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B111" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C111" s="2">
         <v>45416.31867484954</v>
@@ -17545,16 +17623,16 @@
         <v>2940</v>
       </c>
       <c r="I111" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J111" t="b">
         <v>1</v>
       </c>
       <c r="K111" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="L111" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="M111">
         <v>193</v>
@@ -17611,7 +17689,7 @@
         <v>6.01466667</v>
       </c>
       <c r="AE111" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF111">
         <v>0.066667</v>
@@ -17664,10 +17742,10 @@
     </row>
     <row r="112" spans="1:47">
       <c r="A112" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B112" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C112" s="2">
         <v>45416.31936898148</v>
@@ -17688,16 +17766,16 @@
         <v>3000</v>
       </c>
       <c r="I112" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J112" t="b">
         <v>1</v>
       </c>
       <c r="K112" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="L112" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="M112">
         <v>47</v>
@@ -17754,7 +17832,7 @@
         <v>6.92916667</v>
       </c>
       <c r="AE112" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF112">
         <v>0.05</v>
@@ -17807,10 +17885,10 @@
     </row>
     <row r="113" spans="1:48">
       <c r="A113" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B113" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C113" s="2">
         <v>45416.31958745371</v>
@@ -17831,16 +17909,16 @@
         <v>3019</v>
       </c>
       <c r="I113" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J113" t="b">
         <v>1</v>
       </c>
       <c r="K113" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="L113" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="M113">
         <v>41</v>
@@ -17897,7 +17975,7 @@
         <v>6.02822222</v>
       </c>
       <c r="AE113" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF113">
         <v>-0.01642</v>
@@ -17950,10 +18028,10 @@
     </row>
     <row r="114" spans="1:48">
       <c r="A114" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B114" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C114" s="2">
         <v>45416.32065864583</v>
@@ -17974,16 +18052,16 @@
         <v>3109</v>
       </c>
       <c r="I114" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J114" t="b">
         <v>1</v>
       </c>
       <c r="K114" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="L114" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="M114">
         <v>122</v>
@@ -18040,7 +18118,7 @@
         <v>5.94022222</v>
       </c>
       <c r="AE114" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF114">
         <v>-0.00321</v>
@@ -18093,10 +18171,10 @@
     </row>
     <row r="115" spans="1:48">
       <c r="A115" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B115" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C115" s="2">
         <v>45416.3207590625</v>
@@ -18117,16 +18195,16 @@
         <v>3120</v>
       </c>
       <c r="I115" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J115" t="b">
         <v>1</v>
       </c>
       <c r="K115" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="L115" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="M115">
         <v>300</v>
@@ -18183,7 +18261,7 @@
         <v>5.908</v>
       </c>
       <c r="AE115" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF115">
         <v>-0.00088</v>
@@ -18236,10 +18314,10 @@
     </row>
     <row r="116" spans="1:48">
       <c r="A116" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B116" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C116" s="2">
         <v>45416.32097695602</v>
@@ -18260,16 +18338,16 @@
         <v>3139</v>
       </c>
       <c r="I116" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J116" t="b">
         <v>1</v>
       </c>
       <c r="K116" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="L116" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="M116">
         <v>164</v>
@@ -18326,7 +18404,7 @@
         <v>6.39066667</v>
       </c>
       <c r="AE116" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="AF116">
         <v>0.052778</v>
@@ -18379,10 +18457,10 @@
     </row>
     <row r="117" spans="1:48">
       <c r="A117" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B117" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C117" s="2">
         <v>45416.3214525463</v>
@@ -18403,16 +18481,16 @@
         <v>3180</v>
       </c>
       <c r="I117" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J117" t="b">
         <v>1</v>
       </c>
       <c r="K117" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="L117" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="M117">
         <v>112</v>
@@ -18469,7 +18547,7 @@
         <v>6.58366667</v>
       </c>
       <c r="AE117" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF117">
         <v>0.010556</v>
@@ -18520,15 +18598,15 @@
         <v>5.878024</v>
       </c>
       <c r="AV117" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
     </row>
     <row r="118" spans="1:48">
       <c r="A118" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B118" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C118" s="2">
         <v>45416.32182875</v>
@@ -18549,16 +18627,16 @@
         <v>3210</v>
       </c>
       <c r="I118" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J118" t="b">
         <v>1</v>
       </c>
       <c r="K118" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
       <c r="L118" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="M118">
         <v>191</v>
@@ -18615,7 +18693,7 @@
         <v>5.43566667</v>
       </c>
       <c r="AE118" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF118">
         <v>-0.125556</v>
@@ -18668,10 +18746,10 @@
     </row>
     <row r="119" spans="1:48">
       <c r="A119" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B119" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C119" s="2">
         <v>45416.32204784722</v>
@@ -18692,16 +18770,16 @@
         <v>3229</v>
       </c>
       <c r="I119" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J119" t="b">
         <v>1</v>
       </c>
       <c r="K119" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="L119" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="M119">
         <v>28</v>
@@ -18758,7 +18836,7 @@
         <v>6.02833333</v>
       </c>
       <c r="AE119" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF119">
         <v>0.021605</v>
@@ -18811,10 +18889,10 @@
     </row>
     <row r="120" spans="1:48">
       <c r="A120" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B120" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C120" s="2">
         <v>45416.32214707176</v>
@@ -18835,16 +18913,16 @@
         <v>3240</v>
       </c>
       <c r="I120" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J120" t="b">
         <v>1</v>
       </c>
       <c r="K120" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="L120" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="M120">
         <v>321</v>
@@ -18901,7 +18979,7 @@
         <v>5.588</v>
       </c>
       <c r="AE120" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF120">
         <v>-0.048148</v>
@@ -18954,10 +19032,10 @@
     </row>
     <row r="121" spans="1:48">
       <c r="A121" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B121" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C121" s="2">
         <v>45416.32284148148</v>
@@ -18978,16 +19056,16 @@
         <v>3300</v>
       </c>
       <c r="I121" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J121" t="b">
         <v>1</v>
       </c>
       <c r="K121" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="L121" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="M121">
         <v>24</v>
@@ -19044,7 +19122,7 @@
         <v>5.03933333</v>
       </c>
       <c r="AE121" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF121">
         <v>-0.03</v>
@@ -19097,10 +19175,10 @@
     </row>
     <row r="122" spans="1:48">
       <c r="A122" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B122" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C122" s="2">
         <v>45416.32353576389</v>
@@ -19121,16 +19199,16 @@
         <v>3360</v>
       </c>
       <c r="I122" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J122" t="b">
         <v>1</v>
       </c>
       <c r="K122" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="L122" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="M122">
         <v>88</v>
@@ -19187,7 +19265,7 @@
         <v>5.456</v>
       </c>
       <c r="AE122" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF122">
         <v>0.022778</v>
@@ -19240,10 +19318,10 @@
     </row>
     <row r="123" spans="1:48">
       <c r="A123" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B123" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C123" s="2">
         <v>45416.32423038194</v>
@@ -19264,16 +19342,16 @@
         <v>3420</v>
       </c>
       <c r="I123" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J123" t="b">
         <v>1</v>
       </c>
       <c r="K123" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="L123" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="M123">
         <v>221</v>
@@ -19330,7 +19408,7 @@
         <v>5.781</v>
       </c>
       <c r="AE123" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF123">
         <v>0.017778</v>
@@ -19383,10 +19461,10 @@
     </row>
     <row r="124" spans="1:48">
       <c r="A124" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B124" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C124" s="2">
         <v>45416.32492571759</v>
@@ -19407,16 +19485,16 @@
         <v>3480</v>
       </c>
       <c r="I124" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J124" t="b">
         <v>1</v>
       </c>
       <c r="K124" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="L124" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="M124">
         <v>289</v>
@@ -19473,7 +19551,7 @@
         <v>5.6795</v>
       </c>
       <c r="AE124" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF124">
         <v>-0.005556</v>
@@ -19526,10 +19604,10 @@
     </row>
     <row r="125" spans="1:48">
       <c r="A125" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B125" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C125" s="2">
         <v>45416.32561967592</v>
@@ -19550,16 +19628,16 @@
         <v>3540</v>
       </c>
       <c r="I125" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J125" t="b">
         <v>1</v>
       </c>
       <c r="K125" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="L125" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="M125">
         <v>341</v>
@@ -19616,7 +19694,7 @@
         <v>5.66416667</v>
       </c>
       <c r="AE125" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF125">
         <v>-0.000833</v>
@@ -19669,10 +19747,10 @@
     </row>
     <row r="126" spans="1:48">
       <c r="A126" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B126" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C126" s="2">
         <v>45416.32631473379</v>
@@ -19693,16 +19771,16 @@
         <v>3600</v>
       </c>
       <c r="I126" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J126" t="b">
         <v>1</v>
       </c>
       <c r="K126" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="L126" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="M126">
         <v>203</v>
@@ -19759,7 +19837,7 @@
         <v>5.47616667</v>
       </c>
       <c r="AE126" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF126">
         <v>-0.010278</v>
@@ -19812,10 +19890,10 @@
     </row>
     <row r="127" spans="1:48">
       <c r="A127" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B127" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C127" s="2">
         <v>45416.32669028935</v>
@@ -19836,16 +19914,16 @@
         <v>3630</v>
       </c>
       <c r="I127" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J127" t="b">
         <v>1</v>
       </c>
       <c r="K127" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="L127" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="M127">
         <v>293</v>
@@ -19902,7 +19980,7 @@
         <v>5.588</v>
       </c>
       <c r="AE127" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF127">
         <v>0.012222</v>
@@ -19955,10 +20033,10 @@
     </row>
     <row r="128" spans="1:48">
       <c r="A128" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B128" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C128" s="2">
         <v>45416.32700880787</v>
@@ -19979,16 +20057,16 @@
         <v>3660</v>
       </c>
       <c r="I128" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J128" t="b">
         <v>1</v>
       </c>
       <c r="K128" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="L128" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="M128">
         <v>216</v>
@@ -20045,7 +20123,7 @@
         <v>5.771</v>
       </c>
       <c r="AE128" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF128">
         <v>0.02</v>
@@ -20098,10 +20176,10 @@
     </row>
     <row r="129" spans="1:47">
       <c r="A129" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B129" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C129" s="2">
         <v>45416.32770253472</v>
@@ -20122,16 +20200,16 @@
         <v>3720</v>
       </c>
       <c r="I129" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J129" t="b">
         <v>1</v>
       </c>
       <c r="K129" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="L129" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="M129">
         <v>47</v>
@@ -20188,7 +20266,7 @@
         <v>5.69466667</v>
       </c>
       <c r="AE129" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF129">
         <v>-0.004167</v>
@@ -20241,10 +20319,10 @@
     </row>
     <row r="130" spans="1:47">
       <c r="A130" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B130" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C130" s="2">
         <v>45416.3279222338</v>
@@ -20265,16 +20343,16 @@
         <v>3739</v>
       </c>
       <c r="I130" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J130" t="b">
         <v>1</v>
       </c>
       <c r="K130" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="L130" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="M130">
         <v>353</v>
@@ -20331,7 +20409,7 @@
         <v>5.57545098</v>
       </c>
       <c r="AE130" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF130">
         <v>-0.000767</v>
@@ -20384,10 +20462,10 @@
     </row>
     <row r="131" spans="1:47">
       <c r="A131" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B131" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C131" s="2">
         <v>45416.32807935185</v>
@@ -20408,16 +20486,16 @@
         <v>3750</v>
       </c>
       <c r="I131" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J131" t="b">
         <v>1</v>
       </c>
       <c r="K131" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="L131" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="M131">
         <v>5</v>
@@ -20474,7 +20552,7 @@
         <v>5.781</v>
       </c>
       <c r="AE131" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF131">
         <v>0.022484</v>
@@ -20527,10 +20605,10 @@
     </row>
     <row r="132" spans="1:47">
       <c r="A132" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B132" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C132" s="2">
         <v>45416.32909188658</v>
@@ -20551,16 +20629,16 @@
         <v>3840</v>
       </c>
       <c r="I132" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J132" t="b">
         <v>1</v>
       </c>
       <c r="K132" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="L132" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="M132">
         <v>303</v>
@@ -20617,7 +20695,7 @@
         <v>5.83522222</v>
       </c>
       <c r="AE132" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF132">
         <v>0.001975</v>
@@ -20670,10 +20748,10 @@
     </row>
     <row r="133" spans="1:47">
       <c r="A133" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B133" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C133" s="2">
         <v>45416.32978655092</v>
@@ -20694,16 +20772,16 @@
         <v>3900</v>
       </c>
       <c r="I133" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J133" t="b">
         <v>1</v>
       </c>
       <c r="K133" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="L133" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="M133">
         <v>3</v>
@@ -20760,7 +20838,7 @@
         <v>5.654</v>
       </c>
       <c r="AE133" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF133">
         <v>-0.009906999999999999</v>
@@ -20813,10 +20891,10 @@
     </row>
     <row r="134" spans="1:47">
       <c r="A134" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B134" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C134" s="2">
         <v>45416.33048126158</v>
@@ -20837,16 +20915,16 @@
         <v>3960</v>
       </c>
       <c r="I134" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J134" t="b">
         <v>1</v>
       </c>
       <c r="K134" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="L134" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="M134">
         <v>102</v>
@@ -20903,7 +20981,7 @@
         <v>5.40016667</v>
       </c>
       <c r="AE134" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF134">
         <v>-0.013889</v>
@@ -20956,10 +21034,10 @@
     </row>
     <row r="135" spans="1:47">
       <c r="A135" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B135" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C135" s="2">
         <v>45416.33117584491</v>
@@ -20980,16 +21058,16 @@
         <v>4020</v>
       </c>
       <c r="I135" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J135" t="b">
         <v>1</v>
       </c>
       <c r="K135" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="L135" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
       <c r="M135">
         <v>159</v>
@@ -21046,7 +21124,7 @@
         <v>5.6285</v>
       </c>
       <c r="AE135" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF135">
         <v>0.0125</v>
@@ -21099,10 +21177,10 @@
     </row>
     <row r="136" spans="1:47">
       <c r="A136" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B136" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C136" s="2">
         <v>45416.33187099537</v>
@@ -21123,16 +21201,16 @@
         <v>4080</v>
       </c>
       <c r="I136" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J136" t="b">
         <v>1</v>
       </c>
       <c r="K136" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="L136" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="M136">
         <v>48</v>
@@ -21189,7 +21267,7 @@
         <v>5.771</v>
       </c>
       <c r="AE136" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF136">
         <v>0.007778</v>
@@ -21242,10 +21320,10 @@
     </row>
     <row r="137" spans="1:47">
       <c r="A137" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B137" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C137" s="2">
         <v>45416.33256486111</v>
@@ -21266,16 +21344,16 @@
         <v>4140</v>
       </c>
       <c r="I137" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J137" t="b">
         <v>1</v>
       </c>
       <c r="K137" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="L137" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="M137">
         <v>104</v>
@@ -21332,7 +21410,7 @@
         <v>5.4965</v>
       </c>
       <c r="AE137" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF137">
         <v>-0.015</v>
@@ -21385,10 +21463,10 @@
     </row>
     <row r="138" spans="1:47">
       <c r="A138" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B138" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C138" s="2">
         <v>45416.33325940972</v>
@@ -21409,16 +21487,16 @@
         <v>4200</v>
       </c>
       <c r="I138" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J138" t="b">
         <v>1</v>
       </c>
       <c r="K138" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="L138" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="M138">
         <v>236</v>
@@ -21475,7 +21553,7 @@
         <v>5.35433333</v>
       </c>
       <c r="AE138" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF138">
         <v>-0.007778</v>
@@ -21528,10 +21606,10 @@
     </row>
     <row r="139" spans="1:47">
       <c r="A139" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B139" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C139" s="2">
         <v>45416.33395407407</v>
@@ -21552,16 +21630,16 @@
         <v>4260</v>
       </c>
       <c r="I139" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J139" t="b">
         <v>1</v>
       </c>
       <c r="K139" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="L139" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="M139">
         <v>173</v>
@@ -21618,7 +21696,7 @@
         <v>5.588</v>
       </c>
       <c r="AE139" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF139">
         <v>0.012778</v>
@@ -21671,10 +21749,10 @@
     </row>
     <row r="140" spans="1:47">
       <c r="A140" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B140" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C140" s="2">
         <v>45416.33464820602</v>
@@ -21695,16 +21773,16 @@
         <v>4320</v>
       </c>
       <c r="I140" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J140" t="b">
         <v>1</v>
       </c>
       <c r="K140" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="L140" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="M140">
         <v>135</v>
@@ -21761,7 +21839,7 @@
         <v>5.969</v>
       </c>
       <c r="AE140" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF140">
         <v>0.020833</v>
@@ -21814,10 +21892,10 @@
     </row>
     <row r="141" spans="1:47">
       <c r="A141" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B141" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C141" s="2">
         <v>45416.33534385417</v>
@@ -21838,16 +21916,16 @@
         <v>4380</v>
       </c>
       <c r="I141" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J141" t="b">
         <v>1</v>
       </c>
       <c r="K141" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="L141" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="M141">
         <v>55</v>
@@ -21904,7 +21982,7 @@
         <v>6.1875</v>
       </c>
       <c r="AE141" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF141">
         <v>0.011944</v>
@@ -21957,10 +22035,10 @@
     </row>
     <row r="142" spans="1:47">
       <c r="A142" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B142" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C142" s="2">
         <v>45416.33603737268</v>
@@ -21981,16 +22059,16 @@
         <v>4440</v>
       </c>
       <c r="I142" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="J142" t="b">
         <v>1</v>
       </c>
       <c r="K142" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="L142" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
       <c r="M142">
         <v>36</v>
@@ -22047,7 +22125,7 @@
         <v>5.80133333</v>
       </c>
       <c r="AE142" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="AF142">
         <v>-0.021111</v>
@@ -22110,156 +22188,156 @@
   <sheetData>
     <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="AO1" s="1" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="AP1" s="1" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AQ1" s="1" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:48">
       <c r="A2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C2" s="2">
         <v>45416.3367315625</v>
@@ -22280,16 +22358,16 @@
         <v>0</v>
       </c>
       <c r="I2" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="J2" t="b">
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="L2" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="M2">
         <v>189</v>
@@ -22346,7 +22424,7 @@
         <v>-19.37</v>
       </c>
       <c r="AE2" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="AG2">
         <v>-63.55</v>
@@ -22363,10 +22441,10 @@
     </row>
     <row r="3" spans="1:48">
       <c r="A3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C3" s="2">
         <v>45416.33834126157</v>
@@ -22387,16 +22465,16 @@
         <v>139</v>
       </c>
       <c r="I3" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="J3" t="b">
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="L3" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="M3">
         <v>278</v>
@@ -22453,7 +22531,7 @@
         <v>-0.76708889</v>
       </c>
       <c r="AE3" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="AF3">
         <v>0.067815</v>
@@ -22494,10 +22572,10 @@
     </row>
     <row r="4" spans="1:48">
       <c r="A4" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C4" s="2">
         <v>45416.33849724537</v>
@@ -22518,16 +22596,16 @@
         <v>150</v>
       </c>
       <c r="I4" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="J4" t="b">
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="L4" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="M4">
         <v>94</v>
@@ -22584,7 +22662,7 @@
         <v>-25.08713333</v>
       </c>
       <c r="AE4" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="AF4">
         <v>-0.531933</v>
@@ -22637,10 +22715,10 @@
     </row>
     <row r="5" spans="1:48">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C5" s="2">
         <v>45416.33882717592</v>
@@ -22661,16 +22739,16 @@
         <v>180</v>
       </c>
       <c r="I5" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="J5" t="b">
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="L5" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
       <c r="M5">
         <v>314</v>
@@ -22727,7 +22805,7 @@
         <v>-21.17333333</v>
       </c>
       <c r="AE5" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="AF5">
         <v>0.428</v>
@@ -22780,10 +22858,10 @@
     </row>
     <row r="6" spans="1:48">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C6" s="2">
         <v>45416.33919136574</v>
@@ -22804,16 +22882,16 @@
         <v>210</v>
       </c>
       <c r="I6" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="J6" t="b">
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="L6" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="M6">
         <v>229</v>
@@ -22870,7 +22948,7 @@
         <v>-19.32433333</v>
       </c>
       <c r="AE6" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="AF6">
         <v>0.202222</v>
@@ -22923,10 +23001,10 @@
     </row>
     <row r="7" spans="1:48">
       <c r="A7" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2">
         <v>45416.33950978009</v>
@@ -22947,16 +23025,16 @@
         <v>240</v>
       </c>
       <c r="I7" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="J7" t="b">
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="L7" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="M7">
         <v>58</v>
@@ -23013,7 +23091,7 @@
         <v>-17.00766667</v>
       </c>
       <c r="AE7" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="AF7">
         <v>0.253333</v>
@@ -23066,10 +23144,10 @@
     </row>
     <row r="8" spans="1:48">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2">
         <v>45416.33988663195</v>
@@ -23090,16 +23168,16 @@
         <v>270</v>
       </c>
       <c r="I8" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="J8" t="b">
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
       <c r="L8" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
       <c r="M8">
         <v>63</v>
@@ -23156,7 +23234,7 @@
         <v>-15.34166667</v>
       </c>
       <c r="AE8" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="AF8">
         <v>0.182222</v>
@@ -23209,10 +23287,10 @@
     </row>
     <row r="9" spans="1:48">
       <c r="A9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2">
         <v>45416.34020414352</v>
@@ -23233,16 +23311,16 @@
         <v>300</v>
       </c>
       <c r="I9" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="J9" t="b">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="L9" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="M9">
         <v>26</v>
@@ -23299,7 +23377,7 @@
         <v>-16.246</v>
       </c>
       <c r="AE9" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="AF9">
         <v>-0.098889</v>
@@ -23352,10 +23430,10 @@
     </row>
     <row r="10" spans="1:48">
       <c r="A10" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2">
         <v>45416.34111480324</v>
@@ -23376,16 +23454,16 @@
         <v>379</v>
       </c>
       <c r="I10" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="J10" t="b">
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="L10" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
       <c r="M10">
         <v>74</v>
@@ -23442,7 +23520,7 @@
         <v>-17.04845833</v>
       </c>
       <c r="AE10" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="AF10">
         <v>-0.010972</v>
@@ -23495,10 +23573,10 @@
     </row>
     <row r="11" spans="1:48">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B11" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="C11" s="2">
         <v>45416.34197019676</v>
@@ -23519,16 +23597,16 @@
         <v>450</v>
       </c>
       <c r="I11" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="L11" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="M11">
         <v>11</v>
@@ -23585,7 +23663,7 @@
         <v>-14.07973333</v>
       </c>
       <c r="AE11" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="AF11">
         <v>0.064933</v>
@@ -23638,10 +23716,10 @@
     </row>
     <row r="12" spans="1:48">
       <c r="A12" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B12" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="C12" s="2">
         <v>45416.34597724537</v>
@@ -23662,16 +23740,16 @@
         <v>799</v>
       </c>
       <c r="I12" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="L12" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
       <c r="M12">
         <v>59</v>
@@ -23728,7 +23806,7 @@
         <v>-10.95321429</v>
       </c>
       <c r="AE12" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="AF12">
         <v>0.024423</v>
